--- a/metrics and parser/final_list_of_metrics.xlsx
+++ b/metrics and parser/final_list_of_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7672a64f9460fe35/Dokumente/HASEL/Research/DX Metrics Compass/repo/DPE-Metrics-main/metrics and parser/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1165" documentId="11_AD4DB114E441178AC67DF41BA6D2DCBA683EDF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E4C470-41E8-449D-8B44-A9E728CD687B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEB0E02-958F-44F7-8375-64E2B8A3FC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="30360" windowHeight="23385" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="cardsort_subgroup_IDs" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$N$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$N$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">urls!$A$1:$C$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="653">
   <si>
     <t>id</t>
   </si>
@@ -1144,9 +1144,6 @@
     <t>SPACE Framework</t>
   </si>
   <si>
-    <t>Microsoft (Azure)</t>
-  </si>
-  <si>
     <t>chime</t>
   </si>
   <si>
@@ -2165,13 +2162,118 @@
   </si>
   <si>
     <t>506; 501</t>
+  </si>
+  <si>
+    <t>https://newsletter.pragmaticengineer.com/p/how-tech-companies-measure-the-impact-of-ai</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>Orosz and Tacho (2025)</t>
+  </si>
+  <si>
+    <t>511a</t>
+  </si>
+  <si>
+    <t>Monzo</t>
+  </si>
+  <si>
+    <t>Adyen</t>
+  </si>
+  <si>
+    <t>Booking.com</t>
+  </si>
+  <si>
+    <t>Glassdoor</t>
+  </si>
+  <si>
+    <t>Webflow</t>
+  </si>
+  <si>
+    <t>Toast</t>
+  </si>
+  <si>
+    <t>eBay</t>
+  </si>
+  <si>
+    <t>CircleCI</t>
+  </si>
+  <si>
+    <t>CarGurus</t>
+  </si>
+  <si>
+    <t>Xero</t>
+  </si>
+  <si>
+    <t>511b</t>
+  </si>
+  <si>
+    <t>511c</t>
+  </si>
+  <si>
+    <t>511d</t>
+  </si>
+  <si>
+    <t>511e</t>
+  </si>
+  <si>
+    <t>511f</t>
+  </si>
+  <si>
+    <t>511g</t>
+  </si>
+  <si>
+    <t>511h</t>
+  </si>
+  <si>
+    <t>511i</t>
+  </si>
+  <si>
+    <t>511j</t>
+  </si>
+  <si>
+    <t>511k</t>
+  </si>
+  <si>
+    <t>511l</t>
+  </si>
+  <si>
+    <t>511m</t>
+  </si>
+  <si>
+    <t>511n</t>
+  </si>
+  <si>
+    <t>511o</t>
+  </si>
+  <si>
+    <t>511p</t>
+  </si>
+  <si>
+    <t>T-Mobile</t>
+  </si>
+  <si>
+    <t>Grammarly</t>
+  </si>
+  <si>
+    <t>DAU/WAU/MAU for AI tools</t>
+  </si>
+  <si>
+    <t>Daily, weekly or monthly active users of deployed AI tools.</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>511a; 511b; 511c; 511d; 511e; 511f; 511g; 511h; 511i; 511j; 511k; 511l; 511m; 511n; 511o; 511p</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2199,12 +2301,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <strike/>
@@ -2253,7 +2349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2301,7 +2397,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2314,16 +2422,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2369,6 +2467,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2389,21 +2497,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2489,21 +2597,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3073,14 +3181,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P112"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="7"/>
     <col min="2" max="2" width="36.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.5703125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="40.28515625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="36.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="40.28515625" style="20" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" style="7" customWidth="1"/>
     <col min="7" max="7" width="31.7109375" style="7" customWidth="1"/>
     <col min="8" max="9" width="17.85546875" style="7" customWidth="1"/>
@@ -3099,10 +3207,10 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="18" t="s">
         <v>276</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -3130,13 +3238,13 @@
         <v>10</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="120" x14ac:dyDescent="0.25">
@@ -3149,17 +3257,17 @@
       <c r="C2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="19" t="s">
         <v>564</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>563</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
@@ -3205,17 +3313,17 @@
       <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="20">
         <v>201</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>23</v>
@@ -3259,22 +3367,22 @@
         <v>25</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>548</v>
+        <v>279</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>547</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3288,7 +3396,7 @@
         <v>305</v>
       </c>
       <c r="L4" s="7">
-        <f t="shared" ref="L3:L63" si="3">IF(E4="-",0,1)+IF(D4="-",0,2)</f>
+        <f t="shared" ref="L4:L63" si="3">IF(E4="-",0,1)+IF(D4="-",0,2)</f>
         <v>3</v>
       </c>
       <c r="M4" s="7">
@@ -3317,17 +3425,17 @@
       <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>584</v>
+      <c r="D5" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>583</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
@@ -3371,22 +3479,22 @@
         <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>585</v>
+        <v>280</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>584</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3429,17 +3537,17 @@
       <c r="C7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="20">
         <v>183</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>12</v>
@@ -3485,17 +3593,17 @@
       <c r="C8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>566</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>567</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>38</v>
@@ -3541,17 +3649,17 @@
       <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="19">
         <v>170</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>38</v>
@@ -3597,17 +3705,17 @@
       <c r="C10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="D10" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E10" s="20">
         <v>501</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>45</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>38</v>
@@ -3653,17 +3761,17 @@
       <c r="C11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="D11" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E11" s="20">
         <v>501</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
@@ -3709,17 +3817,17 @@
       <c r="C12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>462</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>463</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>38</v>
@@ -3765,17 +3873,17 @@
       <c r="C13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>568</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>569</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>54</v>
@@ -3821,17 +3929,17 @@
       <c r="C14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="D14" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="E14" s="20">
         <v>131</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>57</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>38</v>
@@ -3875,19 +3983,19 @@
         <v>58</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>578</v>
+        <v>281</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>577</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>59</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>60</v>
@@ -3931,22 +4039,22 @@
         <v>62</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="D16" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>483</v>
+      <c r="E16" s="20" t="s">
+        <v>482</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>63</v>
       </c>
       <c r="G16" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
@@ -3989,17 +4097,17 @@
       <c r="C17" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>457</v>
+      <c r="D17" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
@@ -4043,19 +4151,19 @@
         <v>68</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="D18" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>443</v>
+      <c r="E18" s="20" t="s">
+        <v>442</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>54</v>
@@ -4101,17 +4209,17 @@
       <c r="C19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="20">
         <v>508</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>74</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
@@ -4157,17 +4265,17 @@
       <c r="C20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>586</v>
+      <c r="E20" s="20" t="s">
+        <v>585</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>78</v>
@@ -4213,17 +4321,17 @@
       <c r="C21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="D21" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="E21" s="20">
         <v>131</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>80</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>78</v>
@@ -4267,19 +4375,19 @@
         <v>30</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>607</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>466</v>
+      <c r="E22" s="20" t="s">
+        <v>465</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>81</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
@@ -4325,20 +4433,20 @@
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E23" s="8">
+      <c r="D23" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="E23" s="20">
         <v>501</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>84</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4379,19 +4487,19 @@
         <v>85</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="D24" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="20">
         <v>236</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>38</v>
@@ -4437,17 +4545,17 @@
       <c r="C25" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="20" t="s">
         <v>588</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>587</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>88</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>78</v>
@@ -4491,19 +4599,19 @@
         <v>89</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D26" s="7">
+        <v>285</v>
+      </c>
+      <c r="D26" s="19">
         <v>170</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>587</v>
+      <c r="E26" s="20" t="s">
+        <v>586</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>38</v>
@@ -4549,17 +4657,17 @@
       <c r="C27" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E27" s="8">
+      <c r="D27" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E27" s="20">
         <v>501</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>94</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>78</v>
@@ -4605,17 +4713,17 @@
       <c r="C28" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>457</v>
+      <c r="D28" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
@@ -4659,19 +4767,19 @@
         <v>98</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D29" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>570</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>571</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>99</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>23</v>
@@ -4717,20 +4825,20 @@
       <c r="C30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>457</v>
+      <c r="D30" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>101</v>
       </c>
       <c r="G30" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I30" s="7">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
@@ -4771,22 +4879,22 @@
         <v>103</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>572</v>
+        <v>287</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>571</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>104</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I31" s="7">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
@@ -4829,17 +4937,17 @@
       <c r="C32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="20">
         <v>506</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>12</v>
@@ -4883,19 +4991,19 @@
         <v>108</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>478</v>
+        <v>288</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>477</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>109</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>17</v>
@@ -4941,17 +5049,17 @@
       <c r="C34" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>457</v>
+      <c r="D34" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
@@ -4997,20 +5105,20 @@
       <c r="C35" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="20" t="s">
+        <v>554</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>555</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>556</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>113</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I35" s="7">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5051,22 +5159,22 @@
         <v>114</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>458</v>
+        <v>318</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>457</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>115</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I36" s="7">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5107,19 +5215,19 @@
         <v>116</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D37" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>614</v>
+      <c r="E37" s="20" t="s">
+        <v>613</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>117</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>38</v>
@@ -5165,20 +5273,20 @@
       <c r="C38" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>457</v>
+      <c r="D38" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>119</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I38" s="7">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
@@ -5221,17 +5329,17 @@
       <c r="C39" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>573</v>
+      <c r="D39" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>572</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>123</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>23</v>
@@ -5277,17 +5385,17 @@
       <c r="C40" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>479</v>
+      <c r="E40" s="20" t="s">
+        <v>478</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>126</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>23</v>
@@ -5333,17 +5441,17 @@
       <c r="C41" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="8" t="s">
-        <v>482</v>
+      <c r="E41" s="20" t="s">
+        <v>481</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>129</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>54</v>
@@ -5389,20 +5497,20 @@
       <c r="C42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>482</v>
+      <c r="E42" s="20" t="s">
+        <v>481</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>132</v>
       </c>
       <c r="G42" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I42" s="7">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5445,17 +5553,17 @@
       <c r="C43" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="20">
         <v>506</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>134</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>17</v>
@@ -5501,17 +5609,17 @@
       <c r="C44" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="20">
         <v>506</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>136</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
@@ -5555,22 +5663,22 @@
         <v>137</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>585</v>
+        <v>319</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>584</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>138</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I45" s="7">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -5613,17 +5721,17 @@
       <c r="C46" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="20">
         <v>509</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>141</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>12</v>
@@ -5667,22 +5775,22 @@
         <v>142</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D47" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D47" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="8" t="s">
-        <v>613</v>
+      <c r="E47" s="20" t="s">
+        <v>612</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>143</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I47" s="7">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
@@ -5723,22 +5831,22 @@
         <v>144</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>459</v>
+        <v>291</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>458</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>145</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I48" s="7">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -5781,17 +5889,17 @@
       <c r="C49" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>576</v>
+      <c r="D49" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>575</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>149</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>17</v>
@@ -5835,19 +5943,19 @@
         <v>150</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>475</v>
+        <v>292</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>474</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>152</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>38</v>
@@ -5893,17 +6001,17 @@
       <c r="C51" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="20">
         <v>201</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>154</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>23</v>
@@ -5947,19 +6055,19 @@
         <v>155</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D52" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="E52" s="20" t="s">
         <v>574</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>156</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>23</v>
@@ -6003,19 +6111,19 @@
         <v>157</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="D53" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D53" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="20">
         <v>235</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>158</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>54</v>
@@ -6061,17 +6169,17 @@
       <c r="C54" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>457</v>
+      <c r="D54" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>160</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>54</v>
@@ -6115,19 +6223,19 @@
         <v>161</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>460</v>
+        <v>295</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>459</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>162</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>78</v>
@@ -6171,19 +6279,19 @@
         <v>163</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="20" t="s">
         <v>297</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>298</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>164</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>38</v>
@@ -6229,17 +6337,17 @@
       <c r="C57" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>457</v>
+      <c r="D57" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>166</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>17</v>
@@ -6285,17 +6393,17 @@
       <c r="C58" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>457</v>
+      <c r="D58" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>168</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>12</v>
@@ -6341,17 +6449,17 @@
       <c r="C59" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>457</v>
+      <c r="D59" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>171</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>23</v>
@@ -6397,17 +6505,17 @@
       <c r="C60" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="20">
         <v>183</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>174</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>12</v>
@@ -6453,17 +6561,17 @@
       <c r="C61" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="E61" s="8">
+      <c r="D61" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="E61" s="20">
         <v>183</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>176</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>38</v>
@@ -6507,19 +6615,19 @@
         <v>177</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="D62" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D62" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>480</v>
+      <c r="E62" s="20" t="s">
+        <v>479</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>178</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -6565,20 +6673,20 @@
       <c r="C63" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>457</v>
+      <c r="D63" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G63" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I63" s="7">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -6621,20 +6729,20 @@
       <c r="C64" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="E64" s="20" t="s">
         <v>598</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>599</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>183</v>
       </c>
       <c r="G64" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I64" s="7">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
@@ -6677,17 +6785,17 @@
       <c r="C65" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>481</v>
+      <c r="D65" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>480</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>185</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>78</v>
@@ -6733,17 +6841,17 @@
       <c r="C66" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="20">
         <v>509</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>187</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>78</v>
@@ -6789,17 +6897,17 @@
       <c r="C67" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E67" s="8">
+      <c r="D67" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="E67" s="20">
         <v>202</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>189</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>38</v>
@@ -6845,17 +6953,17 @@
       <c r="C68" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="20">
         <v>509</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>191</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>12</v>
@@ -6899,22 +7007,22 @@
         <v>192</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D69" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D69" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>480</v>
+      <c r="E69" s="20" t="s">
+        <v>479</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>193</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I69" s="7">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
@@ -6957,17 +7065,17 @@
       <c r="C70" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E70" s="8">
+      <c r="D70" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="E70" s="20">
         <v>501</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>194</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>23</v>
@@ -7013,17 +7121,17 @@
       <c r="C71" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="E71" s="8" t="s">
+      <c r="D71" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="E71" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>196</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>17</v>
@@ -7069,17 +7177,17 @@
       <c r="C72" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>584</v>
+      <c r="D72" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>583</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>17</v>
@@ -7123,19 +7231,19 @@
         <v>199</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D73" t="s">
-        <v>551</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>442</v>
+        <v>320</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>441</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>200</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>38</v>
@@ -7181,17 +7289,17 @@
       <c r="C74" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D74" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="E74" s="8" t="s">
+      <c r="D74" s="19" t="s">
         <v>467</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>466</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>202</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>38</v>
@@ -7235,19 +7343,19 @@
         <v>203</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D75" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>558</v>
+      </c>
+      <c r="E75" s="20" t="s">
         <v>559</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>560</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>204</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>38</v>
@@ -7291,19 +7399,19 @@
         <v>205</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>579</v>
+        <v>301</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>578</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>206</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>17</v>
@@ -7349,17 +7457,17 @@
       <c r="C77" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>457</v>
+      <c r="D77" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>208</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>54</v>
@@ -7405,17 +7513,17 @@
       <c r="C78" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="20">
         <v>509</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>210</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>12</v>
@@ -7459,19 +7567,19 @@
         <v>211</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="E79" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D79" s="19" t="s">
         <v>469</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>468</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>212</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>78</v>
@@ -7517,17 +7625,17 @@
       <c r="C80" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D80" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>618</v>
+      <c r="D80" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>617</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>215</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>23</v>
@@ -7573,17 +7681,17 @@
       <c r="C81" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="20">
         <v>508</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>217</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>23</v>
@@ -7627,19 +7735,19 @@
         <v>218</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="D82">
+        <v>303</v>
+      </c>
+      <c r="D82" s="17">
         <v>209</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="20">
         <v>506</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>219</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>12</v>
@@ -7685,17 +7793,17 @@
       <c r="C83" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="20">
         <v>508</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>221</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>12</v>
@@ -7741,17 +7849,17 @@
       <c r="C84" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="20">
         <v>509</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>223</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>12</v>
@@ -7797,17 +7905,17 @@
       <c r="C85" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D85" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E85" s="8">
+      <c r="D85" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="E85" s="20">
         <v>501</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>226</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>17</v>
@@ -7853,20 +7961,20 @@
       <c r="C86" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="D86" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E86" s="8" t="s">
+      <c r="D86" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="E86" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>229</v>
       </c>
       <c r="G86" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H86" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I86" s="7">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
@@ -7907,19 +8015,19 @@
         <v>230</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="D87" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="E87" s="20" t="s">
         <v>580</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>581</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>231</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>23</v>
@@ -7965,17 +8073,17 @@
       <c r="C88" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="E88" s="20" t="s">
         <v>557</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>558</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>233</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>17</v>
@@ -8019,19 +8127,19 @@
         <v>234</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="D89" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="E89" s="20" t="s">
         <v>591</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>592</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>235</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>17</v>
@@ -8075,19 +8183,19 @@
         <v>236</v>
       </c>
       <c r="C90" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="D90" s="20" t="s">
         <v>605</v>
       </c>
-      <c r="D90" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>471</v>
+      <c r="E90" s="20" t="s">
+        <v>470</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>237</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>23</v>
@@ -8133,20 +8241,20 @@
       <c r="C91" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="20">
         <v>506</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>239</v>
       </c>
       <c r="G91" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="I91" s="7">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
@@ -8187,19 +8295,19 @@
         <v>241</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D92" t="s">
-        <v>590</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>593</v>
+        <v>321</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>592</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>242</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>60</v>
@@ -8245,17 +8353,17 @@
       <c r="C93" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="D93" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="20">
         <v>183</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>244</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>54</v>
@@ -8299,19 +8407,19 @@
         <v>245</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="E94" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D94" s="19" t="s">
         <v>472</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>471</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>246</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>38</v>
@@ -8357,17 +8465,17 @@
       <c r="C95" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>474</v>
+      <c r="D95" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>473</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>248</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>38</v>
@@ -8413,17 +8521,17 @@
       <c r="C96" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="20">
         <v>201</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>250</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>23</v>
@@ -8469,17 +8577,17 @@
       <c r="C97" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E97" s="8">
+      <c r="D97" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="E97" s="20">
         <v>501</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>253</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>17</v>
@@ -8525,17 +8633,17 @@
       <c r="C98" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D98" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>457</v>
+      <c r="D98" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>456</v>
       </c>
       <c r="F98" s="10" t="s">
         <v>255</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>17</v>
@@ -8579,19 +8687,19 @@
         <v>256</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>461</v>
+        <v>322</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>460</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>257</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>17</v>
@@ -8635,19 +8743,19 @@
         <v>258</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="D100" t="s">
-        <v>590</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>594</v>
+        <v>323</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>593</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>259</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>17</v>
@@ -8693,20 +8801,20 @@
       <c r="C101" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="E101" s="20" t="s">
         <v>561</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>562</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>262</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I101" s="7">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
@@ -8749,17 +8857,17 @@
       <c r="C102" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="E102" s="8">
+      <c r="D102" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="E102" s="20">
         <v>501</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>265</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>60</v>
@@ -8803,19 +8911,19 @@
         <v>266</v>
       </c>
       <c r="C103" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="E103" s="20" t="s">
         <v>308</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>309</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>268</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>60</v>
@@ -8861,17 +8969,17 @@
       <c r="C104" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="E104" s="8">
+      <c r="D104" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="E104" s="20">
         <v>501</v>
       </c>
       <c r="F104" s="10" t="s">
         <v>270</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>60</v>
@@ -8915,19 +9023,19 @@
         <v>271</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D105" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="E105" s="20" t="s">
         <v>582</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>583</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>272</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>60</v>
@@ -8973,20 +9081,20 @@
       <c r="C106" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="E106" s="20" t="s">
         <v>563</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>564</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>274</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I106" s="7">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
@@ -9024,22 +9132,22 @@
         <v>134</v>
       </c>
       <c r="B107" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D107" t="s">
-        <v>590</v>
-      </c>
-      <c r="E107" s="15" t="s">
-        <v>595</v>
+      <c r="D107" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>594</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G107" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H107" t="s">
         <v>38</v>
@@ -9080,25 +9188,25 @@
         <v>135</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E108" s="15">
+      <c r="E108" s="21">
         <v>183</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G108" t="s">
+        <v>544</v>
+      </c>
+      <c r="H108" t="s">
         <v>545</v>
-      </c>
-      <c r="H108" t="s">
-        <v>546</v>
       </c>
       <c r="I108" s="7">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
@@ -9136,22 +9244,22 @@
         <v>136</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E109" s="15">
+      <c r="E109" s="21">
         <v>240</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G109" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H109" t="s">
         <v>60</v>
@@ -9192,25 +9300,25 @@
         <v>137</v>
       </c>
       <c r="B110" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="D110" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="D110" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="15" t="s">
-        <v>316</v>
-      </c>
       <c r="F110" s="8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G110" t="s">
+        <v>544</v>
+      </c>
+      <c r="H110" t="s">
         <v>545</v>
-      </c>
-      <c r="H110" t="s">
-        <v>546</v>
       </c>
       <c r="I110" s="7">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
@@ -9248,22 +9356,22 @@
         <v>138</v>
       </c>
       <c r="B111" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E111" s="15">
+      <c r="E111" s="21">
         <v>236</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G111" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -9304,22 +9412,22 @@
         <v>139</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="7">
+      <c r="D112" s="19">
         <v>510</v>
       </c>
-      <c r="E112" s="8" t="s">
+      <c r="E112" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>23</v>
@@ -9355,8 +9463,148 @@
         <v>1</v>
       </c>
     </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113" s="7">
+        <v>140</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>652</v>
+      </c>
+      <c r="E113" s="20">
+        <v>511</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="7">
+        <f>VLOOKUP(H113,cardsort_group_IDs!A:B,2,0)</f>
+        <v>204</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113" s="7">
+        <f>VLOOKUP(J113,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>327</v>
+      </c>
+      <c r="L113" s="7">
+        <f>IF(E113="-",0,1)+IF(D113="-",0,2)</f>
+        <v>3</v>
+      </c>
+      <c r="M113" s="7">
+        <v>0</v>
+      </c>
+      <c r="N113" s="7">
+        <f t="shared" ref="N113" si="11">IF(D113="-",0,LEN(D113)-LEN(SUBSTITUTE(D113,";",""))+1)</f>
+        <v>16</v>
+      </c>
+      <c r="O113" s="7">
+        <f>IF(E113="-",0,LEN(E113)-LEN(SUBSTITUTE(E113,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="P113" s="7">
+        <f>SUM(N113:O113)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N114" s="7"/>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N115" s="7"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N116" s="7"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N117" s="7"/>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N118" s="7"/>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N119" s="7"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N120" s="7"/>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N121" s="7"/>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N122" s="7"/>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N123" s="7"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N124" s="7"/>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N125" s="7"/>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N126" s="7"/>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N127" s="7"/>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N128" s="7"/>
+    </row>
+    <row r="129" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N129" s="7"/>
+    </row>
+    <row r="130" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N130" s="7"/>
+    </row>
+    <row r="131" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N131" s="7"/>
+    </row>
+    <row r="132" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N132" s="7"/>
+    </row>
+    <row r="133" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N133" s="7"/>
+    </row>
+    <row r="134" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N134" s="7"/>
+    </row>
+    <row r="135" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N135" s="7"/>
+    </row>
+    <row r="136" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N136" s="7"/>
+    </row>
+    <row r="137" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N137" s="7"/>
+    </row>
+    <row r="138" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N138" s="7"/>
+    </row>
+    <row r="139" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N139" s="7"/>
+    </row>
+    <row r="140" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N140" s="7"/>
+    </row>
+    <row r="141" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N141" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N112" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B111">
     <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
@@ -9415,8 +9663,8 @@
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
     <cfRule type="duplicateValues" dxfId="17" priority="7"/>
@@ -9439,20 +9687,20 @@
     <cfRule type="duplicateValues" dxfId="10" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64">
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
     <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69">
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J106">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9461,1270 +9709,1458 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.140625" style="17"/>
     <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="85.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" t="s">
         <v>431</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>433</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="17">
         <v>5</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" t="s">
         <v>325</v>
       </c>
-      <c r="C2" s="15" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" t="s">
         <v>327</v>
       </c>
-      <c r="C3" s="15" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>329</v>
       </c>
-      <c r="C4" s="15" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="C5" s="15" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="15" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="C7" s="15" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="15" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C9" s="15" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C10" s="15" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>596</v>
+      </c>
+      <c r="C11" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>597</v>
-      </c>
-      <c r="C11" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C12" s="15" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C13" s="15" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C14" s="15" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="C15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C16" s="15" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C17" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>601</v>
-      </c>
-      <c r="C17" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C18" s="15" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C19" s="15" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C20" s="15" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>47</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C21" s="15" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>49</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="C22" s="15" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>50</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="C23" s="15" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>51</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C24" s="15" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="15" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C26" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="C26" s="15" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>62</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="C27" s="15" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>70</v>
+      </c>
+      <c r="B28" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>70</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="C28" s="15" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>87</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C29" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C29" s="15" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>616</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>92</v>
-      </c>
-      <c r="B30" t="s">
-        <v>617</v>
-      </c>
-      <c r="C30" s="15" t="s">
+    <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
+        <v>96</v>
+      </c>
+      <c r="B31" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>96</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C31" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="C31" s="15" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
+        <v>101</v>
+      </c>
+      <c r="B32" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>101</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="C32" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C32" s="15" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>105</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C33" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C33" s="15" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
+        <v>108</v>
+      </c>
+      <c r="B34" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>108</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="C34" s="15" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>111</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C35" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="C35" s="15" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="17">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>115</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C36" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>389</v>
-      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="17">
         <v>131</v>
       </c>
       <c r="B37" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="C37" s="15" t="s">
+    </row>
+    <row r="38" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17">
+        <v>146</v>
+      </c>
+      <c r="B38" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>146</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C38" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C38" s="15" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="17">
+        <v>160</v>
+      </c>
+      <c r="B39" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>160</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="C39" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>396</v>
-      </c>
     </row>
     <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="17">
         <v>170</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
       </c>
       <c r="C40" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="17">
+        <v>182</v>
+      </c>
+      <c r="B41" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>182</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="C41" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="C41" s="15" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
+        <v>183</v>
+      </c>
+      <c r="B42" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>183</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="C42" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="C42" s="15" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
+        <v>192</v>
+      </c>
+      <c r="B43" t="s">
+        <v>614</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>192</v>
-      </c>
-      <c r="B43" t="s">
-        <v>615</v>
-      </c>
-      <c r="C43" s="15" t="s">
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
+        <v>199</v>
+      </c>
+      <c r="B44" t="s">
+        <v>651</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>199</v>
-      </c>
-      <c r="B44" t="s">
-        <v>278</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>403</v>
-      </c>
-    </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="17">
         <v>201</v>
       </c>
       <c r="B45" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
+        <v>202</v>
+      </c>
+      <c r="B46" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>202</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="C46" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>406</v>
-      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="17">
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C47" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="A48" s="17">
         <v>209</v>
       </c>
       <c r="B48" t="s">
         <v>264</v>
       </c>
       <c r="C48" s="15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
+        <v>214</v>
+      </c>
+      <c r="B49" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>214</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="C49" s="15" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
+        <v>232</v>
+      </c>
+      <c r="B50" t="s">
         <v>408</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>232</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="C50" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C50" s="15" t="s">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
+        <v>233</v>
+      </c>
+      <c r="B51" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>233</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="C51" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="C51" s="15" t="s">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
+        <v>234</v>
+      </c>
+      <c r="B52" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>234</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="C52" s="15" t="s">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
+        <v>235</v>
+      </c>
+      <c r="B53" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>235</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C53" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="C53" s="15" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
+        <v>236</v>
+      </c>
+      <c r="B54" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>236</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C54" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="C54" s="15" t="s">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
+        <v>237</v>
+      </c>
+      <c r="B55" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>237</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C55" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="C55" s="15" t="s">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="17">
+        <v>238</v>
+      </c>
+      <c r="B56" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>238</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="C56" s="15" t="s">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="17">
+        <v>240</v>
+      </c>
+      <c r="B57" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>240</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="C57" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="C57" s="15" t="s">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="17">
+        <v>241</v>
+      </c>
+      <c r="B58" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>241</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="C58" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="C58" s="15" t="s">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="17">
+        <v>243</v>
+      </c>
+      <c r="B59" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>243</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="C59" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="C59" s="15" t="s">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="17">
+        <v>244</v>
+      </c>
+      <c r="B60" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>244</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="C60" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="C60" s="15" t="s">
-        <v>430</v>
-      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="A61" s="17">
         <v>501</v>
       </c>
       <c r="B61" t="s">
+        <v>434</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="17">
+        <v>502</v>
+      </c>
+      <c r="B62" t="s">
+        <v>436</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>502</v>
-      </c>
-      <c r="B62" t="s">
-        <v>437</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>436</v>
-      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="A63" s="17">
         <v>503</v>
       </c>
       <c r="B63" t="s">
         <v>277</v>
       </c>
       <c r="C63" s="15" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="17">
+        <v>504</v>
+      </c>
+      <c r="B64" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>504</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="C64" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="C64" s="15" t="s">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="17">
+        <v>505</v>
+      </c>
+      <c r="B65" t="s">
+        <v>437</v>
+      </c>
+      <c r="C65" s="15" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>505</v>
-      </c>
-      <c r="B65" t="s">
-        <v>438</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>487</v>
-      </c>
-    </row>
     <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66">
+      <c r="A66" s="17">
         <v>506</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
       </c>
       <c r="C66" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="17">
+        <v>507</v>
+      </c>
+      <c r="B67" t="s">
+        <v>651</v>
+      </c>
+      <c r="C67" s="15" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>507</v>
-      </c>
-      <c r="B67" t="s">
-        <v>278</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>440</v>
-      </c>
-    </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
+      <c r="A68" s="17">
         <v>508</v>
       </c>
       <c r="B68" t="s">
         <v>73</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="A69" s="17">
         <v>509</v>
       </c>
       <c r="B69" t="s">
         <v>140</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
+      <c r="A70" s="17">
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C70" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="B71" t="s">
         <v>499</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="C71" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>501</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
         <v>502</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>503</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="17" t="s">
         <v>504</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>505</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
         <v>506</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>507</v>
       </c>
       <c r="B75" t="s">
         <v>225</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="B76" t="s">
         <v>508</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
         <v>509</v>
       </c>
-      <c r="C76" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>510</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="17" t="s">
         <v>511</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>512</v>
       </c>
       <c r="B78" t="s">
         <v>122</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="B79" t="s">
+        <v>497</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
         <v>513</v>
       </c>
-      <c r="B79" t="s">
-        <v>498</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
+        <v>651</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="B81" t="s">
         <v>514</v>
       </c>
-      <c r="B80" t="s">
-        <v>278</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>476</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="C81" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="C81" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>516</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
         <v>517</v>
       </c>
-      <c r="C82" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>518</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
         <v>519</v>
       </c>
-      <c r="C83" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>520</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>521</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>522</v>
       </c>
       <c r="B85" t="s">
         <v>267</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="B86" t="s">
         <v>523</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
         <v>524</v>
       </c>
-      <c r="C86" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>525</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
         <v>526</v>
       </c>
-      <c r="C87" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>527</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="C88" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>529</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="C89" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>531</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="B91" t="s">
+        <v>529</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="B92" t="s">
+        <v>389</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="C90" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>534</v>
-      </c>
-      <c r="B91" t="s">
-        <v>530</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>535</v>
-      </c>
-      <c r="B92" t="s">
-        <v>390</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>533</v>
-      </c>
       <c r="B93" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>449</v>
+      <c r="A94" s="17" t="s">
+        <v>448</v>
       </c>
       <c r="B94" t="s">
         <v>151</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>577</v>
+      <c r="A95" s="17" t="s">
+        <v>576</v>
       </c>
       <c r="B95" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>590</v>
+      <c r="A96" s="17" t="s">
+        <v>589</v>
       </c>
       <c r="B96" t="s">
         <v>267</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>551</v>
+      <c r="A97" s="17" t="s">
+        <v>550</v>
       </c>
       <c r="B97" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="B98" t="s">
         <v>489</v>
       </c>
-      <c r="B98" t="s">
-        <v>490</v>
-      </c>
       <c r="C98" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>444</v>
+      <c r="A99" s="17" t="s">
+        <v>443</v>
       </c>
       <c r="B99" t="s">
         <v>83</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>445</v>
+      <c r="A100" s="17" t="s">
+        <v>444</v>
       </c>
       <c r="B100" t="s">
         <v>93</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="B101" t="s">
         <v>491</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="C101" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
         <v>493</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="C102" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
         <v>495</v>
       </c>
-      <c r="B103" t="s">
-        <v>496</v>
-      </c>
       <c r="C103" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>447</v>
+      <c r="A104" s="17" t="s">
+        <v>446</v>
       </c>
       <c r="B104" t="s">
         <v>21</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>450</v>
+      <c r="A105" s="17" t="s">
+        <v>449</v>
       </c>
       <c r="B105" t="s">
         <v>225</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>451</v>
+      <c r="A106" s="17" t="s">
+        <v>450</v>
       </c>
       <c r="B106" t="s">
         <v>122</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="B107" t="s">
         <v>497</v>
       </c>
-      <c r="B107" t="s">
-        <v>498</v>
-      </c>
       <c r="C107" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>452</v>
+      <c r="A108" s="17" t="s">
+        <v>451</v>
       </c>
       <c r="B108" t="s">
         <v>264</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B109" t="s">
+        <v>278</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="B109" t="s">
-        <v>279</v>
-      </c>
-      <c r="C109" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
+        <v>651</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="17" t="s">
         <v>455</v>
-      </c>
-      <c r="B110" t="s">
-        <v>278</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>456</v>
       </c>
       <c r="B111" t="s">
         <v>267</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>477</v>
+      <c r="A112" s="17" t="s">
+        <v>476</v>
       </c>
       <c r="B112" t="s">
         <v>41</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>554</v>
+      <c r="A113" s="17" t="s">
+        <v>553</v>
       </c>
       <c r="B113" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>549</v>
+      <c r="A114" s="17" t="s">
+        <v>548</v>
       </c>
       <c r="B114" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="B115" t="s">
+        <v>620</v>
+      </c>
+      <c r="C115" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="17" t="s">
+        <v>621</v>
+      </c>
+      <c r="B116" t="s">
+        <v>531</v>
+      </c>
+      <c r="C116" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="B117" t="s">
+        <v>389</v>
+      </c>
+      <c r="C117" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="17" t="s">
+        <v>633</v>
+      </c>
+      <c r="B118" t="s">
+        <v>499</v>
+      </c>
+      <c r="C118" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="17" t="s">
+        <v>634</v>
+      </c>
+      <c r="B119" t="s">
+        <v>622</v>
+      </c>
+      <c r="C119" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B120" t="s">
+        <v>225</v>
+      </c>
+      <c r="C120" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="17" t="s">
+        <v>636</v>
+      </c>
+      <c r="B121" t="s">
+        <v>623</v>
+      </c>
+      <c r="C121" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="B122" t="s">
+        <v>624</v>
+      </c>
+      <c r="C122" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="17" t="s">
+        <v>638</v>
+      </c>
+      <c r="B123" t="s">
+        <v>648</v>
+      </c>
+      <c r="C123" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="B124" t="s">
+        <v>625</v>
+      </c>
+      <c r="C124" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="B125" t="s">
+        <v>626</v>
+      </c>
+      <c r="C125" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="B126" t="s">
+        <v>627</v>
+      </c>
+      <c r="C126" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="B127" t="s">
+        <v>628</v>
+      </c>
+      <c r="C127" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="17" t="s">
+        <v>643</v>
+      </c>
+      <c r="B128" t="s">
+        <v>629</v>
+      </c>
+      <c r="C128" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="B129" t="s">
+        <v>630</v>
+      </c>
+      <c r="C129" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="17" t="s">
+        <v>645</v>
+      </c>
+      <c r="B130" t="s">
+        <v>647</v>
+      </c>
+      <c r="C130" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="B131" t="s">
+        <v>631</v>
+      </c>
+      <c r="C131" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C114" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C114">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C115">
       <sortCondition ref="A1:A114"/>
     </sortState>
   </autoFilter>
@@ -10758,7 +11194,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B3">
         <v>203</v>

--- a/metrics and parser/final_list_of_metrics.xlsx
+++ b/metrics and parser/final_list_of_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEB0E02-958F-44F7-8375-64E2B8A3FC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A1A81E-47E2-4560-8676-506DC6028078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="30360" windowHeight="23385" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="38115" windowHeight="23385" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -45,26 +45,20 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={F5E482B5-41C4-49D6-9F4E-4D4BE193AF28}</author>
     <author>tc={2443806D-D89D-4F46-8BFE-38F000C63452}</author>
     <author>tc={5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}</author>
     <author>tc={738F5169-58A9-48F4-8196-48D2F743B5DF}</author>
     <author>tc={B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}</author>
     <author>tc={E017DF4E-5656-4CEF-B774-80BA936A6D56}</author>
     <author>tc={8A92D669-9E50-4C59-82E5-97B139270D19}</author>
-    <author>tc={D1402E5C-7B54-496A-9313-5C695A9DF175}</author>
-    <author>tc={5A82E217-4A6B-46B7-9ADC-E64B4DF43DFC}</author>
     <author>tc={CD59760B-76A7-492D-B20B-A2D9CF3FBC59}</author>
     <author>tc={121DA4BD-014E-470E-AB44-B9514592A80F}</author>
     <author>tc={41A1A9E9-8671-443A-BC53-E9E6789FC6B2}</author>
-    <author>tc={D07C1F58-FF51-472F-B628-25B77946F3D6}</author>
     <author>tc={EF886BF9-B28D-42E1-9B64-C8A7E72E082A}</author>
     <author>tc={7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}</author>
     <author>tc={917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}</author>
     <author>tc={FDDDF671-A2B6-4958-A032-5551C66219BE}</author>
-    <author>tc={9BD6282E-AAD8-44B3-94D7-6BADCF15D5F0}</author>
     <author>tc={9ABBA003-3752-4178-8927-349ABCC5DB99}</author>
-    <author>tc={2F0223C9-C77F-4AA1-8A90-F4A399ADDA2A}</author>
     <author>tc={80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}</author>
     <author>tc={45640671-D7E4-4EA6-9099-D4E52C010FD7}</author>
     <author>tc={EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}</author>
@@ -72,18 +66,9 @@
     <author>tc={FCC3DA67-C366-4123-AE95-236C8FC56568}</author>
     <author>tc={24A13EBD-8030-4299-B820-E3DBAA902DCC}</author>
     <author>tc={65177E12-2939-4BCC-8B47-DB95E81C94F5}</author>
-    <author>tc={35A9EE27-ABF3-44C5-B07F-C1029F352D07}</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{F5E482B5-41C4-49D6-9F4E-4D4BE193AF28}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von Business zu Process geändert.</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="1" shapeId="0" xr:uid="{2443806D-D89D-4F46-8BFE-38F000C63452}">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{2443806D-D89D-4F46-8BFE-38F000C63452}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -91,7 +76,7 @@
     Nach Andres Input von „Coding“ zu „Produced Code“ geändert</t>
       </text>
     </comment>
-    <comment ref="C15" authorId="2" shapeId="0" xr:uid="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
+    <comment ref="C15" authorId="1" shapeId="0" xr:uid="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -99,7 +84,7 @@
     Nach Andres Input zusammengefasst zu einem Eintrag.</t>
       </text>
     </comment>
-    <comment ref="H28" authorId="3" shapeId="0" xr:uid="{738F5169-58A9-48F4-8196-48D2F743B5DF}">
+    <comment ref="H28" authorId="2" shapeId="0" xr:uid="{738F5169-58A9-48F4-8196-48D2F743B5DF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -107,7 +92,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="4" shapeId="0" xr:uid="{B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}">
+    <comment ref="B29" authorId="3" shapeId="0" xr:uid="{B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -115,7 +100,7 @@
     Umbenannt von „Developer Build Time“ to  „Local Build Time“ nach Andres Input.</t>
       </text>
     </comment>
-    <comment ref="C29" authorId="5" shapeId="0" xr:uid="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
+    <comment ref="C29" authorId="4" shapeId="0" xr:uid="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -125,7 +110,7 @@
     „Application/Package Build Duration“ von Lattice nach Andres Input ergänzt.</t>
       </text>
     </comment>
-    <comment ref="D29" authorId="6" shapeId="0" xr:uid="{8A92D669-9E50-4C59-82E5-97B139270D19}">
+    <comment ref="D29" authorId="5" shapeId="0" xr:uid="{8A92D669-9E50-4C59-82E5-97B139270D19}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -133,23 +118,7 @@
     Lattice von NextJS Page Compilation Duration</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="7" shapeId="0" xr:uid="{D1402E5C-7B54-496A-9313-5C695A9DF175}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Input von Andre „Satisfaction“ und „Satisfaction with Engineering System“ integriert.</t>
-      </text>
-    </comment>
-    <comment ref="D31" authorId="8" shapeId="0" xr:uid="{5A82E217-4A6B-46B7-9ADC-E64B4DF43DFC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Postman hinzugefügt von Satisfaction</t>
-      </text>
-    </comment>
-    <comment ref="B33" authorId="9" shapeId="0" xr:uid="{CD59760B-76A7-492D-B20B-A2D9CF3FBC59}">
+    <comment ref="B33" authorId="6" shapeId="0" xr:uid="{CD59760B-76A7-492D-B20B-A2D9CF3FBC59}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -157,7 +126,7 @@
     note that meta calls PRs/MRs diffs</t>
       </text>
     </comment>
-    <comment ref="H34" authorId="10" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
+    <comment ref="H34" authorId="7" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -165,7 +134,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="C52" authorId="11" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
+    <comment ref="C52" authorId="8" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -173,15 +142,7 @@
     „Time to Restore Services“ ergänzt nach Andres Input.</t>
       </text>
     </comment>
-    <comment ref="D52" authorId="12" shapeId="0" xr:uid="{D07C1F58-FF51-472F-B628-25B77946F3D6}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    McKinsey Framework; Peloton ergänzt von Time to Restore Services</t>
-      </text>
-    </comment>
-    <comment ref="B54" authorId="13" shapeId="0" xr:uid="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
+    <comment ref="B54" authorId="9" shapeId="0" xr:uid="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -189,7 +150,7 @@
     Name gekürzt nach Andres Input.</t>
       </text>
     </comment>
-    <comment ref="H58" authorId="14" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
+    <comment ref="H58" authorId="10" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -197,7 +158,7 @@
     Nach Andres Input von DevEx zu Business/HR gewechselt.</t>
       </text>
     </comment>
-    <comment ref="H61" authorId="15" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
+    <comment ref="H61" authorId="11" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -205,7 +166,7 @@
     Nach Andres Input von Business zu Quality verschoben.</t>
       </text>
     </comment>
-    <comment ref="J69" authorId="16" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
+    <comment ref="J69" authorId="12" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -213,15 +174,7 @@
     Von Knowledge Expansion zu Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="B75" authorId="17" shapeId="0" xr:uid="{9BD6282E-AAD8-44B3-94D7-6BADCF15D5F0}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Angepasst nach Andres Input. Zuvor „Quality“.</t>
-      </text>
-    </comment>
-    <comment ref="C76" authorId="18" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
+    <comment ref="C76" authorId="13" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -229,7 +182,23 @@
     Nach Andres Kommentar zu einer Metrik zusammengefasst.</t>
       </text>
     </comment>
-    <comment ref="H76" authorId="19" shapeId="0" xr:uid="{2F0223C9-C77F-4AA1-8A90-F4A399ADDA2A}">
+    <comment ref="B77" authorId="14" shapeId="0" xr:uid="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Name angepasst nach Andres Input. Ursprünglich „Quality of Reviews of Work Contributed by Team Members“</t>
+      </text>
+    </comment>
+    <comment ref="C80" authorId="15" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Nach Andres Input Availability hinzugefügt.</t>
+      </text>
+    </comment>
+    <comment ref="H85" authorId="16" shapeId="0" xr:uid="{EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -237,31 +206,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="B77" authorId="20" shapeId="0" xr:uid="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Name angepasst nach Andres Input. Ursprünglich „Quality of Reviews of Work Contributed by Team Members“</t>
-      </text>
-    </comment>
-    <comment ref="C80" authorId="21" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input Availability hinzugefügt.</t>
-      </text>
-    </comment>
-    <comment ref="H85" authorId="22" shapeId="0" xr:uid="{EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von Business zu Process verschoben.</t>
-      </text>
-    </comment>
-    <comment ref="C90" authorId="23" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
+    <comment ref="C90" authorId="17" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -269,7 +214,7 @@
     Nach Andres Input. Production Incidents und System Uptime / Availability hinzugefügt.</t>
       </text>
     </comment>
-    <comment ref="F90" authorId="24" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
+    <comment ref="F90" authorId="18" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -277,7 +222,7 @@
     Nach Andres Input angepasst.</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="25" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
+    <comment ref="H91" authorId="19" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -285,7 +230,7 @@
     Nach Andres Anregung von Business zu DevEx/Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="26" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
+    <comment ref="C92" authorId="20" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -293,20 +238,12 @@
     Zusammengefasst nach Andres Input</t>
       </text>
     </comment>
-    <comment ref="F94" authorId="27" shapeId="0" xr:uid="{35A9EE27-ABF3-44C5-B07F-C1029F352D07}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Definition ausgeweitet.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="699">
   <si>
     <t>id</t>
   </si>
@@ -474,9 +411,6 @@
   </si>
   <si>
     <t>Code Rework Rate</t>
-  </si>
-  <si>
-    <t>Code Churn and Rework</t>
   </si>
   <si>
     <t>Is the percentage of code changes that modify recently changed code.</t>
@@ -1123,12 +1057,6 @@
     <t>The weekly number of design documents generated per engineer.</t>
   </si>
   <si>
-    <t>Weekly Number of Diffs / PR per Developer</t>
-  </si>
-  <si>
-    <t>The weekly Number of diffs / Pull Requests per developer.</t>
-  </si>
-  <si>
     <t>Weekly Time Loss</t>
   </si>
   <si>
@@ -1171,9 +1099,6 @@
     <t>Developer Build Time (P50 and P90); Build Time; NextJS Page Compilation Duration; Application/Package Build Duration; Build Time Efficiency</t>
   </si>
   <si>
-    <t>Developer CSAT; Developer Experience Index (DXI); Developer Satisfaction Score; Developer Sentiment; Developer Survey with a Focus on Perceptions of Friction; DSAT (Developer Satisfaction); Employee satisfaction; Net User Satisfaction (NSAT); Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; Developer Ratings for the New System</t>
-  </si>
-  <si>
     <t>Diff Authoring Time (DAT); Diffs per Engineer (PRs or MRs); Commits Performed by Time; Time Spent per Task; Commit Count, Implementation Time per User Story; Task Completion Time; Coding Time; Time to Commit per LOC Changed</t>
   </si>
   <si>
@@ -1207,12 +1132,6 @@
     <t>New Security Vulnerabilities Introduced</t>
   </si>
   <si>
-    <t>Number of Spikes Executed</t>
-  </si>
-  <si>
-    <t>Unit Test Quality; Code Quality; Process Quality; System Quality</t>
-  </si>
-  <si>
     <t>Self-Service Documentation; Written Communication Effectiveness Through Design Documents</t>
   </si>
   <si>
@@ -1279,9 +1198,6 @@
     <t>PR Time in Review; Code Review Time; Review Time; Median Wall-Clock Review Time; Median Wall-Clock Merge Time</t>
   </si>
   <si>
-    <t>Time to Release; Feature Delivery Time</t>
-  </si>
-  <si>
     <t>D’Angelo et al. (2024)</t>
   </si>
   <si>
@@ -1699,9 +1615,6 @@
     <t>105; 501; 131</t>
   </si>
   <si>
-    <t>131q; 131r</t>
-  </si>
-  <si>
     <t>131m; 131n</t>
   </si>
   <si>
@@ -1963,12 +1876,6 @@
     <t>32a</t>
   </si>
   <si>
-    <t>131l; 32a</t>
-  </si>
-  <si>
-    <t>131s; 131t; 32a</t>
-  </si>
-  <si>
     <t>5a</t>
   </si>
   <si>
@@ -1984,9 +1891,6 @@
     <t xml:space="preserve">5; 501; 115; 183; </t>
   </si>
   <si>
-    <t>501m; 5a</t>
-  </si>
-  <si>
     <t>503; 9; 17; 5; 115; 501; 115; 183; 182</t>
   </si>
   <si>
@@ -2002,12 +1906,6 @@
     <t>160; 501; 146</t>
   </si>
   <si>
-    <t>501a; 501b; 501k</t>
-  </si>
-  <si>
-    <t>501c; 131h; 501g; 202a</t>
-  </si>
-  <si>
     <t>509; 505; 506; 508; 9; 160; 501; 131; 202; 183; 146</t>
   </si>
   <si>
@@ -2029,9 +1927,6 @@
     <t>501; 146</t>
   </si>
   <si>
-    <t>501o; 131a; 131d; 131m; 202a</t>
-  </si>
-  <si>
     <t>508; 506; 9; 50; 160; 131; 202; 182; 146</t>
   </si>
   <si>
@@ -2053,9 +1948,6 @@
     <t>50; 183</t>
   </si>
   <si>
-    <t>501n; 501j; 209</t>
-  </si>
-  <si>
     <t>9; 36; 52; 62; 240; 243; 244; 160; 501; 183</t>
   </si>
   <si>
@@ -2074,9 +1966,6 @@
     <t>505; 506; 509; 508; 9; 96; 160; 501; 131; 202; 146; 182</t>
   </si>
   <si>
-    <t>146b; 131k; 131b; 202a; 501k; 146a; 209</t>
-  </si>
-  <si>
     <t>232a</t>
   </si>
   <si>
@@ -2101,15 +1990,9 @@
     <t>Meyer et al. (2014)</t>
   </si>
   <si>
-    <t>501e; 501d; 501k; 5a; 203</t>
-  </si>
-  <si>
     <t>5; 160; 501; 19; 39</t>
   </si>
   <si>
-    <t>501m; 131p; 32a; 232a</t>
-  </si>
-  <si>
     <t>Meyer et al. (2017)</t>
   </si>
   <si>
@@ -2119,21 +2002,12 @@
     <t>Slack</t>
   </si>
   <si>
-    <t>501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510</t>
-  </si>
-  <si>
     <t>Stability; Stability (CFR and MTTR); Stability of Services/Apps; Production Incidents; System Uptime / Availability; CI Stability</t>
   </si>
   <si>
     <t>501b; 501a; 131k; 131j; 510</t>
   </si>
   <si>
-    <t>Time From Creating a Patch to Patch Release; Time to Value; Time to Merge (TTM)</t>
-  </si>
-  <si>
-    <t>501m; 131i; 501d; 209; 510</t>
-  </si>
-  <si>
     <t>Test Failure Rate</t>
   </si>
   <si>
@@ -2266,14 +2140,215 @@
     <t>Microsoft</t>
   </si>
   <si>
-    <t>511a; 511b; 511c; 511d; 511e; 511f; 511g; 511h; 511i; 511j; 511k; 511l; 511m; 511n; 511o; 511p</t>
+    <t>Utilization</t>
+  </si>
+  <si>
+    <t>Related Metrics</t>
+  </si>
+  <si>
+    <t>PRs assisted by AI</t>
+  </si>
+  <si>
+    <t>Percentage of Pull Requests assisted by AI</t>
+  </si>
+  <si>
+    <t>511e; 511g</t>
+  </si>
+  <si>
+    <t>Code written by AI</t>
+  </si>
+  <si>
+    <t>Percentage of code drafted or submitted by AI</t>
+  </si>
+  <si>
+    <t>501m; 131p; 32a; 232a; 511b</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>501a; 501b; 501k; 511a; 511b; 511c; 511d; 511e; 511f; 511g; 511h; 511i; 511j; 511k; 511l; 511m; 511n; 511o; 511p</t>
+  </si>
+  <si>
+    <t>AI Specific Category</t>
+  </si>
+  <si>
+    <t>Acceptance rate of AI suggestions</t>
+  </si>
+  <si>
+    <t>511b; 511e; 511h; 511o; 511p</t>
+  </si>
+  <si>
+    <t>Metric used for various aspect, such as estimating how much AI code reaches production, satisfaction proxy or for product decisions.</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>AI Power users</t>
+  </si>
+  <si>
+    <t>AI Spend</t>
+  </si>
+  <si>
+    <t>Unused AI licenses</t>
+  </si>
+  <si>
+    <t>Identifying power users to help exchanging best practices.</t>
+  </si>
+  <si>
+    <t>Identifying unused AI licenses to foster adoption or save costs.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>% capacity worked per AI tool</t>
+  </si>
+  <si>
+    <t>511b; 511c; 511e; 511h; 511i</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Costs or capacity of AI use.</t>
+  </si>
+  <si>
+    <t>AI adoption in products</t>
+  </si>
+  <si>
+    <t>Monitors AI being built into products, not just used by engineers.</t>
+  </si>
+  <si>
+    <t>511q</t>
+  </si>
+  <si>
+    <t>Vanguard</t>
+  </si>
+  <si>
+    <t>AI usage intensity; AI usage events; % of developers using AI chat features; AI model usage; AI developer tool adoption</t>
+  </si>
+  <si>
+    <t>511a; 511b; 511c; 511d; 511e; 511f; 511g; 511h; 511i; 511j; 511k; 511l; 511m; 511n; 511o; 511p; 511q</t>
+  </si>
+  <si>
+    <t>Time savings</t>
+  </si>
+  <si>
+    <t>Estimated time savings from using AI</t>
+  </si>
+  <si>
+    <t>511a; 511c; 511d; 411f; 511g; 511k; 511l; 511n; 511q; 511p</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Throughput</t>
+  </si>
+  <si>
+    <t>The number of features, stories, PRs / diffs, … completed per developer within a time interval (e.g. week).</t>
+  </si>
+  <si>
+    <t>501n; 501j; 209; 511e; 511g; 511a; 511c; 511d; 511e; 511f; 511g; 511j; 511k; 511m; 511n; 511p</t>
+  </si>
+  <si>
+    <t>501c; 131h; 501g; 202a; 511a; 511c; 511d; 511r; 511f; 511g; 511j; 511k; 511m; 511i</t>
+  </si>
+  <si>
+    <t>511r</t>
+  </si>
+  <si>
+    <t>Time From Creating a Patch to Patch Release; Time to Value; Time to Merge (TTM); PR Cycle Time</t>
+  </si>
+  <si>
+    <t>501m; 131i; 501d; 209; 510; 511b; 511r; 511m; 511h; 511q; 511p</t>
+  </si>
+  <si>
+    <t>Unit Test Quality; Code Quality; Process Quality; System Quality; Code Maintainability</t>
+  </si>
+  <si>
+    <t>501m; 5a; 511a; 511f</t>
+  </si>
+  <si>
+    <t>Developers' confidence that a change won't change production</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>146b; 131k; 131b; 202a; 501k; 146a; 209; 511i; 511d</t>
+  </si>
+  <si>
+    <t>202a; 511i; 511l</t>
+  </si>
+  <si>
+    <t>501o; 131a; 131d; 131m; 202a; 511i; 511l</t>
+  </si>
+  <si>
+    <t>Innovation rate</t>
+  </si>
+  <si>
+    <t>511a; 511j; 511h</t>
+  </si>
+  <si>
+    <t>Developer CSAT; Developer Experience Index (DXI); Developer Satisfaction Score; Developer Sentiment; Developer Survey with a Focus on Perceptions of Friction; DSAT (Developer Satisfaction); Employee satisfaction; Net User Satisfaction (NSAT); Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; Developer Ratings for the New System; AI tool CSAT; Bad developer days</t>
+  </si>
+  <si>
+    <t>501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; t11k; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r</t>
+  </si>
+  <si>
+    <t>Time to Release; Feature Delivery Time; Innovation Velocity</t>
+  </si>
+  <si>
+    <t>232a; 511r</t>
+  </si>
+  <si>
+    <t>131s; 131t; 32a; 511b</t>
+  </si>
+  <si>
+    <t>AI change/Trust confidence</t>
+  </si>
+  <si>
+    <t>511a; 511b</t>
+  </si>
+  <si>
+    <t>501e; 501d; 501k; 5a; 203; 511b</t>
+  </si>
+  <si>
+    <t>Friction</t>
+  </si>
+  <si>
+    <t>511b; 511l</t>
+  </si>
+  <si>
+    <t>Monitors friction introduced or removed across the developer workflow.</t>
+  </si>
+  <si>
+    <t>40; 46; 59</t>
+  </si>
+  <si>
+    <t>131l; 32a; 511b; 511h</t>
+  </si>
+  <si>
+    <t>PR revert rate</t>
+  </si>
+  <si>
+    <t>131q; 131r; 511k</t>
+  </si>
+  <si>
+    <t>202a; 511i</t>
+  </si>
+  <si>
+    <t>232a; 511i</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2306,6 +2381,12 @@
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2349,7 +2430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2410,6 +2491,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2422,6 +2506,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2632,16 +2726,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3088,9 +3172,6 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H2" dT="2025-06-02T18:30:48.15" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{F5E482B5-41C4-49D6-9F4E-4D4BE193AF28}">
-    <text>Nach Andres Input von Business zu Process geändert.</text>
-  </threadedComment>
   <threadedComment ref="B15" dT="2025-05-23T08:50:23.62" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{2443806D-D89D-4F46-8BFE-38F000C63452}">
     <text>Nach Andres Input von „Coding“ zu „Produced Code“ geändert</text>
   </threadedComment>
@@ -3113,12 +3194,6 @@
   <threadedComment ref="D29" dT="2025-05-23T09:41:06.69" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{8A92D669-9E50-4C59-82E5-97B139270D19}">
     <text>Lattice von NextJS Page Compilation Duration</text>
   </threadedComment>
-  <threadedComment ref="C31" dT="2025-05-23T13:55:02.64" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{D1402E5C-7B54-496A-9313-5C695A9DF175}">
-    <text>Nach Input von Andre „Satisfaction“ und „Satisfaction with Engineering System“ integriert.</text>
-  </threadedComment>
-  <threadedComment ref="D31" dT="2025-05-23T13:55:40.77" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{5A82E217-4A6B-46B7-9ADC-E64B4DF43DFC}">
-    <text>Postman hinzugefügt von Satisfaction</text>
-  </threadedComment>
   <threadedComment ref="B33" dT="2025-04-03T11:15:23.43" personId="{9D9142B8-11C7-4802-A1A1-66D498664CB5}" id="{CD59760B-76A7-492D-B20B-A2D9CF3FBC59}">
     <text>note that meta calls PRs/MRs diffs</text>
   </threadedComment>
@@ -3127,9 +3202,6 @@
   </threadedComment>
   <threadedComment ref="C52" dT="2025-05-23T09:31:57.03" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
     <text>„Time to Restore Services“ ergänzt nach Andres Input.</text>
-  </threadedComment>
-  <threadedComment ref="D52" dT="2025-05-23T09:32:20.44" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{D07C1F58-FF51-472F-B628-25B77946F3D6}">
-    <text>McKinsey Framework; Peloton ergänzt von Time to Restore Services</text>
   </threadedComment>
   <threadedComment ref="B54" dT="2025-05-23T09:06:49.45" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
     <text>Name gekürzt nach Andres Input.</text>
@@ -3143,14 +3215,8 @@
   <threadedComment ref="J69" dT="2025-06-03T11:54:41.83" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
     <text>Von Knowledge Expansion zu Upskilling gewechselt.</text>
   </threadedComment>
-  <threadedComment ref="B75" dT="2025-06-02T14:08:28.18" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{9BD6282E-AAD8-44B3-94D7-6BADCF15D5F0}">
-    <text>Angepasst nach Andres Input. Zuvor „Quality“.</text>
-  </threadedComment>
   <threadedComment ref="C76" dT="2025-06-02T18:24:12.03" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
     <text>Nach Andres Kommentar zu einer Metrik zusammengefasst.</text>
-  </threadedComment>
-  <threadedComment ref="H76" dT="2025-06-02T18:38:57.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{2F0223C9-C77F-4AA1-8A90-F4A399ADDA2A}">
-    <text>Nach Andres Input von Business zu Process verschoben.</text>
   </threadedComment>
   <threadedComment ref="B77" dT="2025-05-23T09:24:06.88" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
     <text>Name angepasst nach Andres Input. Ursprünglich „Quality of Reviews of Work Contributed by Team Members“</text>
@@ -3173,15 +3239,12 @@
   <threadedComment ref="C92" dT="2025-05-23T08:56:36.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
     <text>Zusammengefasst nach Andres Input</text>
   </threadedComment>
-  <threadedComment ref="F94" dT="2025-06-02T14:24:01.73" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{35A9EE27-ABF3-44C5-B07F-C1029F352D07}">
-    <text>Definition ausgeweitet.</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="7"/>
@@ -3194,10 +3257,13 @@
     <col min="8" max="9" width="17.85546875" style="7" customWidth="1"/>
     <col min="10" max="13" width="28.42578125" style="7" customWidth="1"/>
     <col min="14" max="14" width="28.42578125" style="9" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="7"/>
+    <col min="15" max="16" width="9.140625" style="7"/>
+    <col min="17" max="17" width="18.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3208,10 +3274,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3238,16 +3304,22 @@
         <v>10</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>641</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3258,16 +3330,16 @@
         <v>15</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>564</v>
+        <v>640</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
@@ -3292,7 +3364,7 @@
       </c>
       <c r="N2" s="7">
         <f>IF(D2="-",0,LEN(D2)-LEN(SUBSTITUTE(D2,";",""))+1)</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="O2" s="7">
         <f>IF(E2="-",0,LEN(E2)-LEN(SUBSTITUTE(E2,";",""))+1)</f>
@@ -3300,10 +3372,16 @@
       </c>
       <c r="P2" s="7">
         <f>SUM(N2:O2)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>4</v>
       </c>
@@ -3323,7 +3401,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>23</v>
@@ -3358,8 +3436,14 @@
         <f t="shared" ref="P3:P63" si="2">SUM(N3:O3)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q3" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>7</v>
       </c>
@@ -3367,22 +3451,22 @@
         <v>25</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3414,8 +3498,14 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q4" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>9</v>
       </c>
@@ -3426,16 +3516,16 @@
         <v>11</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
@@ -3470,8 +3560,14 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q5" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>10</v>
       </c>
@@ -3479,22 +3575,22 @@
         <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3526,8 +3622,14 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q6" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R6" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>11</v>
       </c>
@@ -3547,7 +3649,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>12</v>
@@ -3582,8 +3684,14 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q7" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>12</v>
       </c>
@@ -3594,16 +3702,16 @@
         <v>11</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>565</v>
+        <v>669</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>38</v>
@@ -3628,7 +3736,7 @@
       </c>
       <c r="N8" s="7">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" si="1"/>
@@ -3636,10 +3744,16 @@
       </c>
       <c r="P8" s="7">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="165" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R8" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>13</v>
       </c>
@@ -3659,7 +3773,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>38</v>
@@ -3694,8 +3808,14 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q9" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>14</v>
       </c>
@@ -3706,7 +3826,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="E10" s="20">
         <v>501</v>
@@ -3715,7 +3835,7 @@
         <v>45</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>38</v>
@@ -3750,8 +3870,14 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="Q10" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>15</v>
       </c>
@@ -3762,7 +3888,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="E11" s="20">
         <v>501</v>
@@ -3771,7 +3897,7 @@
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
@@ -3806,8 +3932,14 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q11" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>16</v>
       </c>
@@ -3818,16 +3950,16 @@
         <v>11</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>38</v>
@@ -3862,8 +3994,14 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q12" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>17</v>
       </c>
@@ -3874,16 +4012,16 @@
         <v>52</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>54</v>
@@ -3918,8 +4056,14 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q13" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R13" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>18</v>
       </c>
@@ -3927,19 +4071,19 @@
         <v>55</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>56</v>
+        <v>695</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>463</v>
+        <v>696</v>
       </c>
       <c r="E14" s="20">
         <v>131</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>38</v>
@@ -3964,7 +4108,7 @@
       </c>
       <c r="N14" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" si="1"/>
@@ -3972,40 +4116,46 @@
       </c>
       <c r="P14" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R14" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>19</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="I15" s="7">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K15" s="7">
         <f>VLOOKUP(J15,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4020,7 +4170,7 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" si="1"/>
@@ -4028,40 +4178,46 @@
       </c>
       <c r="P15" s="7">
         <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R15" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>20</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>474</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="G16" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K16" s="7">
         <f>VLOOKUP(J16,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4086,28 +4242,34 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q16" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R16" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>22</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="G17" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
@@ -4142,28 +4304,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q17" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R17" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>23</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>54</v>
@@ -4173,7 +4341,7 @@
         <v>206</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K18" s="7">
         <f>VLOOKUP(J18,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4198,13 +4366,19 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="Q18" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R18" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>24</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>11</v>
@@ -4216,10 +4390,10 @@
         <v>508</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
@@ -4254,31 +4428,37 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q19" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R19" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>25</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="I20" s="7">
         <f>VLOOKUP(H20,cardsort_group_IDs!A:B,2,0)</f>
@@ -4310,31 +4490,37 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q20" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R20" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>26</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="E21" s="20">
         <v>131</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I21" s="7">
         <f>VLOOKUP(H21,cardsort_group_IDs!A:B,2,0)</f>
@@ -4366,8 +4552,14 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q21" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R21" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>27</v>
       </c>
@@ -4375,19 +4567,19 @@
         <v>30</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>606</v>
+        <v>671</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>607</v>
+        <v>672</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
@@ -4412,7 +4604,7 @@
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O22" s="7">
         <f t="shared" si="1"/>
@@ -4420,33 +4612,39 @@
       </c>
       <c r="P22" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R22" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>28</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E23" s="20">
         <v>501</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4478,16 +4676,22 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q23" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R23" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>29</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>11</v>
@@ -4496,10 +4700,10 @@
         <v>236</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>38</v>
@@ -4534,38 +4738,44 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q24" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R24" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>30</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>572</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>587</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="G25" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I25" s="7">
         <f>VLOOKUP(H25,cardsort_group_IDs!A:B,2,0)</f>
         <v>208</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K25" s="7">
         <f>VLOOKUP(J25,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4580,7 +4790,7 @@
       </c>
       <c r="N25" s="7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O25" s="7">
         <f t="shared" si="1"/>
@@ -4588,30 +4798,36 @@
       </c>
       <c r="P25" s="7">
         <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>31</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D26" s="19">
         <v>170</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>38</v>
@@ -4621,7 +4837,7 @@
         <v>205</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K26" s="7">
         <f>VLOOKUP(J26,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4646,38 +4862,44 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q26" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R26" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>32</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E27" s="20">
         <v>501</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I27" s="7">
         <f>VLOOKUP(H27,cardsort_group_IDs!A:B,2,0)</f>
         <v>208</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K27" s="7">
         <f>VLOOKUP(J27,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4702,28 +4924,34 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q27" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>33</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="G28" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
@@ -4733,7 +4961,7 @@
         <v>204</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K28" s="7">
         <f>VLOOKUP(J28,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4758,28 +4986,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q28" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R28" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>34</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>99</v>
-      </c>
       <c r="G29" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>23</v>
@@ -4814,38 +5048,44 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q29" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R29" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>35</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>101</v>
-      </c>
       <c r="G30" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I30" s="7">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K30" s="7">
         <f>VLOOKUP(J30,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4870,38 +5110,44 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="165" x14ac:dyDescent="0.25">
+      <c r="Q30" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R30" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="180" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>36</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>603</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="G31" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I31" s="7">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K31" s="7">
         <f>VLOOKUP(J31,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4916,7 +5162,7 @@
       </c>
       <c r="N31" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="O31" s="7">
         <f t="shared" si="1"/>
@@ -4924,15 +5170,21 @@
       </c>
       <c r="P31" s="7">
         <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="255" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="Q31" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R31" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="255" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>37</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>11</v>
@@ -4944,10 +5196,10 @@
         <v>506</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>12</v>
@@ -4982,28 +5234,34 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+      <c r="Q32" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R32" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>551</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>477</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>109</v>
-      </c>
       <c r="G33" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>17</v>
@@ -5028,7 +5286,7 @@
       </c>
       <c r="N33" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O33" s="7">
         <f t="shared" si="1"/>
@@ -5036,30 +5294,36 @@
       </c>
       <c r="P33" s="7">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="Q33" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R33" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>39</v>
       </c>
       <c r="B34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="G34" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
@@ -5069,7 +5333,7 @@
         <v>204</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K34" s="7">
         <f>VLOOKUP(J34,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5094,38 +5358,44 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q34" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R34" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>40</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="G35" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I35" s="7">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K35" s="7">
         <f>VLOOKUP(J35,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5150,38 +5420,44 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q35" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R35" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>41</v>
       </c>
       <c r="B36" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>115</v>
-      </c>
       <c r="G36" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I36" s="7">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K36" s="7">
         <f>VLOOKUP(J36,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5206,28 +5482,34 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q36" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R36" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>42</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>613</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>117</v>
-      </c>
       <c r="G37" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>38</v>
@@ -5262,38 +5544,44 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q37" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R37" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>43</v>
       </c>
       <c r="B38" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="G38" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I38" s="7">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K38" s="7">
         <f>VLOOKUP(J38,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5318,28 +5606,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q38" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R38" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>44</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>23</v>
@@ -5349,7 +5643,7 @@
         <v>202</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K39" s="7">
         <f>VLOOKUP(J39,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5374,28 +5668,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q39" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R39" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>45</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>478</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>126</v>
-      </c>
       <c r="G40" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>23</v>
@@ -5405,7 +5705,7 @@
         <v>202</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K40" s="7">
         <f>VLOOKUP(J40,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5430,28 +5730,34 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q40" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R40" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>46</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>129</v>
-      </c>
       <c r="G41" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>54</v>
@@ -5461,7 +5767,7 @@
         <v>206</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K41" s="7">
         <f>VLOOKUP(J41,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5486,31 +5792,37 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q41" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R41" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>50</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="G42" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I42" s="7">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5542,13 +5854,19 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R42" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>51</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>11</v>
@@ -5560,10 +5878,10 @@
         <v>506</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>17</v>
@@ -5598,13 +5916,19 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q43" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R43" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>54</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>11</v>
@@ -5616,10 +5940,10 @@
         <v>506</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
@@ -5654,38 +5978,44 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+      <c r="Q44" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R44" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>56</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>584</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="G45" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I45" s="7">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K45" s="7">
         <f>VLOOKUP(J45,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5710,13 +6040,19 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q45" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R45" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>57</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>11</v>
@@ -5728,10 +6064,10 @@
         <v>509</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>12</v>
@@ -5766,38 +6102,44 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="360" x14ac:dyDescent="0.25">
+      <c r="Q46" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R46" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="360" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>58</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>612</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>143</v>
-      </c>
       <c r="G47" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I47" s="7">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K47" s="7">
         <f>VLOOKUP(J47,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5805,14 +6147,14 @@
       </c>
       <c r="L47" s="7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M47" s="7">
         <v>0</v>
       </c>
       <c r="N47" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="7">
         <f t="shared" si="1"/>
@@ -5820,33 +6162,39 @@
       </c>
       <c r="P47" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R47" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>59</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>145</v>
-      </c>
       <c r="G48" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I48" s="7">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -5878,28 +6226,34 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q48" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R48" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>62</v>
       </c>
       <c r="B49" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="D49" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>149</v>
-      </c>
       <c r="G49" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>17</v>
@@ -5924,7 +6278,7 @@
       </c>
       <c r="N49" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O49" s="7">
         <f t="shared" si="1"/>
@@ -5932,30 +6286,36 @@
       </c>
       <c r="P49" s="7">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R49" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>63</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>448</v>
+        <v>697</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>38</v>
@@ -5980,7 +6340,7 @@
       </c>
       <c r="N50" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="7">
         <f t="shared" si="1"/>
@@ -5988,15 +6348,21 @@
       </c>
       <c r="P50" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R50" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>64</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>11</v>
@@ -6008,10 +6374,10 @@
         <v>11</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>23</v>
@@ -6046,28 +6412,34 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="Q51" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R51" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>65</v>
       </c>
       <c r="B52" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="G52" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>23</v>
@@ -6077,7 +6449,7 @@
         <v>202</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K52" s="7">
         <f>VLOOKUP(J52,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6092,7 +6464,7 @@
       </c>
       <c r="N52" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O52" s="7">
         <f t="shared" si="1"/>
@@ -6100,18 +6472,24 @@
       </c>
       <c r="P52" s="7">
         <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R52" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>66</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>11</v>
@@ -6120,10 +6498,10 @@
         <v>235</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>54</v>
@@ -6158,28 +6536,34 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q53" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R53" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>67</v>
       </c>
       <c r="B54" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>160</v>
-      </c>
       <c r="G54" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>54</v>
@@ -6189,7 +6573,7 @@
         <v>206</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K54" s="7">
         <f>VLOOKUP(J54,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6214,38 +6598,44 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R54" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>69</v>
       </c>
       <c r="B55" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>162</v>
-      </c>
       <c r="G55" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I55" s="7">
         <f>VLOOKUP(H55,cardsort_group_IDs!A:B,2,0)</f>
         <v>208</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K55" s="7">
         <f>VLOOKUP(J55,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6270,28 +6660,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q55" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R55" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>70</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="G56" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>38</v>
@@ -6326,28 +6722,34 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q56" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R56" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>71</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>166</v>
-      </c>
       <c r="G57" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>17</v>
@@ -6382,28 +6784,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q57" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R57" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>72</v>
       </c>
       <c r="B58" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>168</v>
-      </c>
       <c r="G58" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>12</v>
@@ -6413,7 +6821,7 @@
         <v>201</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K58" s="7">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6438,28 +6846,34 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q58" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R58" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>73</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="G59" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>23</v>
@@ -6469,7 +6883,7 @@
         <v>202</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K59" s="7">
         <f>VLOOKUP(J59,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6494,13 +6908,19 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q59" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R59" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>74</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>11</v>
@@ -6512,10 +6932,10 @@
         <v>183</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>12</v>
@@ -6550,28 +6970,34 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q60" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R60" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>75</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E61" s="20">
         <v>183</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>38</v>
@@ -6581,7 +7007,7 @@
         <v>205</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K61" s="7">
         <f>VLOOKUP(J61,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6606,28 +7032,34 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q61" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R61" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>76</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>479</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="G62" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -6637,7 +7069,7 @@
         <v>201</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K62" s="7">
         <f>VLOOKUP(J62,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6662,31 +7094,37 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q62" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R62" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>77</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="G63" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I63" s="7">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -6718,38 +7156,44 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q63" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R63" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>78</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D64" s="19" t="s">
-        <v>597</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>598</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>183</v>
-      </c>
       <c r="G64" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I64" s="7">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K64" s="7">
         <f>VLOOKUP(J64,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6764,7 +7208,7 @@
       </c>
       <c r="N64" s="7">
         <f t="shared" ref="N64:N112" si="5">IF(D64="-",0,LEN(D64)-LEN(SUBSTITUTE(D64,";",""))+1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O64" s="7">
         <f t="shared" ref="O64:O111" si="6">IF(E64="-",0,LEN(E64)-LEN(SUBSTITUTE(E64,";",""))+1)</f>
@@ -6772,40 +7216,46 @@
       </c>
       <c r="P64" s="7">
         <f t="shared" ref="P64:P111" si="7">SUM(N64:O64)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="Q64" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R64" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>79</v>
       </c>
       <c r="B65" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>185</v>
-      </c>
       <c r="G65" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I65" s="7">
         <f>VLOOKUP(H65,cardsort_group_IDs!A:B,2,0)</f>
         <v>208</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K65" s="7">
         <f>VLOOKUP(J65,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6830,13 +7280,19 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="165" x14ac:dyDescent="0.25">
+      <c r="Q65" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R65" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>80</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>11</v>
@@ -6848,13 +7304,13 @@
         <v>509</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I66" s="7">
         <f>VLOOKUP(H66,cardsort_group_IDs!A:B,2,0)</f>
@@ -6886,28 +7342,34 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q66" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R66" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>81</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="E67" s="20">
         <v>202</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>38</v>
@@ -6917,7 +7379,7 @@
         <v>205</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K67" s="7">
         <f>VLOOKUP(J67,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6942,13 +7404,19 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q67" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R67" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>82</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>11</v>
@@ -6960,10 +7428,10 @@
         <v>509</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>12</v>
@@ -6973,7 +7441,7 @@
         <v>201</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K68" s="7">
         <f>VLOOKUP(J68,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6998,38 +7466,44 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q68" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R68" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>83</v>
       </c>
       <c r="B69" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>479</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>193</v>
-      </c>
       <c r="G69" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I69" s="7">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K69" s="7">
         <f>VLOOKUP(J69,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7037,14 +7511,14 @@
       </c>
       <c r="L69" s="7">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M69" s="7">
         <v>0</v>
       </c>
       <c r="N69" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O69" s="7">
         <f t="shared" si="6"/>
@@ -7052,30 +7526,36 @@
       </c>
       <c r="P69" s="7">
         <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R69" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>84</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E70" s="20">
         <v>501</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>23</v>
@@ -7085,7 +7565,7 @@
         <v>202</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K70" s="7">
         <f>VLOOKUP(J70,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7110,28 +7590,34 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q70" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R70" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>85</v>
       </c>
       <c r="B71" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="G71" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>17</v>
@@ -7166,28 +7652,34 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+      <c r="Q71" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R71" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>87</v>
       </c>
       <c r="B72" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>198</v>
-      </c>
       <c r="G72" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>17</v>
@@ -7222,28 +7714,34 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q72" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R72" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>88</v>
       </c>
       <c r="B73" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="D73" s="17" t="s">
-        <v>550</v>
-      </c>
-      <c r="E73" s="20" t="s">
-        <v>441</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>200</v>
-      </c>
       <c r="G73" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>38</v>
@@ -7253,7 +7751,7 @@
         <v>205</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K73" s="7">
         <f>VLOOKUP(J73,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7278,28 +7776,34 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q73" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R73" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>89</v>
       </c>
       <c r="B74" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="G74" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>38</v>
@@ -7309,7 +7813,7 @@
         <v>205</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K74" s="7">
         <f>VLOOKUP(J74,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7334,28 +7838,34 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q74" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R74" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>90</v>
       </c>
       <c r="B75" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="F75" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>558</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="G75" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>38</v>
@@ -7365,7 +7875,7 @@
         <v>205</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K75" s="7">
         <f>VLOOKUP(J75,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7380,7 +7890,7 @@
       </c>
       <c r="N75" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O75" s="7">
         <f t="shared" si="6"/>
@@ -7388,30 +7898,36 @@
       </c>
       <c r="P75" s="7">
         <f t="shared" si="7"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="Q75" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R75" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>91</v>
       </c>
       <c r="B76" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="E76" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>206</v>
-      </c>
       <c r="G76" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>17</v>
@@ -7421,7 +7937,7 @@
         <v>204</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K76" s="7">
         <f>VLOOKUP(J76,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7446,28 +7962,34 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q76" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R76" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>92</v>
       </c>
       <c r="B77" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F77" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E77" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="G77" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>54</v>
@@ -7477,7 +7999,7 @@
         <v>206</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K77" s="7">
         <f>VLOOKUP(J77,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7502,13 +8024,19 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q77" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R77" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>93</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>11</v>
@@ -7520,10 +8048,10 @@
         <v>509</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>12</v>
@@ -7558,38 +8086,44 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q78" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R78" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>94</v>
       </c>
       <c r="B79" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="E79" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>212</v>
-      </c>
       <c r="G79" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I79" s="7">
         <f>VLOOKUP(H79,cardsort_group_IDs!A:B,2,0)</f>
         <v>208</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K79" s="7">
         <f>VLOOKUP(J79,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7614,28 +8148,34 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q79" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R79" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>95</v>
       </c>
       <c r="B80" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="D80" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D80" s="20" t="s">
-        <v>450</v>
-      </c>
-      <c r="E80" s="20" t="s">
-        <v>617</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="G80" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>23</v>
@@ -7645,7 +8185,7 @@
         <v>202</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K80" s="7">
         <f>VLOOKUP(J80,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7670,13 +8210,19 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q80" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R80" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>97</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>11</v>
@@ -7688,10 +8234,10 @@
         <v>508</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>23</v>
@@ -7701,7 +8247,7 @@
         <v>202</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K81" s="7">
         <f>VLOOKUP(J81,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7726,16 +8272,22 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q81" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R81" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>98</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D82" s="17">
         <v>209</v>
@@ -7744,10 +8296,10 @@
         <v>506</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>12</v>
@@ -7757,7 +8309,7 @@
         <v>201</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K82" s="7">
         <f>VLOOKUP(J82,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7782,13 +8334,19 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R82" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>99</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>11</v>
@@ -7800,10 +8358,10 @@
         <v>508</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>12</v>
@@ -7813,7 +8371,7 @@
         <v>201</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K83" s="7">
         <f>VLOOKUP(J83,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7838,13 +8396,19 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q83" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R83" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>100</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>11</v>
@@ -7856,10 +8420,10 @@
         <v>509</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>12</v>
@@ -7869,7 +8433,7 @@
         <v>201</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K84" s="7">
         <f>VLOOKUP(J84,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7894,28 +8458,34 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q84" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R84" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>102</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="E85" s="20">
         <v>501</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>17</v>
@@ -7925,7 +8495,7 @@
         <v>204</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K85" s="7">
         <f>VLOOKUP(J85,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7950,38 +8520,44 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q85" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R85" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>104</v>
       </c>
       <c r="B86" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="D86" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="D86" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="E86" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>229</v>
-      </c>
       <c r="G86" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I86" s="7">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K86" s="7">
         <f>VLOOKUP(J86,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8006,28 +8582,34 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q86" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R86" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>105</v>
       </c>
       <c r="B87" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="F87" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="D87" s="20" t="s">
-        <v>579</v>
-      </c>
-      <c r="E87" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>231</v>
-      </c>
       <c r="G87" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>23</v>
@@ -8037,7 +8619,7 @@
         <v>202</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K87" s="7">
         <f>VLOOKUP(J87,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8062,28 +8644,34 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" ht="180" x14ac:dyDescent="0.25">
+      <c r="Q87" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R87" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="180" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>107</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="F88" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D88" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>233</v>
-      </c>
       <c r="G88" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>17</v>
@@ -8118,28 +8706,34 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q88" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R88" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>108</v>
       </c>
       <c r="B89" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="F89" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>590</v>
-      </c>
-      <c r="E89" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>235</v>
-      </c>
       <c r="G89" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>17</v>
@@ -8174,28 +8768,34 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q89" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R89" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>109</v>
       </c>
       <c r="B90" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="F90" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>605</v>
-      </c>
-      <c r="E90" s="20" t="s">
-        <v>470</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>237</v>
-      </c>
       <c r="G90" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>23</v>
@@ -8205,7 +8805,7 @@
         <v>202</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K90" s="7">
         <f>VLOOKUP(J90,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8230,13 +8830,19 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q90" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R90" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>112</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>11</v>
@@ -8248,20 +8854,20 @@
         <v>506</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I91" s="7">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K91" s="7">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8286,38 +8892,44 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+      <c r="Q91" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R91" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>114</v>
       </c>
       <c r="B92" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="E92" s="20" t="s">
-        <v>592</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>242</v>
-      </c>
       <c r="G92" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I92" s="7">
         <f>VLOOKUP(H92,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K92" s="7">
         <f>VLOOKUP(J92,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8342,13 +8954,19 @@
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q92" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R92" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>115</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>11</v>
@@ -8360,10 +8978,10 @@
         <v>183</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>54</v>
@@ -8373,7 +8991,7 @@
         <v>206</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K93" s="7">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8398,28 +9016,34 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q93" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R93" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>116</v>
       </c>
       <c r="B94" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="F94" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="E94" s="20" t="s">
-        <v>471</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>246</v>
-      </c>
       <c r="G94" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>38</v>
@@ -8429,7 +9053,7 @@
         <v>205</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K94" s="7">
         <f>VLOOKUP(J94,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8454,8 +9078,14 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q94" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R94" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>117</v>
       </c>
@@ -8463,19 +9093,19 @@
         <v>43</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>38</v>
@@ -8510,13 +9140,19 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q95" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R95" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>118</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>11</v>
@@ -8528,10 +9164,10 @@
         <v>11</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>23</v>
@@ -8541,7 +9177,7 @@
         <v>202</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K96" s="7">
         <f>VLOOKUP(J96,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8566,28 +9202,34 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q96" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R96" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>119</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="E97" s="20">
         <v>501</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>17</v>
@@ -8622,28 +9264,34 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R97" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>120</v>
       </c>
       <c r="B98" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="E98" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>255</v>
-      </c>
       <c r="G98" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>17</v>
@@ -8678,28 +9326,34 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q98" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R98" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>121</v>
       </c>
       <c r="B99" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D99" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="E99" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>257</v>
-      </c>
       <c r="G99" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>17</v>
@@ -8724,7 +9378,7 @@
       </c>
       <c r="N99" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O99" s="7">
         <f t="shared" si="6"/>
@@ -8732,30 +9386,36 @@
       </c>
       <c r="P99" s="7">
         <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="Q99" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R99" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>122</v>
       </c>
       <c r="B100" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="F100" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D100" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="E100" s="20" t="s">
-        <v>593</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>259</v>
-      </c>
       <c r="G100" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>17</v>
@@ -8780,7 +9440,7 @@
       </c>
       <c r="N100" s="7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100" s="7">
         <f t="shared" si="6"/>
@@ -8788,40 +9448,46 @@
       </c>
       <c r="P100" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R100" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>124</v>
       </c>
       <c r="B101" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="D101" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>550</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="D101" s="19" t="s">
-        <v>560</v>
-      </c>
-      <c r="E101" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>262</v>
-      </c>
       <c r="G101" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I101" s="7">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K101" s="7">
         <f>VLOOKUP(J101,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8846,38 +9512,44 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q101" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R101" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>126</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E102" s="20">
         <v>501</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I102" s="7">
         <f>VLOOKUP(H102,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K102" s="7">
         <f>VLOOKUP(J102,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8902,38 +9574,44 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q102" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R102" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>127</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I103" s="7">
         <f>VLOOKUP(H103,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K103" s="7">
         <f>VLOOKUP(J103,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8958,38 +9636,44 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q103" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R103" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>128</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E104" s="20">
         <v>501</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I104" s="7">
         <f>VLOOKUP(H104,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K104" s="7">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9014,38 +9698,44 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q104" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R104" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>129</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>271</v>
+        <v>666</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>581</v>
+        <v>668</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>272</v>
+        <v>667</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I105" s="7">
         <f>VLOOKUP(H105,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K105" s="7">
         <f>VLOOKUP(J105,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9060,7 +9750,7 @@
       </c>
       <c r="N105" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="O105" s="7">
         <f t="shared" si="6"/>
@@ -9068,40 +9758,46 @@
       </c>
       <c r="P105" s="7">
         <f t="shared" si="7"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="Q105" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R105" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>130</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I106" s="7">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K106" s="7">
         <f>VLOOKUP(J106,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9126,28 +9822,34 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q106" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R106" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>134</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>589</v>
+        <v>698</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="G107" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H107" t="s">
         <v>38</v>
@@ -9157,7 +9859,7 @@
         <v>205</v>
       </c>
       <c r="J107" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K107" s="7">
         <f>VLOOKUP(J107,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9172,7 +9874,7 @@
       </c>
       <c r="N107" s="7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O107" s="7">
         <f t="shared" si="6"/>
@@ -9180,15 +9882,21 @@
       </c>
       <c r="P107" s="7">
         <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="Q107" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R107" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>135</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>11</v>
@@ -9200,20 +9908,20 @@
         <v>183</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="G108" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H108" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I108" s="7">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K108" s="7">
         <f>VLOOKUP(J108,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9238,13 +9946,19 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q108" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R108" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>136</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>11</v>
@@ -9256,20 +9970,20 @@
         <v>240</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G109" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H109" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I109" s="7">
         <f>VLOOKUP(H109,cardsort_group_IDs!A:B,2,0)</f>
         <v>207</v>
       </c>
       <c r="J109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K109" s="7">
         <f>VLOOKUP(J109,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9294,38 +10008,44 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q109" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R109" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>137</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D110" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E110" s="21" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G110" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H110" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I110" s="7">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K110" s="7">
         <f>VLOOKUP(J110,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9350,16 +10070,22 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q110" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R110" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>138</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D111" s="19" t="s">
         <v>11</v>
@@ -9368,10 +10094,10 @@
         <v>236</v>
       </c>
       <c r="F111" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="G111" t="s">
         <v>535</v>
-      </c>
-      <c r="G111" t="s">
-        <v>543</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -9406,13 +10132,19 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q111" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R111" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>139</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>11</v>
@@ -9424,10 +10156,10 @@
         <v>11</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>23</v>
@@ -9437,7 +10169,7 @@
         <v>202</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K112" s="7">
         <f>VLOOKUP(J112,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9462,28 +10194,34 @@
         <f t="shared" ref="P112" si="10">SUM(N112:O112)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q112" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R112" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>140</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>11</v>
+        <v>660</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>652</v>
-      </c>
-      <c r="E113" s="20">
-        <v>511</v>
+        <v>661</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>17</v>
@@ -9501,67 +10239,664 @@
       </c>
       <c r="L113" s="7">
         <f>IF(E113="-",0,1)+IF(D113="-",0,2)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M113" s="7">
         <v>0</v>
       </c>
       <c r="N113" s="7">
-        <f t="shared" ref="N113" si="11">IF(D113="-",0,LEN(D113)-LEN(SUBSTITUTE(D113,";",""))+1)</f>
-        <v>16</v>
+        <f t="shared" ref="N113:N114" si="11">IF(D113="-",0,LEN(D113)-LEN(SUBSTITUTE(D113,";",""))+1)</f>
+        <v>17</v>
       </c>
       <c r="O113" s="7">
         <f>IF(E113="-",0,LEN(E113)-LEN(SUBSTITUTE(E113,";",""))+1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113" s="7">
         <f>SUM(N113:O113)</f>
         <v>17</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N114" s="7"/>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N115" s="7"/>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N116" s="7"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N117" s="7"/>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N118" s="7"/>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N119" s="7"/>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N120" s="7"/>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N121" s="7"/>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N122" s="7"/>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N123" s="7"/>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q113" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="R113" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" s="7">
+        <v>141</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I114" s="7">
+        <f>VLOOKUP(H114,cardsort_group_IDs!A:B,2,0)</f>
+        <v>207</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K114" s="7">
+        <f>VLOOKUP(J114,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>312</v>
+      </c>
+      <c r="L114" s="7">
+        <f>IF(E114="-",0,1)+IF(D114="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M114" s="7">
+        <v>0</v>
+      </c>
+      <c r="N114" s="7">
+        <f t="shared" ref="N114:N115" si="12">IF(D114="-",0,LEN(D114)-LEN(SUBSTITUTE(D114,";",""))+1)</f>
+        <v>2</v>
+      </c>
+      <c r="O114" s="7">
+        <f>IF(E114="-",0,LEN(E114)-LEN(SUBSTITUTE(E114,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P114" s="7">
+        <f>SUM(N114:O114)</f>
+        <v>2</v>
+      </c>
+      <c r="Q114" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="R114" s="19">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A115" s="7">
+        <v>142</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I115" s="7">
+        <f>VLOOKUP(H115,cardsort_group_IDs!A:B,2,0)</f>
+        <v>207</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K115" s="7">
+        <f>VLOOKUP(J115,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>312</v>
+      </c>
+      <c r="L115" s="7">
+        <f>IF(E115="-",0,1)+IF(D115="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M115" s="7">
+        <v>1</v>
+      </c>
+      <c r="N115" s="7">
+        <f t="shared" ref="N115" si="13">IF(D115="-",0,LEN(D115)-LEN(SUBSTITUTE(D115,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O115" s="7">
+        <f>IF(E115="-",0,LEN(E115)-LEN(SUBSTITUTE(E115,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P115" s="7">
+        <f>SUM(N115:O115)</f>
+        <v>1</v>
+      </c>
+      <c r="Q115" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="R115" s="19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A116" s="7">
+        <v>143</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I116" s="7">
+        <f>VLOOKUP(H116,cardsort_group_IDs!A:B,2,0)</f>
+        <v>207</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K116" s="7">
+        <f>VLOOKUP(J116,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>312</v>
+      </c>
+      <c r="L116" s="7">
+        <f>IF(E116="-",0,1)+IF(D116="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M116" s="7">
+        <v>2</v>
+      </c>
+      <c r="N116" s="7">
+        <f t="shared" ref="N116" si="14">IF(D116="-",0,LEN(D116)-LEN(SUBSTITUTE(D116,";",""))+1)</f>
+        <v>5</v>
+      </c>
+      <c r="O116" s="7">
+        <f>IF(E116="-",0,LEN(E116)-LEN(SUBSTITUTE(E116,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P116" s="7">
+        <f>SUM(N116:O116)</f>
+        <v>5</v>
+      </c>
+      <c r="Q116" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="R116" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A117" s="7">
+        <v>144</v>
+      </c>
+      <c r="B117" t="s">
+        <v>646</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" s="7">
+        <f>VLOOKUP(H117,cardsort_group_IDs!A:B,2,0)</f>
+        <v>204</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K117" s="7">
+        <f>VLOOKUP(J117,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>327</v>
+      </c>
+      <c r="L117" s="7">
+        <f>IF(E117="-",0,1)+IF(D117="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M117" s="7">
+        <v>3</v>
+      </c>
+      <c r="N117" s="7">
+        <f t="shared" ref="N117" si="15">IF(D117="-",0,LEN(D117)-LEN(SUBSTITUTE(D117,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O117" s="7">
+        <f>IF(E117="-",0,LEN(E117)-LEN(SUBSTITUTE(E117,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P117" s="7">
+        <f>SUM(N117:O117)</f>
+        <v>1</v>
+      </c>
+      <c r="Q117" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="R117" s="19" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A118" s="7">
+        <v>145</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" s="7">
+        <f>VLOOKUP(H118,cardsort_group_IDs!A:B,2,0)</f>
+        <v>201</v>
+      </c>
+      <c r="J118" t="s">
+        <v>19</v>
+      </c>
+      <c r="K118" s="7">
+        <f>VLOOKUP(J118,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>302</v>
+      </c>
+      <c r="L118" s="7">
+        <f t="shared" ref="L118:L119" si="16">IF(E118="-",0,1)+IF(D118="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M118" s="7">
+        <v>4</v>
+      </c>
+      <c r="N118" s="7">
+        <f t="shared" ref="N118:N119" si="17">IF(D118="-",0,LEN(D118)-LEN(SUBSTITUTE(D118,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O118" s="7">
+        <f t="shared" ref="O118:O119" si="18">IF(E118="-",0,LEN(E118)-LEN(SUBSTITUTE(E118,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P118" s="7">
+        <f t="shared" ref="P118:P119" si="19">SUM(N118:O118)</f>
+        <v>1</v>
+      </c>
+      <c r="Q118" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="R118" s="19" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A119" s="7">
+        <v>146</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="D119" t="s">
+        <v>653</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" s="7">
+        <f>VLOOKUP(H119,cardsort_group_IDs!A:B,2,0)</f>
+        <v>201</v>
+      </c>
+      <c r="J119" t="s">
+        <v>19</v>
+      </c>
+      <c r="K119" s="7">
+        <f>VLOOKUP(J119,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>302</v>
+      </c>
+      <c r="L119" s="7">
+        <f t="shared" ref="L119" si="20">IF(E119="-",0,1)+IF(D119="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M119" s="7">
+        <v>5</v>
+      </c>
+      <c r="N119" s="7">
+        <f t="shared" ref="N119" si="21">IF(D119="-",0,LEN(D119)-LEN(SUBSTITUTE(D119,";",""))+1)</f>
+        <v>5</v>
+      </c>
+      <c r="O119" s="7">
+        <f t="shared" ref="O119:O122" si="22">IF(E119="-",0,LEN(E119)-LEN(SUBSTITUTE(E119,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P119" s="7">
+        <f t="shared" ref="P119:P122" si="23">SUM(N119:O119)</f>
+        <v>5</v>
+      </c>
+      <c r="Q119" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="R119" s="19" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A120" s="7">
+        <v>147</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" s="7">
+        <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
+        <v>204</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" s="7">
+        <f>VLOOKUP(J120,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>327</v>
+      </c>
+      <c r="L120" s="7">
+        <f t="shared" ref="L120" si="24">IF(E120="-",0,1)+IF(D120="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M120" s="7">
+        <v>6</v>
+      </c>
+      <c r="N120" s="7">
+        <f t="shared" ref="N120" si="25">IF(D120="-",0,LEN(D120)-LEN(SUBSTITUTE(D120,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O120" s="7">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P120" s="7">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="Q120" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="R120" s="19" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A121" s="7">
+        <v>148</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" t="s">
+        <v>664</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I121" s="7">
+        <f>VLOOKUP(H121,cardsort_group_IDs!A:B,2,0)</f>
+        <v>201</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K121" s="7">
+        <f>VLOOKUP(J121,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>302</v>
+      </c>
+      <c r="L121" s="7">
+        <f t="shared" ref="L121:L122" si="26">IF(E121="-",0,1)+IF(D121="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M121" s="7">
+        <v>7</v>
+      </c>
+      <c r="N121" s="7">
+        <f t="shared" ref="N121:N122" si="27">IF(D121="-",0,LEN(D121)-LEN(SUBSTITUTE(D121,";",""))+1)</f>
+        <v>10</v>
+      </c>
+      <c r="O121" s="7">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P121" s="7">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="Q121" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R121" s="19" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A122" s="7">
+        <v>149</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="E122" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I122" s="7">
+        <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
+        <v>202</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K122" s="7">
+        <f>VLOOKUP(J122,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>304</v>
+      </c>
+      <c r="L122" s="7">
+        <f t="shared" ref="L122:L123" si="28">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M122" s="7">
+        <v>8</v>
+      </c>
+      <c r="N122" s="7">
+        <f t="shared" ref="N122" si="29">IF(D122="-",0,LEN(D122)-LEN(SUBSTITUTE(D122,";",""))+1)</f>
+        <v>2</v>
+      </c>
+      <c r="O122" s="7">
+        <f t="shared" ref="O122:O123" si="30">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P122" s="7">
+        <f t="shared" ref="P122" si="31">SUM(N122:O122)</f>
+        <v>2</v>
+      </c>
+      <c r="Q122" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R122" s="19" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A123" s="7">
+        <v>150</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>691</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="I123" s="7">
+        <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J123" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K123" s="7">
+        <f>VLOOKUP(J123,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>313</v>
+      </c>
+      <c r="L123" s="7">
+        <f t="shared" ref="L123" si="32">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
+        <v>2</v>
+      </c>
+      <c r="M123" s="7">
+        <v>9</v>
+      </c>
+      <c r="N123" s="7">
+        <f t="shared" ref="N123" si="33">IF(D123="-",0,LEN(D123)-LEN(SUBSTITUTE(D123,";",""))+1)</f>
+        <v>2</v>
+      </c>
+      <c r="O123" s="7">
+        <f t="shared" ref="O123" si="34">IF(E123="-",0,LEN(E123)-LEN(SUBSTITUTE(E123,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P123" s="7">
+        <f t="shared" ref="P123" si="35">SUM(N123:O123)</f>
+        <v>2</v>
+      </c>
+      <c r="Q123" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R123" s="19" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N124" s="7"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N125" s="7"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N126" s="7"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D127"/>
       <c r="N127" s="7"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N128" s="7"/>
     </row>
     <row r="129" spans="14:14" x14ac:dyDescent="0.25">
@@ -9605,6 +10940,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B1:B111">
     <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
@@ -9653,63 +10989,64 @@
   <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112:B1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="37"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J35">
-    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J106">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112:B116 B119:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="17"/>
@@ -9719,13 +11056,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9733,10 +11070,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -9744,10 +11081,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9755,10 +11092,10 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -9766,10 +11103,10 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -9777,10 +11114,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -9788,10 +11125,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -9799,10 +11136,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -9810,10 +11147,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -9821,10 +11158,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -9832,10 +11169,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="C11" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -9843,10 +11180,10 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -9854,10 +11191,10 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -9865,10 +11202,10 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9876,10 +11213,10 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -9887,10 +11224,10 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -9898,10 +11235,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="C17" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -9909,10 +11246,10 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -9920,10 +11257,10 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -9931,10 +11268,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -9942,10 +11279,10 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -9953,10 +11290,10 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -9964,10 +11301,10 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -9975,10 +11312,10 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9986,10 +11323,10 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9997,10 +11334,10 @@
         <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -10008,10 +11345,10 @@
         <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -10019,10 +11356,10 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -10030,10 +11367,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -10041,10 +11378,10 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -10052,10 +11389,10 @@
         <v>96</v>
       </c>
       <c r="B31" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -10063,10 +11400,10 @@
         <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -10074,10 +11411,10 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -10085,10 +11422,10 @@
         <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -10096,10 +11433,10 @@
         <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -10107,10 +11444,10 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -10118,10 +11455,10 @@
         <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -10129,10 +11466,10 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -10140,10 +11477,10 @@
         <v>160</v>
       </c>
       <c r="B39" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -10154,7 +11491,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -10162,10 +11499,10 @@
         <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -10173,10 +11510,10 @@
         <v>183</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -10184,10 +11521,10 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -10195,10 +11532,10 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -10209,7 +11546,7 @@
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -10217,10 +11554,10 @@
         <v>202</v>
       </c>
       <c r="B46" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -10228,10 +11565,10 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C47" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -10239,10 +11576,10 @@
         <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -10250,10 +11587,10 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -10261,10 +11598,10 @@
         <v>232</v>
       </c>
       <c r="B50" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -10272,10 +11609,10 @@
         <v>233</v>
       </c>
       <c r="B51" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -10283,10 +11620,10 @@
         <v>234</v>
       </c>
       <c r="B52" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -10294,10 +11631,10 @@
         <v>235</v>
       </c>
       <c r="B53" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -10305,10 +11642,10 @@
         <v>236</v>
       </c>
       <c r="B54" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -10316,10 +11653,10 @@
         <v>237</v>
       </c>
       <c r="B55" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -10327,10 +11664,10 @@
         <v>238</v>
       </c>
       <c r="B56" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -10338,10 +11675,10 @@
         <v>240</v>
       </c>
       <c r="B57" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -10349,10 +11686,10 @@
         <v>241</v>
       </c>
       <c r="B58" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -10360,10 +11697,10 @@
         <v>243</v>
       </c>
       <c r="B59" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -10371,10 +11708,10 @@
         <v>244</v>
       </c>
       <c r="B60" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -10382,10 +11719,10 @@
         <v>501</v>
       </c>
       <c r="B61" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -10393,10 +11730,10 @@
         <v>502</v>
       </c>
       <c r="B62" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -10404,10 +11741,10 @@
         <v>503</v>
       </c>
       <c r="B63" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -10415,10 +11752,10 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -10426,10 +11763,10 @@
         <v>505</v>
       </c>
       <c r="B65" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -10437,10 +11774,10 @@
         <v>506</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -10448,10 +11785,10 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -10459,10 +11796,10 @@
         <v>508</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -10470,10 +11807,10 @@
         <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -10481,681 +11818,703 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="C70" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="B76" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B77" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B81" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B82" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="B83" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B84" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="B85" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B89" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="B90" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B92" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B93" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="B94" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="B95" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="B96" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B98" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B99" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="B101" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="B102" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B103" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B104" t="s">
         <v>21</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B105" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B106" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B107" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B108" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B109" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B110" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B111" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B112" t="s">
         <v>41</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="B113" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="B114" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="B115" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="C115" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="B116" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C116" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="B117" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C117" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="B118" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C118" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="B119" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="C119" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="B120" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C120" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="B121" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="C121" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="B122" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="C122" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="B123" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="C123" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="B124" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="C124" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="B125" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="C125" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="B126" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="C126" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="B127" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="C127" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="B128" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="C128" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="B129" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="C129" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="B130" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="C130" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="B131" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="C131" t="s">
-        <v>618</v>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="B132" t="s">
+        <v>659</v>
+      </c>
+      <c r="C132" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="B133" t="s">
+        <v>630</v>
+      </c>
+      <c r="C133" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -11194,7 +12553,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -11226,7 +12585,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>207</v>
@@ -11234,7 +12593,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>208</v>
@@ -11279,7 +12638,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -11343,7 +12702,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>312</v>
@@ -11351,7 +12710,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>313</v>
@@ -11359,7 +12718,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14">
         <v>314</v>
@@ -11367,7 +12726,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15">
         <v>316</v>
@@ -11383,7 +12742,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17">
         <v>318</v>
@@ -11391,7 +12750,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18">
         <v>319</v>
@@ -11399,7 +12758,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19">
         <v>320</v>
@@ -11407,7 +12766,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B20">
         <v>321</v>
@@ -11415,7 +12774,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21">
         <v>322</v>
@@ -11423,7 +12782,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B22">
         <v>323</v>
@@ -11431,7 +12790,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B23">
         <v>324</v>
@@ -11439,7 +12798,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B24">
         <v>325</v>
@@ -11447,7 +12806,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B25">
         <v>326</v>
@@ -11463,7 +12822,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -11471,7 +12830,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -11479,7 +12838,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -11487,7 +12846,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -11495,7 +12854,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B31">
         <v>332</v>

--- a/metrics and parser/final_list_of_metrics.xlsx
+++ b/metrics and parser/final_list_of_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A1A81E-47E2-4560-8676-506DC6028078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C6841A-BFC1-4029-87B2-EA96336792B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="38115" windowHeight="23385" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="705">
   <si>
     <t>id</t>
   </si>
@@ -1072,9 +1072,6 @@
     <t>SPACE Framework</t>
   </si>
   <si>
-    <t>chime</t>
-  </si>
-  <si>
     <t>Av. Weekly Focus Time per Engineer; Avg. Number of Days with Sufficient Focus Time; Focus Time and Interruption Metrics; Uninterrupted Focus Time</t>
   </si>
   <si>
@@ -1663,9 +1660,6 @@
     <t>509; 9</t>
   </si>
   <si>
-    <t>509; 501</t>
-  </si>
-  <si>
     <t>504; 214</t>
   </si>
   <si>
@@ -1891,9 +1885,6 @@
     <t xml:space="preserve">5; 501; 115; 183; </t>
   </si>
   <si>
-    <t>503; 9; 17; 5; 115; 501; 115; 183; 182</t>
-  </si>
-  <si>
     <t>202a; 131i; 131g</t>
   </si>
   <si>
@@ -1906,9 +1897,6 @@
     <t>160; 501; 146</t>
   </si>
   <si>
-    <t>509; 505; 506; 508; 9; 160; 501; 131; 202; 183; 146</t>
-  </si>
-  <si>
     <t>170; 146b; 131l</t>
   </si>
   <si>
@@ -1921,9 +1909,6 @@
     <t>50; 234; 131; 146</t>
   </si>
   <si>
-    <t>509; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146</t>
-  </si>
-  <si>
     <t>501; 146</t>
   </si>
   <si>
@@ -1948,9 +1933,6 @@
     <t>50; 183</t>
   </si>
   <si>
-    <t>9; 36; 52; 62; 240; 243; 244; 160; 501; 183</t>
-  </si>
-  <si>
     <t>501; 183</t>
   </si>
   <si>
@@ -2203,9 +2185,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>% capacity worked per AI tool</t>
-  </si>
-  <si>
     <t>511b; 511c; 511e; 511h; 511i</t>
   </si>
   <si>
@@ -2239,9 +2218,6 @@
     <t>Estimated time savings from using AI</t>
   </si>
   <si>
-    <t>511a; 511c; 511d; 411f; 511g; 511k; 511l; 511n; 511q; 511p</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
@@ -2308,9 +2284,6 @@
     <t>131s; 131t; 32a; 511b</t>
   </si>
   <si>
-    <t>AI change/Trust confidence</t>
-  </si>
-  <si>
     <t>511a; 511b</t>
   </si>
   <si>
@@ -2342,6 +2315,51 @@
   </si>
   <si>
     <t>232a; 511i</t>
+  </si>
+  <si>
+    <t>511a; 511c; 511d; 511f; 511g; 511k; 511l; 511n; 511q; 511p</t>
+  </si>
+  <si>
+    <t>https://getdx.com/uploads/ai-measurement-framework.pdf</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>Chime</t>
+  </si>
+  <si>
+    <t>Tasks assigned to AI agents</t>
+  </si>
+  <si>
+    <t>Number of tasks that developers assign to their AI agents.</t>
+  </si>
+  <si>
+    <t>509; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512</t>
+  </si>
+  <si>
+    <t>9; 36; 52; 62; 240; 243; 244; 160; 501; 183; 512</t>
+  </si>
+  <si>
+    <t>509; 501; 512</t>
+  </si>
+  <si>
+    <t>503; 9; 17; 5; 115; 501; 115; 183; 182; 512</t>
+  </si>
+  <si>
+    <t>AI change/trust confidence</t>
+  </si>
+  <si>
+    <t>509; 505; 506; 508; 9; 160; 501; 131; 202; 183; 146; 512</t>
+  </si>
+  <si>
+    <t>% capacity worked per AI tool; Agent hourly rate</t>
+  </si>
+  <si>
+    <t>Net time gain per developer</t>
+  </si>
+  <si>
+    <t>Human-equivalent hours of work completed by agents</t>
   </si>
 </sst>
 </file>
@@ -3304,19 +3322,19 @@
         <v>10</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="R1" s="22" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
@@ -3330,16 +3348,16 @@
         <v>15</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
@@ -3375,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R2" s="19" t="s">
         <v>11</v>
@@ -3401,7 +3419,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>23</v>
@@ -3437,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R3" s="19" t="s">
         <v>11</v>
@@ -3451,22 +3469,22 @@
         <v>25</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3499,7 +3517,7 @@
         <v>8</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R4" s="19" t="s">
         <v>11</v>
@@ -3516,16 +3534,16 @@
         <v>11</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
@@ -3561,7 +3579,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R5" s="19" t="s">
         <v>11</v>
@@ -3575,22 +3593,22 @@
         <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3623,7 +3641,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R6" s="19" t="s">
         <v>11</v>
@@ -3649,7 +3667,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>12</v>
@@ -3685,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R7" s="19" t="s">
         <v>11</v>
@@ -3702,16 +3720,16 @@
         <v>11</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>553</v>
+        <v>701</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>38</v>
@@ -3740,11 +3758,11 @@
       </c>
       <c r="O8" s="7">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="19" t="s">
         <v>136</v>
@@ -3773,7 +3791,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>38</v>
@@ -3809,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R9" s="19" t="s">
         <v>11</v>
@@ -3826,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E10" s="20">
         <v>501</v>
@@ -3835,7 +3853,7 @@
         <v>45</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>38</v>
@@ -3871,7 +3889,7 @@
         <v>2</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R10" s="19" t="s">
         <v>11</v>
@@ -3888,7 +3906,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E11" s="20">
         <v>501</v>
@@ -3897,7 +3915,7 @@
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
@@ -3933,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R11" s="19" t="s">
         <v>11</v>
@@ -3950,16 +3968,16 @@
         <v>11</v>
       </c>
       <c r="D12" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>454</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>455</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>38</v>
@@ -3995,7 +4013,7 @@
         <v>6</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R12" s="19" t="s">
         <v>11</v>
@@ -4012,16 +4030,16 @@
         <v>52</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>54</v>
@@ -4057,7 +4075,7 @@
         <v>8</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R13" s="19" t="s">
         <v>11</v>
@@ -4071,10 +4089,10 @@
         <v>55</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="E14" s="20">
         <v>131</v>
@@ -4083,7 +4101,7 @@
         <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>38</v>
@@ -4133,19 +4151,19 @@
         <v>57</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>59</v>
@@ -4181,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R15" s="19" t="s">
         <v>11</v>
@@ -4195,22 +4213,22 @@
         <v>61</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
@@ -4243,7 +4261,7 @@
         <v>4</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R16" s="19" t="s">
         <v>11</v>
@@ -4260,16 +4278,16 @@
         <v>11</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>66</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
@@ -4305,7 +4323,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R17" s="19" t="s">
         <v>11</v>
@@ -4319,19 +4337,19 @@
         <v>67</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>54</v>
@@ -4367,7 +4385,7 @@
         <v>2</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R18" s="19" t="s">
         <v>11</v>
@@ -4393,7 +4411,7 @@
         <v>73</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
@@ -4429,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R19" s="19" t="s">
         <v>11</v>
@@ -4449,13 +4467,13 @@
         <v>11</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>77</v>
@@ -4491,7 +4509,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R20" s="19" t="s">
         <v>11</v>
@@ -4508,7 +4526,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E21" s="20">
         <v>131</v>
@@ -4517,7 +4535,7 @@
         <v>79</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>77</v>
@@ -4553,7 +4571,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R21" s="19" t="s">
         <v>11</v>
@@ -4567,19 +4585,19 @@
         <v>30</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>80</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
@@ -4632,7 +4650,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E23" s="20">
         <v>501</v>
@@ -4641,10 +4659,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4677,7 +4695,7 @@
         <v>2</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R23" s="19" t="s">
         <v>11</v>
@@ -4691,7 +4709,7 @@
         <v>84</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>11</v>
@@ -4703,7 +4721,7 @@
         <v>85</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>38</v>
@@ -4739,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="Q24" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R24" s="19" t="s">
         <v>11</v>
@@ -4756,16 +4774,16 @@
         <v>11</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>77</v>
@@ -4815,19 +4833,19 @@
         <v>88</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D26" s="19">
         <v>170</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>38</v>
@@ -4863,7 +4881,7 @@
         <v>4</v>
       </c>
       <c r="Q26" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R26" s="19" t="s">
         <v>11</v>
@@ -4880,7 +4898,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E27" s="20">
         <v>501</v>
@@ -4889,7 +4907,7 @@
         <v>93</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>77</v>
@@ -4925,7 +4943,7 @@
         <v>2</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R27" s="19" t="s">
         <v>11</v>
@@ -4942,16 +4960,16 @@
         <v>11</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>95</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
@@ -4987,7 +5005,7 @@
         <v>3</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R28" s="19" t="s">
         <v>11</v>
@@ -5001,19 +5019,19 @@
         <v>97</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>98</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>23</v>
@@ -5049,7 +5067,7 @@
         <v>8</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R29" s="19" t="s">
         <v>11</v>
@@ -5066,19 +5084,19 @@
         <v>11</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>100</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I30" s="7">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
@@ -5111,7 +5129,7 @@
         <v>3</v>
       </c>
       <c r="Q30" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R30" s="19" t="s">
         <v>11</v>
@@ -5125,22 +5143,22 @@
         <v>102</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>558</v>
+        <v>696</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>103</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I31" s="7">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
@@ -5166,11 +5184,11 @@
       </c>
       <c r="O31" s="7">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P31" s="7">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q31" s="19" t="s">
         <v>136</v>
@@ -5199,7 +5217,7 @@
         <v>106</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>12</v>
@@ -5235,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R32" s="19" t="s">
         <v>11</v>
@@ -5249,19 +5267,19 @@
         <v>107</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>108</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>17</v>
@@ -5314,16 +5332,16 @@
         <v>11</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>110</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
@@ -5359,7 +5377,7 @@
         <v>3</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R34" s="19" t="s">
         <v>11</v>
@@ -5376,19 +5394,19 @@
         <v>111</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>112</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I35" s="7">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5435,22 +5453,22 @@
         <v>113</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>114</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I36" s="7">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5483,7 +5501,7 @@
         <v>6</v>
       </c>
       <c r="Q36" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R36" s="19" t="s">
         <v>11</v>
@@ -5497,19 +5515,19 @@
         <v>115</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>116</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>38</v>
@@ -5545,7 +5563,7 @@
         <v>2</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R37" s="19" t="s">
         <v>11</v>
@@ -5562,19 +5580,19 @@
         <v>11</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I38" s="7">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
@@ -5607,7 +5625,7 @@
         <v>3</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R38" s="19" t="s">
         <v>11</v>
@@ -5621,19 +5639,19 @@
         <v>120</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>122</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>23</v>
@@ -5689,13 +5707,13 @@
         <v>11</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>23</v>
@@ -5731,7 +5749,7 @@
         <v>2</v>
       </c>
       <c r="Q40" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R40" s="19" t="s">
         <v>11</v>
@@ -5751,13 +5769,13 @@
         <v>11</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>128</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>54</v>
@@ -5813,16 +5831,16 @@
         <v>11</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>131</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I42" s="7">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5855,7 +5873,7 @@
         <v>2</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R42" s="19" t="s">
         <v>11</v>
@@ -5881,7 +5899,7 @@
         <v>133</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>17</v>
@@ -5917,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="Q43" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R43" s="19" t="s">
         <v>11</v>
@@ -5943,7 +5961,7 @@
         <v>135</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
@@ -5979,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="Q44" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R44" s="19" t="s">
         <v>11</v>
@@ -5993,22 +6011,22 @@
         <v>136</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>137</v>
       </c>
       <c r="G45" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I45" s="7">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6041,7 +6059,7 @@
         <v>4</v>
       </c>
       <c r="Q45" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R45" s="19" t="s">
         <v>11</v>
@@ -6067,7 +6085,7 @@
         <v>140</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>12</v>
@@ -6103,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="Q46" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R46" s="19" t="s">
         <v>11</v>
@@ -6117,22 +6135,22 @@
         <v>141</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>142</v>
       </c>
       <c r="G47" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I47" s="7">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
@@ -6179,22 +6197,22 @@
         <v>143</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>447</v>
+        <v>11</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>144</v>
       </c>
       <c r="G48" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I48" s="7">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -6209,14 +6227,14 @@
       </c>
       <c r="L48" s="7">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M48" s="7">
         <v>1</v>
       </c>
       <c r="N48" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="7">
         <f t="shared" si="1"/>
@@ -6224,7 +6242,7 @@
       </c>
       <c r="P48" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q48" s="19" t="s">
         <v>136</v>
@@ -6244,16 +6262,16 @@
         <v>147</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>148</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>17</v>
@@ -6289,7 +6307,7 @@
         <v>11</v>
       </c>
       <c r="Q49" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R49" s="19" t="s">
         <v>11</v>
@@ -6303,19 +6321,19 @@
         <v>149</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>151</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>38</v>
@@ -6377,7 +6395,7 @@
         <v>153</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>23</v>
@@ -6413,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="Q51" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R51" s="19" t="s">
         <v>11</v>
@@ -6427,19 +6445,19 @@
         <v>154</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>155</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>23</v>
@@ -6475,7 +6493,7 @@
         <v>16</v>
       </c>
       <c r="Q52" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R52" s="19" t="s">
         <v>11</v>
@@ -6489,7 +6507,7 @@
         <v>156</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>11</v>
@@ -6501,7 +6519,7 @@
         <v>157</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>54</v>
@@ -6537,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="Q53" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R53" s="19" t="s">
         <v>11</v>
@@ -6554,16 +6572,16 @@
         <v>11</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>159</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>54</v>
@@ -6599,7 +6617,7 @@
         <v>3</v>
       </c>
       <c r="Q54" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R54" s="19" t="s">
         <v>11</v>
@@ -6613,19 +6631,19 @@
         <v>160</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>161</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>77</v>
@@ -6661,7 +6679,7 @@
         <v>3</v>
       </c>
       <c r="Q55" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R55" s="19" t="s">
         <v>11</v>
@@ -6675,19 +6693,19 @@
         <v>162</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="20" t="s">
         <v>292</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>293</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>163</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>38</v>
@@ -6723,7 +6741,7 @@
         <v>2</v>
       </c>
       <c r="Q56" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R56" s="19" t="s">
         <v>11</v>
@@ -6740,16 +6758,16 @@
         <v>11</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>165</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>17</v>
@@ -6785,7 +6803,7 @@
         <v>3</v>
       </c>
       <c r="Q57" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R57" s="19" t="s">
         <v>11</v>
@@ -6802,16 +6820,16 @@
         <v>11</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>167</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>12</v>
@@ -6847,7 +6865,7 @@
         <v>3</v>
       </c>
       <c r="Q58" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R58" s="19" t="s">
         <v>11</v>
@@ -6864,16 +6882,16 @@
         <v>11</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>170</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>23</v>
@@ -6909,7 +6927,7 @@
         <v>3</v>
       </c>
       <c r="Q59" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R59" s="19" t="s">
         <v>11</v>
@@ -6935,7 +6953,7 @@
         <v>173</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>12</v>
@@ -6971,7 +6989,7 @@
         <v>1</v>
       </c>
       <c r="Q60" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R60" s="19" t="s">
         <v>11</v>
@@ -6988,7 +7006,7 @@
         <v>11</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E61" s="20">
         <v>183</v>
@@ -6997,7 +7015,7 @@
         <v>175</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>38</v>
@@ -7033,7 +7051,7 @@
         <v>2</v>
       </c>
       <c r="Q61" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R61" s="19" t="s">
         <v>11</v>
@@ -7047,19 +7065,19 @@
         <v>176</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>177</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -7095,7 +7113,7 @@
         <v>2</v>
       </c>
       <c r="Q62" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R62" s="19" t="s">
         <v>11</v>
@@ -7112,19 +7130,19 @@
         <v>11</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>179</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I63" s="7">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -7157,7 +7175,7 @@
         <v>3</v>
       </c>
       <c r="Q63" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R63" s="19" t="s">
         <v>11</v>
@@ -7174,19 +7192,19 @@
         <v>181</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I64" s="7">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
@@ -7236,16 +7254,16 @@
         <v>11</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>472</v>
+        <v>698</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>77</v>
@@ -7274,14 +7292,14 @@
       </c>
       <c r="O65" s="7">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P65" s="7">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q65" s="19" t="s">
-        <v>639</v>
+        <v>136</v>
       </c>
       <c r="R65" s="19" t="s">
         <v>11</v>
@@ -7307,7 +7325,7 @@
         <v>186</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>77</v>
@@ -7343,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="Q66" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R66" s="19" t="s">
         <v>11</v>
@@ -7360,7 +7378,7 @@
         <v>11</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E67" s="20">
         <v>202</v>
@@ -7369,7 +7387,7 @@
         <v>188</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>38</v>
@@ -7405,7 +7423,7 @@
         <v>2</v>
       </c>
       <c r="Q67" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R67" s="19" t="s">
         <v>11</v>
@@ -7431,7 +7449,7 @@
         <v>190</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>12</v>
@@ -7467,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R68" s="19" t="s">
         <v>11</v>
@@ -7481,22 +7499,22 @@
         <v>191</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G69" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H69" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I69" s="7">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
@@ -7546,7 +7564,7 @@
         <v>11</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E70" s="20">
         <v>501</v>
@@ -7555,7 +7573,7 @@
         <v>193</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>23</v>
@@ -7591,7 +7609,7 @@
         <v>2</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R70" s="19" t="s">
         <v>11</v>
@@ -7608,7 +7626,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E71" s="20" t="s">
         <v>11</v>
@@ -7617,7 +7635,7 @@
         <v>195</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>17</v>
@@ -7653,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R71" s="19" t="s">
         <v>11</v>
@@ -7670,16 +7688,16 @@
         <v>11</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>197</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>17</v>
@@ -7715,7 +7733,7 @@
         <v>3</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R72" s="19" t="s">
         <v>11</v>
@@ -7729,19 +7747,19 @@
         <v>198</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>199</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>38</v>
@@ -7777,7 +7795,7 @@
         <v>3</v>
       </c>
       <c r="Q73" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R73" s="19" t="s">
         <v>11</v>
@@ -7794,16 +7812,16 @@
         <v>11</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>201</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>38</v>
@@ -7839,7 +7857,7 @@
         <v>4</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R74" s="19" t="s">
         <v>11</v>
@@ -7853,19 +7871,19 @@
         <v>202</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>203</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>38</v>
@@ -7894,11 +7912,11 @@
       </c>
       <c r="O75" s="7">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P75" s="7">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q75" s="19" t="s">
         <v>136</v>
@@ -7915,19 +7933,19 @@
         <v>204</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>205</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>17</v>
@@ -7963,7 +7981,7 @@
         <v>4</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R76" s="19" t="s">
         <v>11</v>
@@ -7980,16 +7998,16 @@
         <v>11</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>207</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>54</v>
@@ -8025,7 +8043,7 @@
         <v>3</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R77" s="19" t="s">
         <v>11</v>
@@ -8051,7 +8069,7 @@
         <v>209</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>12</v>
@@ -8087,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R78" s="19" t="s">
         <v>11</v>
@@ -8101,19 +8119,19 @@
         <v>210</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>211</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>77</v>
@@ -8149,7 +8167,7 @@
         <v>4</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R79" s="19" t="s">
         <v>11</v>
@@ -8166,16 +8184,16 @@
         <v>213</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>214</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>23</v>
@@ -8211,7 +8229,7 @@
         <v>3</v>
       </c>
       <c r="Q80" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R80" s="19" t="s">
         <v>11</v>
@@ -8237,7 +8255,7 @@
         <v>216</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>23</v>
@@ -8273,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R81" s="19" t="s">
         <v>11</v>
@@ -8287,7 +8305,7 @@
         <v>217</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D82" s="17">
         <v>209</v>
@@ -8299,7 +8317,7 @@
         <v>218</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>12</v>
@@ -8335,7 +8353,7 @@
         <v>2</v>
       </c>
       <c r="Q82" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R82" s="19" t="s">
         <v>11</v>
@@ -8361,7 +8379,7 @@
         <v>220</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>12</v>
@@ -8397,7 +8415,7 @@
         <v>1</v>
       </c>
       <c r="Q83" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R83" s="19" t="s">
         <v>11</v>
@@ -8423,7 +8441,7 @@
         <v>222</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>12</v>
@@ -8459,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="Q84" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R84" s="19" t="s">
         <v>11</v>
@@ -8476,7 +8494,7 @@
         <v>11</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E85" s="20">
         <v>501</v>
@@ -8485,7 +8503,7 @@
         <v>225</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>17</v>
@@ -8521,7 +8539,7 @@
         <v>2</v>
       </c>
       <c r="Q85" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R85" s="19" t="s">
         <v>11</v>
@@ -8538,7 +8556,7 @@
         <v>227</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E86" s="20" t="s">
         <v>11</v>
@@ -8547,10 +8565,10 @@
         <v>228</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I86" s="7">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
@@ -8583,7 +8601,7 @@
         <v>2</v>
       </c>
       <c r="Q86" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R86" s="19" t="s">
         <v>11</v>
@@ -8597,19 +8615,19 @@
         <v>229</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>230</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>23</v>
@@ -8645,7 +8663,7 @@
         <v>4</v>
       </c>
       <c r="Q87" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R87" s="19" t="s">
         <v>11</v>
@@ -8662,16 +8680,16 @@
         <v>11</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>17</v>
@@ -8707,7 +8725,7 @@
         <v>7</v>
       </c>
       <c r="Q88" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R88" s="19" t="s">
         <v>11</v>
@@ -8721,19 +8739,19 @@
         <v>233</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>234</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>17</v>
@@ -8769,7 +8787,7 @@
         <v>8</v>
       </c>
       <c r="Q89" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R89" s="19" t="s">
         <v>11</v>
@@ -8783,19 +8801,19 @@
         <v>235</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D90" s="20" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>236</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>23</v>
@@ -8831,7 +8849,7 @@
         <v>8</v>
       </c>
       <c r="Q90" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R90" s="19" t="s">
         <v>11</v>
@@ -8857,10 +8875,10 @@
         <v>238</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I91" s="7">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
@@ -8893,7 +8911,7 @@
         <v>1</v>
       </c>
       <c r="Q91" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R91" s="19" t="s">
         <v>11</v>
@@ -8907,19 +8925,19 @@
         <v>240</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>241</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>59</v>
@@ -8955,7 +8973,7 @@
         <v>13</v>
       </c>
       <c r="Q92" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R92" s="19" t="s">
         <v>11</v>
@@ -8981,7 +8999,7 @@
         <v>243</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>54</v>
@@ -9017,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="Q93" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R93" s="19" t="s">
         <v>11</v>
@@ -9031,19 +9049,19 @@
         <v>244</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>245</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>38</v>
@@ -9079,7 +9097,7 @@
         <v>4</v>
       </c>
       <c r="Q94" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R94" s="19" t="s">
         <v>11</v>
@@ -9093,19 +9111,19 @@
         <v>43</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>247</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>38</v>
@@ -9167,7 +9185,7 @@
         <v>249</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>23</v>
@@ -9203,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R96" s="19" t="s">
         <v>11</v>
@@ -9220,7 +9238,7 @@
         <v>11</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E97" s="20">
         <v>501</v>
@@ -9229,7 +9247,7 @@
         <v>252</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>17</v>
@@ -9265,7 +9283,7 @@
         <v>2</v>
       </c>
       <c r="Q97" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R97" s="19" t="s">
         <v>11</v>
@@ -9282,16 +9300,16 @@
         <v>11</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F98" s="10" t="s">
         <v>254</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>17</v>
@@ -9327,7 +9345,7 @@
         <v>3</v>
       </c>
       <c r="Q98" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R98" s="19" t="s">
         <v>11</v>
@@ -9341,19 +9359,19 @@
         <v>255</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>256</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>17</v>
@@ -9403,19 +9421,19 @@
         <v>257</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>258</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>17</v>
@@ -9468,19 +9486,19 @@
         <v>260</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>261</v>
       </c>
       <c r="G101" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H101" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I101" s="7">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
@@ -9513,7 +9531,7 @@
         <v>7</v>
       </c>
       <c r="Q101" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R101" s="19" t="s">
         <v>11</v>
@@ -9530,7 +9548,7 @@
         <v>11</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E102" s="20">
         <v>501</v>
@@ -9539,7 +9557,7 @@
         <v>264</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>59</v>
@@ -9575,7 +9593,7 @@
         <v>2</v>
       </c>
       <c r="Q102" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R102" s="19" t="s">
         <v>11</v>
@@ -9589,19 +9607,19 @@
         <v>265</v>
       </c>
       <c r="C103" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="E103" s="20" t="s">
         <v>301</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="E103" s="20" t="s">
-        <v>302</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>267</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>59</v>
@@ -9637,7 +9655,7 @@
         <v>3</v>
       </c>
       <c r="Q103" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R103" s="19" t="s">
         <v>11</v>
@@ -9654,7 +9672,7 @@
         <v>11</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E104" s="20">
         <v>501</v>
@@ -9663,7 +9681,7 @@
         <v>269</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>59</v>
@@ -9699,7 +9717,7 @@
         <v>2</v>
       </c>
       <c r="Q104" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R104" s="19" t="s">
         <v>11</v>
@@ -9710,22 +9728,22 @@
         <v>129</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>567</v>
+        <v>697</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>59</v>
@@ -9754,11 +9772,11 @@
       </c>
       <c r="O105" s="7">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P105" s="7">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q105" s="19" t="s">
         <v>136</v>
@@ -9778,19 +9796,19 @@
         <v>11</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>271</v>
       </c>
       <c r="G106" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H106" s="7" t="s">
         <v>535</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="I106" s="7">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
@@ -9823,7 +9841,7 @@
         <v>5</v>
       </c>
       <c r="Q106" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R106" s="19" t="s">
         <v>11</v>
@@ -9834,22 +9852,22 @@
         <v>134</v>
       </c>
       <c r="B107" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>305</v>
-      </c>
       <c r="D107" s="17" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G107" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H107" t="s">
         <v>38</v>
@@ -9896,7 +9914,7 @@
         <v>135</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>11</v>
@@ -9908,13 +9926,13 @@
         <v>183</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G108" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H108" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I108" s="7">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
@@ -9947,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R108" s="19" t="s">
         <v>11</v>
@@ -9958,7 +9976,7 @@
         <v>136</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>11</v>
@@ -9970,10 +9988,10 @@
         <v>240</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G109" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H109" t="s">
         <v>59</v>
@@ -10009,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="Q109" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R109" s="19" t="s">
         <v>11</v>
@@ -10020,25 +10038,25 @@
         <v>137</v>
       </c>
       <c r="B110" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="D110" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="D110" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="21" t="s">
-        <v>309</v>
-      </c>
       <c r="F110" s="8" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G110" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H110" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I110" s="7">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
@@ -10071,7 +10089,7 @@
         <v>6</v>
       </c>
       <c r="Q110" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R110" s="19" t="s">
         <v>11</v>
@@ -10082,10 +10100,10 @@
         <v>138</v>
       </c>
       <c r="B111" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>310</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>311</v>
       </c>
       <c r="D111" s="19" t="s">
         <v>11</v>
@@ -10094,10 +10112,10 @@
         <v>236</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G111" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -10133,7 +10151,7 @@
         <v>1</v>
       </c>
       <c r="Q111" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R111" s="19" t="s">
         <v>11</v>
@@ -10144,7 +10162,7 @@
         <v>139</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>11</v>
@@ -10156,10 +10174,10 @@
         <v>11</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>23</v>
@@ -10195,7 +10213,7 @@
         <v>1</v>
       </c>
       <c r="Q112" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="R112" s="19" t="s">
         <v>11</v>
@@ -10206,22 +10224,22 @@
         <v>140</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>11</v>
+        <v>692</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>17</v>
@@ -10239,7 +10257,7 @@
       </c>
       <c r="L113" s="7">
         <f>IF(E113="-",0,1)+IF(D113="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M113" s="7">
         <v>0</v>
@@ -10250,14 +10268,14 @@
       </c>
       <c r="O113" s="7">
         <f>IF(E113="-",0,LEN(E113)-LEN(SUBSTITUTE(E113,";",""))+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P113" s="7">
         <f>SUM(N113:O113)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q113" s="19" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="R113" s="19">
         <v>2</v>
@@ -10268,22 +10286,22 @@
         <v>141</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>11</v>
+        <v>692</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>59</v>
@@ -10301,7 +10319,7 @@
       </c>
       <c r="L114" s="7">
         <f>IF(E114="-",0,1)+IF(D114="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M114" s="7">
         <v>0</v>
@@ -10312,14 +10330,14 @@
       </c>
       <c r="O114" s="7">
         <f>IF(E114="-",0,LEN(E114)-LEN(SUBSTITUTE(E114,";",""))+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P114" s="7">
         <f>SUM(N114:O114)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q114" s="19" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="R114" s="19">
         <v>129</v>
@@ -10330,22 +10348,22 @@
         <v>142</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>11</v>
+        <v>692</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>59</v>
@@ -10363,7 +10381,7 @@
       </c>
       <c r="L115" s="7">
         <f>IF(E115="-",0,1)+IF(D115="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M115" s="7">
         <v>1</v>
@@ -10374,14 +10392,14 @@
       </c>
       <c r="O115" s="7">
         <f>IF(E115="-",0,LEN(E115)-LEN(SUBSTITUTE(E115,";",""))+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P115" s="7">
         <f>SUM(N115:O115)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q115" s="19" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="R115" s="19">
         <v>19</v>
@@ -10392,22 +10410,22 @@
         <v>143</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="E116" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>59</v>
@@ -10443,7 +10461,7 @@
         <v>5</v>
       </c>
       <c r="Q116" s="19" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="R116" s="19" t="s">
         <v>11</v>
@@ -10454,22 +10472,22 @@
         <v>144</v>
       </c>
       <c r="B117" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E117" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>17</v>
@@ -10505,10 +10523,10 @@
         <v>1</v>
       </c>
       <c r="Q117" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R117" s="19" t="s">
         <v>645</v>
-      </c>
-      <c r="R117" s="19" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
@@ -10516,22 +10534,22 @@
         <v>145</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E118" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H118" t="s">
         <v>12</v>
@@ -10567,33 +10585,33 @@
         <v>1</v>
       </c>
       <c r="Q118" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="R118" s="19" t="s">
         <v>645</v>
       </c>
-      <c r="R118" s="19" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>146</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>652</v>
+        <v>702</v>
       </c>
       <c r="D119" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>11</v>
+        <v>692</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -10611,7 +10629,7 @@
       </c>
       <c r="L119" s="7">
         <f t="shared" ref="L119" si="20">IF(E119="-",0,1)+IF(D119="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M119" s="7">
         <v>5</v>
@@ -10622,17 +10640,17 @@
       </c>
       <c r="O119" s="7">
         <f t="shared" ref="O119:O122" si="22">IF(E119="-",0,LEN(E119)-LEN(SUBSTITUTE(E119,";",""))+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" s="7">
         <f t="shared" ref="P119:P122" si="23">SUM(N119:O119)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q119" s="19" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="R119" s="19" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
@@ -10640,22 +10658,22 @@
         <v>147</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E120" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>17</v>
@@ -10691,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="Q120" s="19" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="R120" s="19" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
@@ -10702,22 +10720,22 @@
         <v>148</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>11</v>
+        <v>703</v>
       </c>
       <c r="D121" t="s">
-        <v>664</v>
+        <v>690</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>11</v>
+        <v>692</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>12</v>
@@ -10735,7 +10753,7 @@
       </c>
       <c r="L121" s="7">
         <f t="shared" ref="L121:L122" si="26">IF(E121="-",0,1)+IF(D121="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M121" s="7">
         <v>7</v>
@@ -10746,17 +10764,17 @@
       </c>
       <c r="O121" s="7">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P121" s="7">
         <f t="shared" si="23"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q121" s="19" t="s">
         <v>136</v>
       </c>
       <c r="R121" s="19" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
@@ -10764,22 +10782,22 @@
         <v>149</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>687</v>
+        <v>700</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>11</v>
+        <v>692</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>23</v>
@@ -10797,7 +10815,7 @@
       </c>
       <c r="L122" s="7">
         <f t="shared" ref="L122:L123" si="28">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M122" s="7">
         <v>8</v>
@@ -10808,17 +10826,17 @@
       </c>
       <c r="O122" s="7">
         <f t="shared" ref="O122:O123" si="30">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P122" s="7">
         <f t="shared" ref="P122" si="31">SUM(N122:O122)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="19" t="s">
         <v>136</v>
       </c>
       <c r="R122" s="19" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
@@ -10826,25 +10844,25 @@
         <v>150</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="E123" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I123" s="7">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -10858,7 +10876,7 @@
         <v>313</v>
       </c>
       <c r="L123" s="7">
-        <f t="shared" ref="L123" si="32">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
+        <f t="shared" ref="L123:L124" si="32">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
         <v>2</v>
       </c>
       <c r="M123" s="7">
@@ -10869,7 +10887,7 @@
         <v>2</v>
       </c>
       <c r="O123" s="7">
-        <f t="shared" ref="O123" si="34">IF(E123="-",0,LEN(E123)-LEN(SUBSTITUTE(E123,";",""))+1)</f>
+        <f t="shared" ref="O123:O124" si="34">IF(E123="-",0,LEN(E123)-LEN(SUBSTITUTE(E123,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="P123" s="7">
@@ -10880,11 +10898,67 @@
         <v>136</v>
       </c>
       <c r="R123" s="19" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N124" s="7"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A124" s="7">
+        <v>151</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" s="7">
+        <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
+        <v>204</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" s="7">
+        <f>VLOOKUP(J124,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>327</v>
+      </c>
+      <c r="L124" s="7">
+        <f t="shared" ref="L124" si="36">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
+        <v>1</v>
+      </c>
+      <c r="M124" s="7">
+        <v>10</v>
+      </c>
+      <c r="N124" s="7">
+        <f t="shared" ref="N124" si="37">IF(D124="-",0,LEN(D124)-LEN(SUBSTITUTE(D124,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="O124" s="7">
+        <f t="shared" ref="O124" si="38">IF(E124="-",0,LEN(E124)-LEN(SUBSTITUTE(E124,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="P124" s="7">
+        <f t="shared" ref="P124" si="39">SUM(N124:O124)</f>
+        <v>1</v>
+      </c>
+      <c r="Q124" s="19" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N125" s="7"/>
@@ -11046,7 +11120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="17"/>
@@ -11056,13 +11130,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" t="s">
         <v>423</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="15" t="s">
         <v>424</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11070,10 +11144,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" t="s">
         <v>317</v>
-      </c>
-      <c r="C2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -11081,10 +11155,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" t="s">
         <v>319</v>
-      </c>
-      <c r="C3" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -11092,10 +11166,10 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" t="s">
         <v>321</v>
-      </c>
-      <c r="C4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -11103,10 +11177,10 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>323</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -11114,10 +11188,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>325</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -11125,10 +11199,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>326</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>327</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -11136,10 +11210,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>329</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -11147,10 +11221,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>331</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -11158,10 +11232,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>333</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -11169,10 +11243,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C11" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -11180,10 +11254,10 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>335</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -11191,10 +11265,10 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>337</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -11202,10 +11276,10 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -11213,10 +11287,10 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>341</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -11224,10 +11298,10 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>343</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -11235,10 +11309,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C17" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -11246,10 +11320,10 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
+        <v>344</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -11257,10 +11331,10 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
+        <v>346</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>347</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -11268,10 +11342,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
+        <v>348</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>349</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -11279,10 +11353,10 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>351</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -11290,10 +11364,10 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
+        <v>352</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -11301,10 +11375,10 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
+        <v>354</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -11312,10 +11386,10 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>357</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -11323,10 +11397,10 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>359</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -11334,10 +11408,10 @@
         <v>57</v>
       </c>
       <c r="B26" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -11345,10 +11419,10 @@
         <v>62</v>
       </c>
       <c r="B27" t="s">
+        <v>362</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -11356,10 +11430,10 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
+        <v>364</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>365</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -11367,10 +11441,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
+        <v>366</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>367</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -11378,10 +11452,10 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -11389,10 +11463,10 @@
         <v>96</v>
       </c>
       <c r="B31" t="s">
+        <v>369</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -11400,10 +11474,10 @@
         <v>101</v>
       </c>
       <c r="B32" t="s">
+        <v>371</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -11411,10 +11485,10 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
+        <v>373</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -11422,10 +11496,10 @@
         <v>108</v>
       </c>
       <c r="B34" t="s">
+        <v>375</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>376</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -11433,10 +11507,10 @@
         <v>111</v>
       </c>
       <c r="B35" t="s">
+        <v>377</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>378</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -11444,10 +11518,10 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>380</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -11455,10 +11529,10 @@
         <v>131</v>
       </c>
       <c r="B37" t="s">
+        <v>382</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>383</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="38" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -11466,10 +11540,10 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
+        <v>384</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>385</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -11477,10 +11551,10 @@
         <v>160</v>
       </c>
       <c r="B39" t="s">
+        <v>386</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>387</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -11491,7 +11565,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -11499,10 +11573,10 @@
         <v>182</v>
       </c>
       <c r="B41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>390</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -11510,10 +11584,10 @@
         <v>183</v>
       </c>
       <c r="B42" t="s">
+        <v>391</v>
+      </c>
+      <c r="C42" s="15" t="s">
         <v>392</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -11521,10 +11595,10 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -11532,10 +11606,10 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -11546,7 +11620,7 @@
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -11554,10 +11628,10 @@
         <v>202</v>
       </c>
       <c r="B46" t="s">
+        <v>396</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>397</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -11565,10 +11639,10 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C47" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -11579,7 +11653,7 @@
         <v>263</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -11587,10 +11661,10 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -11598,10 +11672,10 @@
         <v>232</v>
       </c>
       <c r="B50" t="s">
+        <v>400</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>401</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -11609,10 +11683,10 @@
         <v>233</v>
       </c>
       <c r="B51" t="s">
+        <v>402</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>403</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -11620,10 +11694,10 @@
         <v>234</v>
       </c>
       <c r="B52" t="s">
+        <v>404</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -11631,10 +11705,10 @@
         <v>235</v>
       </c>
       <c r="B53" t="s">
+        <v>406</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>407</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -11642,10 +11716,10 @@
         <v>236</v>
       </c>
       <c r="B54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>409</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -11653,10 +11727,10 @@
         <v>237</v>
       </c>
       <c r="B55" t="s">
+        <v>410</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>411</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -11664,10 +11738,10 @@
         <v>238</v>
       </c>
       <c r="B56" t="s">
+        <v>412</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>413</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -11675,10 +11749,10 @@
         <v>240</v>
       </c>
       <c r="B57" t="s">
+        <v>414</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>415</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -11686,10 +11760,10 @@
         <v>241</v>
       </c>
       <c r="B58" t="s">
+        <v>416</v>
+      </c>
+      <c r="C58" s="15" t="s">
         <v>417</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -11697,10 +11771,10 @@
         <v>243</v>
       </c>
       <c r="B59" t="s">
+        <v>418</v>
+      </c>
+      <c r="C59" s="15" t="s">
         <v>419</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -11708,10 +11782,10 @@
         <v>244</v>
       </c>
       <c r="B60" t="s">
+        <v>420</v>
+      </c>
+      <c r="C60" s="15" t="s">
         <v>421</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -11719,10 +11793,10 @@
         <v>501</v>
       </c>
       <c r="B61" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -11730,10 +11804,10 @@
         <v>502</v>
       </c>
       <c r="B62" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -11744,7 +11818,7 @@
         <v>274</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -11752,10 +11826,10 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -11763,10 +11837,10 @@
         <v>505</v>
       </c>
       <c r="B65" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -11777,7 +11851,7 @@
         <v>68</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -11785,10 +11859,10 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -11799,7 +11873,7 @@
         <v>72</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -11810,7 +11884,7 @@
         <v>139</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -11818,703 +11892,714 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C70" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B72" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B74" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s">
         <v>224</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B76" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B80" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B81" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B82" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B84" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B85" t="s">
         <v>266</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B86" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B89" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B90" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B91" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B92" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B93" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B94" t="s">
         <v>150</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B95" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B96" t="s">
         <v>266</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B97" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B98" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B99" t="s">
         <v>82</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B100" t="s">
         <v>92</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B101" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B102" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B103" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B104" t="s">
         <v>21</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B105" t="s">
         <v>224</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B106" t="s">
         <v>121</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B107" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B108" t="s">
         <v>263</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B109" t="s">
-        <v>275</v>
+        <v>693</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B110" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B111" t="s">
         <v>266</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B112" t="s">
         <v>41</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B113" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B114" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="B115" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C115" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B116" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C116" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B117" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C117" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B118" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C118" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B119" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C119" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B120" t="s">
         <v>224</v>
       </c>
       <c r="C120" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B121" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C121" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B122" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C122" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B123" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C123" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B124" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C124" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B125" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C125" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C126" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C127" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B128" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C128" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B129" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C129" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B130" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C130" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B131" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C131" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B132" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C132" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B133" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C133" t="s">
-        <v>597</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="B134" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -12553,7 +12638,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B3">
         <v>203</v>

--- a/metrics and parser/final_list_of_metrics.xlsx
+++ b/metrics and parser/final_list_of_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C6841A-BFC1-4029-87B2-EA96336792B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3628999B-BA60-4DEE-BF1A-78C2B5652A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="38115" windowHeight="23385" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,6 @@
     <author>tc={B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}</author>
     <author>tc={E017DF4E-5656-4CEF-B774-80BA936A6D56}</author>
     <author>tc={8A92D669-9E50-4C59-82E5-97B139270D19}</author>
-    <author>tc={CD59760B-76A7-492D-B20B-A2D9CF3FBC59}</author>
     <author>tc={121DA4BD-014E-470E-AB44-B9514592A80F}</author>
     <author>tc={41A1A9E9-8671-443A-BC53-E9E6789FC6B2}</author>
     <author>tc={EF886BF9-B28D-42E1-9B64-C8A7E72E082A}</author>
@@ -118,15 +117,7 @@
     Lattice von NextJS Page Compilation Duration</t>
       </text>
     </comment>
-    <comment ref="B33" authorId="6" shapeId="0" xr:uid="{CD59760B-76A7-492D-B20B-A2D9CF3FBC59}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    note that meta calls PRs/MRs diffs</t>
-      </text>
-    </comment>
-    <comment ref="H34" authorId="7" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
+    <comment ref="H34" authorId="6" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -134,7 +125,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="C52" authorId="8" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
+    <comment ref="C52" authorId="7" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -142,7 +133,7 @@
     „Time to Restore Services“ ergänzt nach Andres Input.</t>
       </text>
     </comment>
-    <comment ref="B54" authorId="9" shapeId="0" xr:uid="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
+    <comment ref="B54" authorId="8" shapeId="0" xr:uid="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -150,7 +141,7 @@
     Name gekürzt nach Andres Input.</t>
       </text>
     </comment>
-    <comment ref="H58" authorId="10" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
+    <comment ref="H58" authorId="9" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -158,7 +149,7 @@
     Nach Andres Input von DevEx zu Business/HR gewechselt.</t>
       </text>
     </comment>
-    <comment ref="H61" authorId="11" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
+    <comment ref="H61" authorId="10" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -166,7 +157,7 @@
     Nach Andres Input von Business zu Quality verschoben.</t>
       </text>
     </comment>
-    <comment ref="J69" authorId="12" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
+    <comment ref="J69" authorId="11" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -174,7 +165,7 @@
     Von Knowledge Expansion zu Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="C76" authorId="13" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
+    <comment ref="C76" authorId="12" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -182,7 +173,7 @@
     Nach Andres Kommentar zu einer Metrik zusammengefasst.</t>
       </text>
     </comment>
-    <comment ref="B77" authorId="14" shapeId="0" xr:uid="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
+    <comment ref="B77" authorId="13" shapeId="0" xr:uid="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -190,7 +181,7 @@
     Name angepasst nach Andres Input. Ursprünglich „Quality of Reviews of Work Contributed by Team Members“</t>
       </text>
     </comment>
-    <comment ref="C80" authorId="15" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
+    <comment ref="C80" authorId="14" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -198,7 +189,7 @@
     Nach Andres Input Availability hinzugefügt.</t>
       </text>
     </comment>
-    <comment ref="H85" authorId="16" shapeId="0" xr:uid="{EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}">
+    <comment ref="H85" authorId="15" shapeId="0" xr:uid="{EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -206,7 +197,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="C90" authorId="17" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
+    <comment ref="C90" authorId="16" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -214,7 +205,7 @@
     Nach Andres Input. Production Incidents und System Uptime / Availability hinzugefügt.</t>
       </text>
     </comment>
-    <comment ref="F90" authorId="18" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
+    <comment ref="F90" authorId="17" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -222,7 +213,7 @@
     Nach Andres Input angepasst.</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="19" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
+    <comment ref="H91" authorId="18" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -230,7 +221,7 @@
     Nach Andres Anregung von Business zu DevEx/Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="20" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
+    <comment ref="C92" authorId="19" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -243,7 +234,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="718">
   <si>
     <t>id</t>
   </si>
@@ -1663,9 +1654,6 @@
     <t>504; 214</t>
   </si>
   <si>
-    <t>504; 11; 96; 214</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1145/3454122.3454124</t>
   </si>
   <si>
@@ -1957,9 +1945,6 @@
     <t>105; 501; 131; 232</t>
   </si>
   <si>
-    <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 232</t>
-  </si>
-  <si>
     <t>508; 237; 232</t>
   </si>
   <si>
@@ -2360,6 +2345,51 @@
   </si>
   <si>
     <t>Human-equivalent hours of work completed by agents</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2602.03593</t>
+  </si>
+  <si>
+    <t>Chen (2026)</t>
+  </si>
+  <si>
+    <t>504; 11; 96; 214; 513</t>
+  </si>
+  <si>
+    <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 232; 513</t>
+  </si>
+  <si>
+    <t>Self-sufficiency</t>
+  </si>
+  <si>
+    <t>Degree to which AI reduces context-switching and reliance on external resources.</t>
+  </si>
+  <si>
+    <t>Code ownership</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>Whether developers maintain deep understanding of and accountability for AI-assisted code.</t>
+  </si>
+  <si>
+    <t>506; 512</t>
+  </si>
+  <si>
+    <t>Technical expertise development; Skill development</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Ease of peer review</t>
+  </si>
+  <si>
+    <t>Perceived ease and effort to perform a PR.</t>
   </si>
 </sst>
 </file>
@@ -2923,7 +2953,6 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Patrick Meyer" id="{2315245B-EC09-46AB-A06E-DE769C358132}" userId="S::patrick.meyer@oec.uzh.ch::70537bee-da28-4c70-a2c9-3c1febc86743" providerId="AD"/>
-  <person displayName="André Meyer" id="{9D9142B8-11C7-4802-A1A1-66D498664CB5}" userId="S::andre.meyer@access.uzh.ch::3b573077-43ef-44d1-acd0-87895ce1f23f" providerId="AD"/>
 </personList>
 </file>
 
@@ -3212,9 +3241,6 @@
   <threadedComment ref="D29" dT="2025-05-23T09:41:06.69" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{8A92D669-9E50-4C59-82E5-97B139270D19}">
     <text>Lattice von NextJS Page Compilation Duration</text>
   </threadedComment>
-  <threadedComment ref="B33" dT="2025-04-03T11:15:23.43" personId="{9D9142B8-11C7-4802-A1A1-66D498664CB5}" id="{CD59760B-76A7-492D-B20B-A2D9CF3FBC59}">
-    <text>note that meta calls PRs/MRs diffs</text>
-  </threadedComment>
   <threadedComment ref="H34" dT="2025-06-02T18:38:57.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{121DA4BD-014E-470E-AB44-B9514592A80F}">
     <text>Nach Andres Input von Business zu Process verschoben.</text>
   </threadedComment>
@@ -3322,19 +3348,19 @@
         <v>10</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R1" s="22" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
@@ -3348,16 +3374,16 @@
         <v>15</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
@@ -3393,7 +3419,7 @@
         <v>22</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R2" s="19" t="s">
         <v>11</v>
@@ -3419,7 +3445,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>23</v>
@@ -3455,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R3" s="19" t="s">
         <v>11</v>
@@ -3472,19 +3498,19 @@
         <v>275</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3517,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R4" s="19" t="s">
         <v>11</v>
@@ -3534,16 +3560,16 @@
         <v>11</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
@@ -3579,7 +3605,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R5" s="19" t="s">
         <v>11</v>
@@ -3599,16 +3625,16 @@
         <v>446</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3641,7 +3667,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R6" s="19" t="s">
         <v>11</v>
@@ -3667,7 +3693,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>12</v>
@@ -3703,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R7" s="19" t="s">
         <v>11</v>
@@ -3720,16 +3746,16 @@
         <v>11</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>38</v>
@@ -3791,7 +3817,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>38</v>
@@ -3827,7 +3853,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R9" s="19" t="s">
         <v>11</v>
@@ -3853,7 +3879,7 @@
         <v>45</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>38</v>
@@ -3889,7 +3915,7 @@
         <v>2</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R10" s="19" t="s">
         <v>11</v>
@@ -3915,7 +3941,7 @@
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
@@ -3951,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R11" s="19" t="s">
         <v>11</v>
@@ -3977,7 +4003,7 @@
         <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>38</v>
@@ -4013,7 +4039,7 @@
         <v>6</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R12" s="19" t="s">
         <v>11</v>
@@ -4030,16 +4056,16 @@
         <v>52</v>
       </c>
       <c r="D13" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>550</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>551</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>54</v>
@@ -4075,7 +4101,7 @@
         <v>8</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R13" s="19" t="s">
         <v>11</v>
@@ -4089,10 +4115,10 @@
         <v>55</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E14" s="20">
         <v>131</v>
@@ -4101,7 +4127,7 @@
         <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>38</v>
@@ -4154,16 +4180,16 @@
         <v>277</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>59</v>
@@ -4199,7 +4225,7 @@
         <v>26</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R15" s="19" t="s">
         <v>11</v>
@@ -4219,16 +4245,16 @@
         <v>11</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>472</v>
+        <v>706</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
@@ -4254,14 +4280,14 @@
       </c>
       <c r="O16" s="7">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>633</v>
+        <v>136</v>
       </c>
       <c r="R16" s="19" t="s">
         <v>11</v>
@@ -4287,7 +4313,7 @@
         <v>66</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
@@ -4323,7 +4349,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R17" s="19" t="s">
         <v>11</v>
@@ -4349,7 +4375,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>54</v>
@@ -4385,7 +4411,7 @@
         <v>2</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R18" s="19" t="s">
         <v>11</v>
@@ -4411,7 +4437,7 @@
         <v>73</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
@@ -4447,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R19" s="19" t="s">
         <v>11</v>
@@ -4467,13 +4493,13 @@
         <v>11</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>77</v>
@@ -4509,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R20" s="19" t="s">
         <v>11</v>
@@ -4535,7 +4561,7 @@
         <v>79</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>77</v>
@@ -4571,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R21" s="19" t="s">
         <v>11</v>
@@ -4585,10 +4611,10 @@
         <v>30</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>456</v>
@@ -4597,7 +4623,7 @@
         <v>80</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
@@ -4659,10 +4685,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4695,7 +4721,7 @@
         <v>2</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R23" s="19" t="s">
         <v>11</v>
@@ -4721,7 +4747,7 @@
         <v>85</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>38</v>
@@ -4757,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="Q24" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R24" s="19" t="s">
         <v>11</v>
@@ -4774,16 +4800,16 @@
         <v>11</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>77</v>
@@ -4839,13 +4865,13 @@
         <v>170</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>38</v>
@@ -4881,7 +4907,7 @@
         <v>4</v>
       </c>
       <c r="Q26" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R26" s="19" t="s">
         <v>11</v>
@@ -4907,7 +4933,7 @@
         <v>93</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>77</v>
@@ -4943,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R27" s="19" t="s">
         <v>11</v>
@@ -4969,7 +4995,7 @@
         <v>95</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
@@ -5005,7 +5031,7 @@
         <v>3</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R28" s="19" t="s">
         <v>11</v>
@@ -5022,16 +5048,16 @@
         <v>282</v>
       </c>
       <c r="D29" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>552</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>553</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>98</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>23</v>
@@ -5067,7 +5093,7 @@
         <v>8</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R29" s="19" t="s">
         <v>11</v>
@@ -5093,10 +5119,10 @@
         <v>100</v>
       </c>
       <c r="G30" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I30" s="7">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
@@ -5129,7 +5155,7 @@
         <v>3</v>
       </c>
       <c r="Q30" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R30" s="19" t="s">
         <v>11</v>
@@ -5143,22 +5169,22 @@
         <v>102</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>103</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I31" s="7">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
@@ -5217,7 +5243,7 @@
         <v>106</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>12</v>
@@ -5253,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R32" s="19" t="s">
         <v>11</v>
@@ -5270,7 +5296,7 @@
         <v>283</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>468</v>
@@ -5279,7 +5305,7 @@
         <v>108</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>17</v>
@@ -5341,7 +5367,7 @@
         <v>110</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
@@ -5377,7 +5403,7 @@
         <v>3</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R34" s="19" t="s">
         <v>11</v>
@@ -5394,19 +5420,19 @@
         <v>111</v>
       </c>
       <c r="D35" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>542</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>543</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>112</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I35" s="7">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5465,10 +5491,10 @@
         <v>114</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I36" s="7">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5501,7 +5527,7 @@
         <v>6</v>
       </c>
       <c r="Q36" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R36" s="19" t="s">
         <v>11</v>
@@ -5521,13 +5547,13 @@
         <v>11</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>116</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>38</v>
@@ -5563,7 +5589,7 @@
         <v>2</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R37" s="19" t="s">
         <v>11</v>
@@ -5589,10 +5615,10 @@
         <v>118</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I38" s="7">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
@@ -5625,7 +5651,7 @@
         <v>3</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R38" s="19" t="s">
         <v>11</v>
@@ -5639,19 +5665,19 @@
         <v>120</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>442</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>122</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>23</v>
@@ -5713,7 +5739,7 @@
         <v>125</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>23</v>
@@ -5749,7 +5775,7 @@
         <v>2</v>
       </c>
       <c r="Q40" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R40" s="19" t="s">
         <v>11</v>
@@ -5775,7 +5801,7 @@
         <v>128</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>54</v>
@@ -5837,10 +5863,10 @@
         <v>131</v>
       </c>
       <c r="G42" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I42" s="7">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5873,7 +5899,7 @@
         <v>2</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R42" s="19" t="s">
         <v>11</v>
@@ -5899,7 +5925,7 @@
         <v>133</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>17</v>
@@ -5935,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="Q43" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R43" s="19" t="s">
         <v>11</v>
@@ -5961,7 +5987,7 @@
         <v>135</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
@@ -5997,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="Q44" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R44" s="19" t="s">
         <v>11</v>
@@ -6017,16 +6043,16 @@
         <v>446</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>137</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I45" s="7">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6059,7 +6085,7 @@
         <v>4</v>
       </c>
       <c r="Q45" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R45" s="19" t="s">
         <v>11</v>
@@ -6085,7 +6111,7 @@
         <v>140</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>12</v>
@@ -6121,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="Q46" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R46" s="19" t="s">
         <v>11</v>
@@ -6138,19 +6164,19 @@
         <v>285</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>142</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I47" s="7">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
@@ -6209,10 +6235,10 @@
         <v>144</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I48" s="7">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -6262,16 +6288,16 @@
         <v>147</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>148</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>17</v>
@@ -6307,7 +6333,7 @@
         <v>11</v>
       </c>
       <c r="Q49" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R49" s="19" t="s">
         <v>11</v>
@@ -6324,7 +6350,7 @@
         <v>287</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E50" s="20" t="s">
         <v>465</v>
@@ -6333,7 +6359,7 @@
         <v>151</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>38</v>
@@ -6395,7 +6421,7 @@
         <v>153</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>23</v>
@@ -6431,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="Q51" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R51" s="19" t="s">
         <v>11</v>
@@ -6448,16 +6474,16 @@
         <v>288</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>155</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>23</v>
@@ -6493,7 +6519,7 @@
         <v>16</v>
       </c>
       <c r="Q52" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R52" s="19" t="s">
         <v>11</v>
@@ -6519,7 +6545,7 @@
         <v>157</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>54</v>
@@ -6555,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="Q53" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R53" s="19" t="s">
         <v>11</v>
@@ -6581,7 +6607,7 @@
         <v>159</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>54</v>
@@ -6617,7 +6643,7 @@
         <v>3</v>
       </c>
       <c r="Q54" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R54" s="19" t="s">
         <v>11</v>
@@ -6643,7 +6669,7 @@
         <v>161</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>77</v>
@@ -6679,7 +6705,7 @@
         <v>3</v>
       </c>
       <c r="Q55" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R55" s="19" t="s">
         <v>11</v>
@@ -6705,7 +6731,7 @@
         <v>163</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>38</v>
@@ -6741,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="Q56" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R56" s="19" t="s">
         <v>11</v>
@@ -6767,7 +6793,7 @@
         <v>165</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>17</v>
@@ -6803,7 +6829,7 @@
         <v>3</v>
       </c>
       <c r="Q57" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R57" s="19" t="s">
         <v>11</v>
@@ -6829,7 +6855,7 @@
         <v>167</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>12</v>
@@ -6865,7 +6891,7 @@
         <v>3</v>
       </c>
       <c r="Q58" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R58" s="19" t="s">
         <v>11</v>
@@ -6891,7 +6917,7 @@
         <v>170</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>23</v>
@@ -6927,7 +6953,7 @@
         <v>3</v>
       </c>
       <c r="Q59" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R59" s="19" t="s">
         <v>11</v>
@@ -6953,7 +6979,7 @@
         <v>173</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>12</v>
@@ -6989,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="Q60" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R60" s="19" t="s">
         <v>11</v>
@@ -7006,7 +7032,7 @@
         <v>11</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E61" s="20">
         <v>183</v>
@@ -7015,7 +7041,7 @@
         <v>175</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>38</v>
@@ -7051,7 +7077,7 @@
         <v>2</v>
       </c>
       <c r="Q61" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R61" s="19" t="s">
         <v>11</v>
@@ -7077,7 +7103,7 @@
         <v>177</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -7113,7 +7139,7 @@
         <v>2</v>
       </c>
       <c r="Q62" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R62" s="19" t="s">
         <v>11</v>
@@ -7139,10 +7165,10 @@
         <v>179</v>
       </c>
       <c r="G63" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I63" s="7">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -7175,7 +7201,7 @@
         <v>3</v>
       </c>
       <c r="Q63" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R63" s="19" t="s">
         <v>11</v>
@@ -7192,19 +7218,19 @@
         <v>181</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G64" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I64" s="7">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
@@ -7257,13 +7283,13 @@
         <v>445</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>77</v>
@@ -7325,7 +7351,7 @@
         <v>186</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>77</v>
@@ -7361,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="Q66" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R66" s="19" t="s">
         <v>11</v>
@@ -7387,7 +7413,7 @@
         <v>188</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>38</v>
@@ -7423,7 +7449,7 @@
         <v>2</v>
       </c>
       <c r="Q67" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R67" s="19" t="s">
         <v>11</v>
@@ -7449,7 +7475,7 @@
         <v>190</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>12</v>
@@ -7485,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R68" s="19" t="s">
         <v>11</v>
@@ -7499,10 +7525,10 @@
         <v>191</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E69" s="20" t="s">
         <v>470</v>
@@ -7511,10 +7537,10 @@
         <v>192</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I69" s="7">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
@@ -7573,7 +7599,7 @@
         <v>193</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>23</v>
@@ -7609,7 +7635,7 @@
         <v>2</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R70" s="19" t="s">
         <v>11</v>
@@ -7635,7 +7661,7 @@
         <v>195</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>17</v>
@@ -7671,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R71" s="19" t="s">
         <v>11</v>
@@ -7691,13 +7717,13 @@
         <v>441</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>197</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>17</v>
@@ -7733,7 +7759,7 @@
         <v>3</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R72" s="19" t="s">
         <v>11</v>
@@ -7750,7 +7776,7 @@
         <v>313</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E73" s="20" t="s">
         <v>433</v>
@@ -7759,7 +7785,7 @@
         <v>199</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>38</v>
@@ -7795,7 +7821,7 @@
         <v>3</v>
       </c>
       <c r="Q73" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R73" s="19" t="s">
         <v>11</v>
@@ -7821,7 +7847,7 @@
         <v>201</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>38</v>
@@ -7857,7 +7883,7 @@
         <v>4</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R74" s="19" t="s">
         <v>11</v>
@@ -7871,19 +7897,19 @@
         <v>202</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>203</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>38</v>
@@ -7939,13 +7965,13 @@
         <v>441</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>205</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>17</v>
@@ -7981,7 +8007,7 @@
         <v>4</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R76" s="19" t="s">
         <v>11</v>
@@ -8007,7 +8033,7 @@
         <v>207</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>54</v>
@@ -8043,7 +8069,7 @@
         <v>3</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R77" s="19" t="s">
         <v>11</v>
@@ -8069,7 +8095,7 @@
         <v>209</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>12</v>
@@ -8105,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R78" s="19" t="s">
         <v>11</v>
@@ -8131,7 +8157,7 @@
         <v>211</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>77</v>
@@ -8167,7 +8193,7 @@
         <v>4</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R79" s="19" t="s">
         <v>11</v>
@@ -8187,13 +8213,13 @@
         <v>442</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>214</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>23</v>
@@ -8229,7 +8255,7 @@
         <v>3</v>
       </c>
       <c r="Q80" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R80" s="19" t="s">
         <v>11</v>
@@ -8255,7 +8281,7 @@
         <v>216</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>23</v>
@@ -8291,7 +8317,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R81" s="19" t="s">
         <v>11</v>
@@ -8317,7 +8343,7 @@
         <v>218</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>12</v>
@@ -8353,7 +8379,7 @@
         <v>2</v>
       </c>
       <c r="Q82" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R82" s="19" t="s">
         <v>11</v>
@@ -8379,7 +8405,7 @@
         <v>220</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>12</v>
@@ -8415,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="Q83" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R83" s="19" t="s">
         <v>11</v>
@@ -8441,7 +8467,7 @@
         <v>222</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>12</v>
@@ -8477,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="Q84" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R84" s="19" t="s">
         <v>11</v>
@@ -8503,7 +8529,7 @@
         <v>225</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>17</v>
@@ -8539,7 +8565,7 @@
         <v>2</v>
       </c>
       <c r="Q85" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R85" s="19" t="s">
         <v>11</v>
@@ -8565,10 +8591,10 @@
         <v>228</v>
       </c>
       <c r="G86" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H86" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I86" s="7">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
@@ -8601,7 +8627,7 @@
         <v>2</v>
       </c>
       <c r="Q86" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R86" s="19" t="s">
         <v>11</v>
@@ -8618,16 +8644,16 @@
         <v>297</v>
       </c>
       <c r="D87" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="E87" s="20" t="s">
         <v>560</v>
-      </c>
-      <c r="E87" s="20" t="s">
-        <v>561</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>230</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>23</v>
@@ -8663,7 +8689,7 @@
         <v>4</v>
       </c>
       <c r="Q87" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R87" s="19" t="s">
         <v>11</v>
@@ -8680,16 +8706,16 @@
         <v>11</v>
       </c>
       <c r="D88" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="E88" s="20" t="s">
         <v>544</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>545</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>17</v>
@@ -8725,7 +8751,7 @@
         <v>7</v>
       </c>
       <c r="Q88" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R88" s="19" t="s">
         <v>11</v>
@@ -8742,16 +8768,16 @@
         <v>298</v>
       </c>
       <c r="D89" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="E89" s="20" t="s">
         <v>568</v>
-      </c>
-      <c r="E89" s="20" t="s">
-        <v>569</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>234</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>17</v>
@@ -8787,7 +8813,7 @@
         <v>8</v>
       </c>
       <c r="Q89" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R89" s="19" t="s">
         <v>11</v>
@@ -8801,10 +8827,10 @@
         <v>235</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D90" s="20" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E90" s="20" t="s">
         <v>461</v>
@@ -8813,7 +8839,7 @@
         <v>236</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>23</v>
@@ -8849,7 +8875,7 @@
         <v>8</v>
       </c>
       <c r="Q90" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R90" s="19" t="s">
         <v>11</v>
@@ -8863,22 +8889,22 @@
         <v>237</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>11</v>
+        <v>714</v>
       </c>
       <c r="D91" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="20">
-        <v>506</v>
+      <c r="E91" s="20" t="s">
+        <v>713</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>238</v>
       </c>
       <c r="G91" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I91" s="7">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
@@ -8904,14 +8930,14 @@
       </c>
       <c r="O91" s="7">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P91" s="7">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="19" t="s">
-        <v>633</v>
+        <v>136</v>
       </c>
       <c r="R91" s="19" t="s">
         <v>11</v>
@@ -8928,16 +8954,16 @@
         <v>314</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>570</v>
+        <v>707</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>241</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>59</v>
@@ -8966,14 +8992,14 @@
       </c>
       <c r="O92" s="7">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P92" s="7">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q92" s="19" t="s">
-        <v>633</v>
+        <v>136</v>
       </c>
       <c r="R92" s="19" t="s">
         <v>11</v>
@@ -8999,7 +9025,7 @@
         <v>243</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>54</v>
@@ -9035,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="Q93" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R93" s="19" t="s">
         <v>11</v>
@@ -9061,7 +9087,7 @@
         <v>245</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>38</v>
@@ -9097,7 +9123,7 @@
         <v>4</v>
       </c>
       <c r="Q94" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R94" s="19" t="s">
         <v>11</v>
@@ -9111,7 +9137,7 @@
         <v>43</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D95" s="19" t="s">
         <v>466</v>
@@ -9123,7 +9149,7 @@
         <v>247</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>38</v>
@@ -9185,7 +9211,7 @@
         <v>249</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>23</v>
@@ -9221,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R96" s="19" t="s">
         <v>11</v>
@@ -9247,7 +9273,7 @@
         <v>252</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>17</v>
@@ -9283,7 +9309,7 @@
         <v>2</v>
       </c>
       <c r="Q97" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R97" s="19" t="s">
         <v>11</v>
@@ -9309,7 +9335,7 @@
         <v>254</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>17</v>
@@ -9345,7 +9371,7 @@
         <v>3</v>
       </c>
       <c r="Q98" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R98" s="19" t="s">
         <v>11</v>
@@ -9362,7 +9388,7 @@
         <v>315</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E99" s="20" t="s">
         <v>452</v>
@@ -9371,7 +9397,7 @@
         <v>256</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>17</v>
@@ -9421,19 +9447,19 @@
         <v>257</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>258</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>17</v>
@@ -9486,19 +9512,19 @@
         <v>260</v>
       </c>
       <c r="D101" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="E101" s="20" t="s">
         <v>546</v>
-      </c>
-      <c r="E101" s="20" t="s">
-        <v>547</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>261</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I101" s="7">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
@@ -9531,7 +9557,7 @@
         <v>7</v>
       </c>
       <c r="Q101" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R101" s="19" t="s">
         <v>11</v>
@@ -9557,7 +9583,7 @@
         <v>264</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>59</v>
@@ -9593,7 +9619,7 @@
         <v>2</v>
       </c>
       <c r="Q102" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R102" s="19" t="s">
         <v>11</v>
@@ -9619,7 +9645,7 @@
         <v>267</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>59</v>
@@ -9655,7 +9681,7 @@
         <v>3</v>
       </c>
       <c r="Q103" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R103" s="19" t="s">
         <v>11</v>
@@ -9681,7 +9707,7 @@
         <v>269</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>59</v>
@@ -9717,7 +9743,7 @@
         <v>2</v>
       </c>
       <c r="Q104" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R104" s="19" t="s">
         <v>11</v>
@@ -9728,22 +9754,22 @@
         <v>129</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>302</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>59</v>
@@ -9796,19 +9822,19 @@
         <v>11</v>
       </c>
       <c r="D106" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="E106" s="20" t="s">
         <v>548</v>
-      </c>
-      <c r="E106" s="20" t="s">
-        <v>549</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>271</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I106" s="7">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
@@ -9841,7 +9867,7 @@
         <v>5</v>
       </c>
       <c r="Q106" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R106" s="19" t="s">
         <v>11</v>
@@ -9858,16 +9884,16 @@
         <v>304</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G107" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H107" t="s">
         <v>38</v>
@@ -9926,13 +9952,13 @@
         <v>183</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G108" t="s">
+        <v>533</v>
+      </c>
+      <c r="H108" t="s">
         <v>534</v>
-      </c>
-      <c r="H108" t="s">
-        <v>535</v>
       </c>
       <c r="I108" s="7">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
@@ -9965,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R108" s="19" t="s">
         <v>11</v>
@@ -9976,7 +10002,7 @@
         <v>136</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>11</v>
@@ -9988,10 +10014,10 @@
         <v>240</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G109" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H109" t="s">
         <v>59</v>
@@ -10027,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="Q109" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R109" s="19" t="s">
         <v>11</v>
@@ -10050,13 +10076,13 @@
         <v>308</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G110" t="s">
+        <v>533</v>
+      </c>
+      <c r="H110" t="s">
         <v>534</v>
-      </c>
-      <c r="H110" t="s">
-        <v>535</v>
       </c>
       <c r="I110" s="7">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
@@ -10089,7 +10115,7 @@
         <v>6</v>
       </c>
       <c r="Q110" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R110" s="19" t="s">
         <v>11</v>
@@ -10112,10 +10138,10 @@
         <v>236</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G111" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -10151,7 +10177,7 @@
         <v>1</v>
       </c>
       <c r="Q111" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R111" s="19" t="s">
         <v>11</v>
@@ -10162,7 +10188,7 @@
         <v>139</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>11</v>
@@ -10174,10 +10200,10 @@
         <v>11</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>23</v>
@@ -10213,7 +10239,7 @@
         <v>1</v>
       </c>
       <c r="Q112" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="R112" s="19" t="s">
         <v>11</v>
@@ -10224,22 +10250,22 @@
         <v>140</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>17</v>
@@ -10275,7 +10301,7 @@
         <v>18</v>
       </c>
       <c r="Q113" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="R113" s="19">
         <v>2</v>
@@ -10286,22 +10312,22 @@
         <v>141</v>
       </c>
       <c r="B114" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="19" t="s">
         <v>627</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" s="19" t="s">
-        <v>629</v>
-      </c>
       <c r="E114" s="20" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>59</v>
@@ -10337,7 +10363,7 @@
         <v>3</v>
       </c>
       <c r="Q114" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="R114" s="19">
         <v>129</v>
@@ -10348,22 +10374,22 @@
         <v>142</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>59</v>
@@ -10399,7 +10425,7 @@
         <v>2</v>
       </c>
       <c r="Q115" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="R115" s="19">
         <v>19</v>
@@ -10410,22 +10436,22 @@
         <v>143</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="E116" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>638</v>
-      </c>
       <c r="G116" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>59</v>
@@ -10461,7 +10487,7 @@
         <v>5</v>
       </c>
       <c r="Q116" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="R116" s="19" t="s">
         <v>11</v>
@@ -10472,22 +10498,22 @@
         <v>144</v>
       </c>
       <c r="B117" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E117" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>17</v>
@@ -10523,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="Q117" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="R117" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
@@ -10534,22 +10560,22 @@
         <v>145</v>
       </c>
       <c r="B118" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="17" t="s">
+        <v>612</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="7" t="s">
         <v>642</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D118" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="E118" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>644</v>
-      </c>
       <c r="G118" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H118" t="s">
         <v>12</v>
@@ -10585,10 +10611,10 @@
         <v>1</v>
       </c>
       <c r="Q118" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="R118" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -10596,22 +10622,22 @@
         <v>146</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D119" t="s">
+        <v>644</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="F119" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="E119" s="20" t="s">
-        <v>692</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>648</v>
-      </c>
       <c r="G119" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -10647,10 +10673,10 @@
         <v>6</v>
       </c>
       <c r="Q119" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="R119" s="19" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
@@ -10658,22 +10684,22 @@
         <v>147</v>
       </c>
       <c r="B120" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="17" t="s">
         <v>649</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" s="17" t="s">
-        <v>651</v>
-      </c>
       <c r="E120" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>17</v>
@@ -10709,10 +10735,10 @@
         <v>1</v>
       </c>
       <c r="Q120" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="R120" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
@@ -10720,22 +10746,22 @@
         <v>148</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D121" t="s">
+        <v>688</v>
+      </c>
+      <c r="E121" s="20" t="s">
         <v>690</v>
       </c>
-      <c r="E121" s="20" t="s">
-        <v>692</v>
-      </c>
       <c r="F121" s="7" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>12</v>
@@ -10774,7 +10800,7 @@
         <v>136</v>
       </c>
       <c r="R121" s="19" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
@@ -10782,22 +10808,22 @@
         <v>149</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>23</v>
@@ -10836,7 +10862,7 @@
         <v>136</v>
       </c>
       <c r="R122" s="19" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
@@ -10844,25 +10870,25 @@
         <v>150</v>
       </c>
       <c r="B123" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="C123" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>682</v>
-      </c>
-      <c r="E123" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>683</v>
-      </c>
       <c r="G123" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H123" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="I123" s="7">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -10898,7 +10924,7 @@
         <v>136</v>
       </c>
       <c r="R123" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="124" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -10906,22 +10932,22 @@
         <v>151</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>17</v>
@@ -10938,37 +10964,216 @@
         <v>327</v>
       </c>
       <c r="L124" s="7">
-        <f t="shared" ref="L124" si="36">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
+        <f t="shared" ref="L124:L125" si="36">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M124" s="7">
         <v>10</v>
       </c>
       <c r="N124" s="7">
-        <f t="shared" ref="N124" si="37">IF(D124="-",0,LEN(D124)-LEN(SUBSTITUTE(D124,";",""))+1)</f>
+        <f t="shared" ref="N124:N125" si="37">IF(D124="-",0,LEN(D124)-LEN(SUBSTITUTE(D124,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="O124" s="7">
-        <f t="shared" ref="O124" si="38">IF(E124="-",0,LEN(E124)-LEN(SUBSTITUTE(E124,";",""))+1)</f>
+        <f t="shared" ref="O124:O125" si="38">IF(E124="-",0,LEN(E124)-LEN(SUBSTITUTE(E124,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="P124" s="7">
-        <f t="shared" ref="P124" si="39">SUM(N124:O124)</f>
+        <f t="shared" ref="P124:P125" si="39">SUM(N124:O124)</f>
         <v>1</v>
       </c>
       <c r="Q124" s="19" t="s">
         <v>136</v>
       </c>
+      <c r="R124" s="19" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N125" s="7"/>
+      <c r="A125" s="7">
+        <v>152</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="I125" s="7">
+        <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K125" s="7">
+        <f>VLOOKUP(J125,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>321</v>
+      </c>
+      <c r="L125" s="7">
+        <f t="shared" ref="L125" si="40">IF(E125="-",0,1)+IF(D125="-",0,2)</f>
+        <v>1</v>
+      </c>
+      <c r="M125" s="7">
+        <v>11</v>
+      </c>
+      <c r="N125" s="7">
+        <f t="shared" ref="N125" si="41">IF(D125="-",0,LEN(D125)-LEN(SUBSTITUTE(D125,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="O125" s="7">
+        <f t="shared" ref="O125" si="42">IF(E125="-",0,LEN(E125)-LEN(SUBSTITUTE(E125,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="P125" s="7">
+        <f t="shared" ref="P125" si="43">SUM(N125:O125)</f>
+        <v>1</v>
+      </c>
+      <c r="Q125" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R125" s="19" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N126" s="7"/>
+      <c r="A126" s="7">
+        <v>153</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="F126" t="s">
+        <v>712</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="I126" s="7">
+        <f>VLOOKUP(H126,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K126" s="7">
+        <f>VLOOKUP(J126,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>322</v>
+      </c>
+      <c r="L126" s="7">
+        <f t="shared" ref="L126" si="44">IF(E126="-",0,1)+IF(D126="-",0,2)</f>
+        <v>1</v>
+      </c>
+      <c r="M126" s="7">
+        <v>12</v>
+      </c>
+      <c r="N126" s="7">
+        <f t="shared" ref="N126" si="45">IF(D126="-",0,LEN(D126)-LEN(SUBSTITUTE(D126,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="O126" s="7">
+        <f t="shared" ref="O126" si="46">IF(E126="-",0,LEN(E126)-LEN(SUBSTITUTE(E126,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="P126" s="7">
+        <f t="shared" ref="P126" si="47">SUM(N126:O126)</f>
+        <v>1</v>
+      </c>
+      <c r="Q126" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R126" s="19" t="s">
+        <v>711</v>
+      </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D127"/>
-      <c r="N127" s="7"/>
+      <c r="A127" s="7">
+        <v>154</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="I127" s="7">
+        <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J127" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K127" s="7">
+        <f>VLOOKUP(J127,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>313</v>
+      </c>
+      <c r="L127" s="7">
+        <f t="shared" ref="L127" si="48">IF(E127="-",0,1)+IF(D127="-",0,2)</f>
+        <v>1</v>
+      </c>
+      <c r="M127" s="7">
+        <v>13</v>
+      </c>
+      <c r="N127" s="7">
+        <f t="shared" ref="N127" si="49">IF(D127="-",0,LEN(D127)-LEN(SUBSTITUTE(D127,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="O127" s="7">
+        <f t="shared" ref="O127" si="50">IF(E127="-",0,LEN(E127)-LEN(SUBSTITUTE(E127,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="P127" s="7">
+        <f t="shared" ref="P127" si="51">SUM(N127:O127)</f>
+        <v>1</v>
+      </c>
+      <c r="Q127" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="R127" s="19" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N128" s="7"/>
@@ -11120,7 +11325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="17"/>
@@ -11243,10 +11448,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -11309,10 +11514,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C17" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -11452,7 +11657,7 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>368</v>
@@ -11595,7 +11800,7 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>393</v>
@@ -11606,7 +11811,7 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>394</v>
@@ -11639,10 +11844,10 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C47" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -11664,7 +11869,7 @@
         <v>399</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -11818,7 +12023,7 @@
         <v>274</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -11826,10 +12031,10 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
+        <v>473</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>474</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -11840,7 +12045,7 @@
         <v>429</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -11859,7 +12064,7 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>431</v>
@@ -11884,7 +12089,7 @@
         <v>139</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -11892,18 +12097,18 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C70" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="B71" t="s">
         <v>488</v>
-      </c>
-      <c r="B71" t="s">
-        <v>489</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>383</v>
@@ -11911,10 +12116,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B72" t="s">
         <v>490</v>
-      </c>
-      <c r="B72" t="s">
-        <v>491</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>383</v>
@@ -11922,10 +12127,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="B73" t="s">
         <v>492</v>
-      </c>
-      <c r="B73" t="s">
-        <v>493</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>383</v>
@@ -11933,10 +12138,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B74" t="s">
         <v>494</v>
-      </c>
-      <c r="B74" t="s">
-        <v>495</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>383</v>
@@ -11944,7 +12149,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s">
         <v>224</v>
@@ -11955,10 +12160,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="B76" t="s">
         <v>497</v>
-      </c>
-      <c r="B76" t="s">
-        <v>498</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>383</v>
@@ -11966,10 +12171,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="B77" t="s">
         <v>499</v>
-      </c>
-      <c r="B77" t="s">
-        <v>500</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>383</v>
@@ -11977,7 +12182,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
@@ -11988,10 +12193,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>383</v>
@@ -11999,10 +12204,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B80" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>383</v>
@@ -12013,7 +12218,7 @@
         <v>466</v>
       </c>
       <c r="B81" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>383</v>
@@ -12021,10 +12226,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="B82" t="s">
         <v>505</v>
-      </c>
-      <c r="B82" t="s">
-        <v>506</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>383</v>
@@ -12032,10 +12237,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="B83" t="s">
         <v>507</v>
-      </c>
-      <c r="B83" t="s">
-        <v>508</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>383</v>
@@ -12043,10 +12248,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="B84" t="s">
         <v>509</v>
-      </c>
-      <c r="B84" t="s">
-        <v>510</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>383</v>
@@ -12054,7 +12259,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B85" t="s">
         <v>266</v>
@@ -12065,10 +12270,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="B86" t="s">
         <v>512</v>
-      </c>
-      <c r="B86" t="s">
-        <v>513</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>383</v>
@@ -12076,10 +12281,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="B87" t="s">
         <v>514</v>
-      </c>
-      <c r="B87" t="s">
-        <v>515</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>383</v>
@@ -12087,10 +12292,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="B88" t="s">
         <v>516</v>
-      </c>
-      <c r="B88" t="s">
-        <v>517</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>383</v>
@@ -12098,10 +12303,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="B89" t="s">
         <v>518</v>
-      </c>
-      <c r="B89" t="s">
-        <v>519</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>383</v>
@@ -12109,10 +12314,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="B90" t="s">
         <v>520</v>
-      </c>
-      <c r="B90" t="s">
-        <v>521</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>383</v>
@@ -12120,10 +12325,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B91" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>385</v>
@@ -12131,7 +12336,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B92" t="s">
         <v>381</v>
@@ -12142,10 +12347,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B93" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>392</v>
@@ -12164,7 +12369,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B95" t="s">
         <v>381</v>
@@ -12175,7 +12380,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B96" t="s">
         <v>266</v>
@@ -12186,7 +12391,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B97" t="s">
         <v>381</v>
@@ -12197,10 +12402,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="B98" t="s">
         <v>478</v>
-      </c>
-      <c r="B98" t="s">
-        <v>479</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>425</v>
@@ -12230,10 +12435,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="B101" t="s">
         <v>480</v>
-      </c>
-      <c r="B101" t="s">
-        <v>481</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>425</v>
@@ -12241,10 +12446,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="B102" t="s">
         <v>482</v>
-      </c>
-      <c r="B102" t="s">
-        <v>483</v>
       </c>
       <c r="C102" s="15" t="s">
         <v>425</v>
@@ -12252,10 +12457,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="B103" t="s">
         <v>484</v>
-      </c>
-      <c r="B103" t="s">
-        <v>485</v>
       </c>
       <c r="C103" s="15" t="s">
         <v>425</v>
@@ -12296,10 +12501,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="B107" t="s">
         <v>486</v>
-      </c>
-      <c r="B107" t="s">
-        <v>487</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>425</v>
@@ -12321,7 +12526,7 @@
         <v>445</v>
       </c>
       <c r="B109" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>425</v>
@@ -12332,7 +12537,7 @@
         <v>446</v>
       </c>
       <c r="B110" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>425</v>
@@ -12362,7 +12567,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B113" t="s">
         <v>381</v>
@@ -12373,7 +12578,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B114" t="s">
         <v>381</v>
@@ -12384,222 +12589,233 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B115" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C115" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B116" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C116" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B117" t="s">
         <v>381</v>
       </c>
       <c r="C117" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B118" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C118" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B119" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C119" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B120" t="s">
         <v>224</v>
       </c>
       <c r="C120" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B121" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C121" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B122" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C122" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B123" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C123" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B124" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C124" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B125" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C125" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B126" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C126" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B127" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C127" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B128" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C128" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B129" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C129" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="B130" t="s">
         <v>618</v>
       </c>
-      <c r="B130" t="s">
-        <v>620</v>
-      </c>
       <c r="C130" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B131" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C131" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B132" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C132" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C133" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B134" t="s">
         <v>396</v>
       </c>
       <c r="C134" t="s">
-        <v>691</v>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="B135" t="s">
+        <v>705</v>
+      </c>
+      <c r="C135" t="s">
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -12638,7 +12854,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B3">
         <v>203</v>

--- a/metrics and parser/final_list_of_metrics.xlsx
+++ b/metrics and parser/final_list_of_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3628999B-BA60-4DEE-BF1A-78C2B5652A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAACB6FF-1614-4915-ADC8-8F0A32D28403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="38115" windowHeight="23385" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="562" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -1753,9 +1753,6 @@
     <t>131l</t>
   </si>
   <si>
-    <t>Facebook (Meta)</t>
-  </si>
-  <si>
     <t>131m</t>
   </si>
   <si>
@@ -2257,9 +2254,6 @@
     <t>Developer CSAT; Developer Experience Index (DXI); Developer Satisfaction Score; Developer Sentiment; Developer Survey with a Focus on Perceptions of Friction; DSAT (Developer Satisfaction); Employee satisfaction; Net User Satisfaction (NSAT); Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; Developer Ratings for the New System; AI tool CSAT; Bad developer days</t>
   </si>
   <si>
-    <t>501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; t11k; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r</t>
-  </si>
-  <si>
     <t>Time to Release; Feature Delivery Time; Innovation Velocity</t>
   </si>
   <si>
@@ -2390,6 +2384,12 @@
   </si>
   <si>
     <t>Perceived ease and effort to perform a PR.</t>
+  </si>
+  <si>
+    <t>501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; 511k; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r</t>
+  </si>
+  <si>
+    <t>Meta</t>
   </si>
 </sst>
 </file>
@@ -2609,16 +2609,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2639,21 +2629,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2739,6 +2729,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2759,21 +2759,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3348,19 +3348,19 @@
         <v>10</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R1" s="22" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
@@ -3374,16 +3374,16 @@
         <v>15</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
@@ -3419,7 +3419,7 @@
         <v>22</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R2" s="19" t="s">
         <v>11</v>
@@ -3445,7 +3445,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>23</v>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R3" s="19" t="s">
         <v>11</v>
@@ -3498,19 +3498,19 @@
         <v>275</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3543,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R4" s="19" t="s">
         <v>11</v>
@@ -3563,13 +3563,13 @@
         <v>485</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
@@ -3605,7 +3605,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R5" s="19" t="s">
         <v>11</v>
@@ -3625,16 +3625,16 @@
         <v>446</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3667,7 +3667,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R6" s="19" t="s">
         <v>11</v>
@@ -3693,7 +3693,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>12</v>
@@ -3729,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R7" s="19" t="s">
         <v>11</v>
@@ -3746,16 +3746,16 @@
         <v>11</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>38</v>
@@ -3817,7 +3817,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>38</v>
@@ -3853,7 +3853,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R9" s="19" t="s">
         <v>11</v>
@@ -3879,7 +3879,7 @@
         <v>45</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>38</v>
@@ -3915,7 +3915,7 @@
         <v>2</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R10" s="19" t="s">
         <v>11</v>
@@ -3941,7 +3941,7 @@
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R11" s="19" t="s">
         <v>11</v>
@@ -4003,7 +4003,7 @@
         <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>38</v>
@@ -4039,7 +4039,7 @@
         <v>6</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R12" s="19" t="s">
         <v>11</v>
@@ -4056,16 +4056,16 @@
         <v>52</v>
       </c>
       <c r="D13" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>549</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>550</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>54</v>
@@ -4101,7 +4101,7 @@
         <v>8</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R13" s="19" t="s">
         <v>11</v>
@@ -4115,10 +4115,10 @@
         <v>55</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E14" s="20">
         <v>131</v>
@@ -4127,7 +4127,7 @@
         <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>38</v>
@@ -4180,16 +4180,16 @@
         <v>277</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>59</v>
@@ -4225,7 +4225,7 @@
         <v>26</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R15" s="19" t="s">
         <v>11</v>
@@ -4245,16 +4245,16 @@
         <v>11</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
@@ -4313,7 +4313,7 @@
         <v>66</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
@@ -4349,7 +4349,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R17" s="19" t="s">
         <v>11</v>
@@ -4375,7 +4375,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>54</v>
@@ -4411,7 +4411,7 @@
         <v>2</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R18" s="19" t="s">
         <v>11</v>
@@ -4437,7 +4437,7 @@
         <v>73</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R19" s="19" t="s">
         <v>11</v>
@@ -4493,13 +4493,13 @@
         <v>11</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>77</v>
@@ -4535,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R20" s="19" t="s">
         <v>11</v>
@@ -4561,7 +4561,7 @@
         <v>79</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>77</v>
@@ -4597,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R21" s="19" t="s">
         <v>11</v>
@@ -4611,10 +4611,10 @@
         <v>30</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>661</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>662</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>456</v>
@@ -4623,7 +4623,7 @@
         <v>80</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
@@ -4685,10 +4685,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4721,7 +4721,7 @@
         <v>2</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R23" s="19" t="s">
         <v>11</v>
@@ -4747,7 +4747,7 @@
         <v>85</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>38</v>
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="Q24" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R24" s="19" t="s">
         <v>11</v>
@@ -4800,16 +4800,16 @@
         <v>11</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>77</v>
@@ -4865,13 +4865,13 @@
         <v>170</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>38</v>
@@ -4907,7 +4907,7 @@
         <v>4</v>
       </c>
       <c r="Q26" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R26" s="19" t="s">
         <v>11</v>
@@ -4933,7 +4933,7 @@
         <v>93</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>77</v>
@@ -4969,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R27" s="19" t="s">
         <v>11</v>
@@ -4995,7 +4995,7 @@
         <v>95</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
@@ -5031,7 +5031,7 @@
         <v>3</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R28" s="19" t="s">
         <v>11</v>
@@ -5048,16 +5048,16 @@
         <v>282</v>
       </c>
       <c r="D29" s="20" t="s">
+        <v>550</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>551</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>552</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>98</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>23</v>
@@ -5093,7 +5093,7 @@
         <v>8</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R29" s="19" t="s">
         <v>11</v>
@@ -5119,10 +5119,10 @@
         <v>100</v>
       </c>
       <c r="G30" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I30" s="7">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
@@ -5155,7 +5155,7 @@
         <v>3</v>
       </c>
       <c r="Q30" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R30" s="19" t="s">
         <v>11</v>
@@ -5169,22 +5169,22 @@
         <v>102</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>673</v>
+        <v>716</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>103</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I31" s="7">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
@@ -5243,7 +5243,7 @@
         <v>106</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>12</v>
@@ -5279,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R32" s="19" t="s">
         <v>11</v>
@@ -5296,7 +5296,7 @@
         <v>283</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>468</v>
@@ -5305,7 +5305,7 @@
         <v>108</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>17</v>
@@ -5367,7 +5367,7 @@
         <v>110</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
@@ -5403,7 +5403,7 @@
         <v>3</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R34" s="19" t="s">
         <v>11</v>
@@ -5420,19 +5420,19 @@
         <v>111</v>
       </c>
       <c r="D35" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>541</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>542</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>112</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I35" s="7">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5491,10 +5491,10 @@
         <v>114</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I36" s="7">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5527,7 +5527,7 @@
         <v>6</v>
       </c>
       <c r="Q36" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R36" s="19" t="s">
         <v>11</v>
@@ -5547,13 +5547,13 @@
         <v>11</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>116</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>38</v>
@@ -5589,7 +5589,7 @@
         <v>2</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R37" s="19" t="s">
         <v>11</v>
@@ -5615,10 +5615,10 @@
         <v>118</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I38" s="7">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
@@ -5651,7 +5651,7 @@
         <v>3</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R38" s="19" t="s">
         <v>11</v>
@@ -5665,19 +5665,19 @@
         <v>120</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>442</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>122</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>23</v>
@@ -5739,7 +5739,7 @@
         <v>125</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>23</v>
@@ -5775,7 +5775,7 @@
         <v>2</v>
       </c>
       <c r="Q40" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R40" s="19" t="s">
         <v>11</v>
@@ -5801,7 +5801,7 @@
         <v>128</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>54</v>
@@ -5863,10 +5863,10 @@
         <v>131</v>
       </c>
       <c r="G42" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I42" s="7">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5899,7 +5899,7 @@
         <v>2</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R42" s="19" t="s">
         <v>11</v>
@@ -5925,7 +5925,7 @@
         <v>133</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>17</v>
@@ -5961,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="Q43" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R43" s="19" t="s">
         <v>11</v>
@@ -5987,7 +5987,7 @@
         <v>135</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
@@ -6023,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="Q44" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R44" s="19" t="s">
         <v>11</v>
@@ -6043,16 +6043,16 @@
         <v>446</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>137</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I45" s="7">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6085,7 +6085,7 @@
         <v>4</v>
       </c>
       <c r="Q45" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R45" s="19" t="s">
         <v>11</v>
@@ -6111,7 +6111,7 @@
         <v>140</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>12</v>
@@ -6147,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="Q46" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R46" s="19" t="s">
         <v>11</v>
@@ -6164,19 +6164,19 @@
         <v>285</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>142</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I47" s="7">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
@@ -6235,10 +6235,10 @@
         <v>144</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I48" s="7">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -6288,16 +6288,16 @@
         <v>147</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>148</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>17</v>
@@ -6333,7 +6333,7 @@
         <v>11</v>
       </c>
       <c r="Q49" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R49" s="19" t="s">
         <v>11</v>
@@ -6350,7 +6350,7 @@
         <v>287</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E50" s="20" t="s">
         <v>465</v>
@@ -6359,7 +6359,7 @@
         <v>151</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>38</v>
@@ -6421,7 +6421,7 @@
         <v>153</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>23</v>
@@ -6457,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="Q51" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R51" s="19" t="s">
         <v>11</v>
@@ -6474,16 +6474,16 @@
         <v>288</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>155</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>23</v>
@@ -6519,7 +6519,7 @@
         <v>16</v>
       </c>
       <c r="Q52" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R52" s="19" t="s">
         <v>11</v>
@@ -6545,7 +6545,7 @@
         <v>157</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>54</v>
@@ -6581,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="Q53" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R53" s="19" t="s">
         <v>11</v>
@@ -6607,7 +6607,7 @@
         <v>159</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>54</v>
@@ -6643,7 +6643,7 @@
         <v>3</v>
       </c>
       <c r="Q54" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R54" s="19" t="s">
         <v>11</v>
@@ -6669,7 +6669,7 @@
         <v>161</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>77</v>
@@ -6705,7 +6705,7 @@
         <v>3</v>
       </c>
       <c r="Q55" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R55" s="19" t="s">
         <v>11</v>
@@ -6731,7 +6731,7 @@
         <v>163</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>38</v>
@@ -6767,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="Q56" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R56" s="19" t="s">
         <v>11</v>
@@ -6793,7 +6793,7 @@
         <v>165</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>17</v>
@@ -6829,7 +6829,7 @@
         <v>3</v>
       </c>
       <c r="Q57" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R57" s="19" t="s">
         <v>11</v>
@@ -6855,7 +6855,7 @@
         <v>167</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>12</v>
@@ -6891,7 +6891,7 @@
         <v>3</v>
       </c>
       <c r="Q58" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R58" s="19" t="s">
         <v>11</v>
@@ -6917,7 +6917,7 @@
         <v>170</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>23</v>
@@ -6953,7 +6953,7 @@
         <v>3</v>
       </c>
       <c r="Q59" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R59" s="19" t="s">
         <v>11</v>
@@ -6979,7 +6979,7 @@
         <v>173</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>12</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="Q60" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R60" s="19" t="s">
         <v>11</v>
@@ -7032,7 +7032,7 @@
         <v>11</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E61" s="20">
         <v>183</v>
@@ -7041,7 +7041,7 @@
         <v>175</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>38</v>
@@ -7077,7 +7077,7 @@
         <v>2</v>
       </c>
       <c r="Q61" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R61" s="19" t="s">
         <v>11</v>
@@ -7103,7 +7103,7 @@
         <v>177</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -7139,7 +7139,7 @@
         <v>2</v>
       </c>
       <c r="Q62" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R62" s="19" t="s">
         <v>11</v>
@@ -7165,10 +7165,10 @@
         <v>179</v>
       </c>
       <c r="G63" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I63" s="7">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -7201,7 +7201,7 @@
         <v>3</v>
       </c>
       <c r="Q63" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R63" s="19" t="s">
         <v>11</v>
@@ -7218,19 +7218,19 @@
         <v>181</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G64" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I64" s="7">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
@@ -7283,13 +7283,13 @@
         <v>445</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>77</v>
@@ -7351,7 +7351,7 @@
         <v>186</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>77</v>
@@ -7387,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="Q66" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R66" s="19" t="s">
         <v>11</v>
@@ -7413,7 +7413,7 @@
         <v>188</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>38</v>
@@ -7449,7 +7449,7 @@
         <v>2</v>
       </c>
       <c r="Q67" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R67" s="19" t="s">
         <v>11</v>
@@ -7475,7 +7475,7 @@
         <v>190</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>12</v>
@@ -7511,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R68" s="19" t="s">
         <v>11</v>
@@ -7525,10 +7525,10 @@
         <v>191</v>
       </c>
       <c r="C69" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="D69" s="19" t="s">
         <v>670</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>671</v>
       </c>
       <c r="E69" s="20" t="s">
         <v>470</v>
@@ -7537,10 +7537,10 @@
         <v>192</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I69" s="7">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
@@ -7599,7 +7599,7 @@
         <v>193</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>23</v>
@@ -7635,7 +7635,7 @@
         <v>2</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R70" s="19" t="s">
         <v>11</v>
@@ -7661,7 +7661,7 @@
         <v>195</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>17</v>
@@ -7697,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R71" s="19" t="s">
         <v>11</v>
@@ -7717,13 +7717,13 @@
         <v>441</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>197</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>17</v>
@@ -7759,7 +7759,7 @@
         <v>3</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R72" s="19" t="s">
         <v>11</v>
@@ -7776,7 +7776,7 @@
         <v>313</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E73" s="20" t="s">
         <v>433</v>
@@ -7785,7 +7785,7 @@
         <v>199</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>38</v>
@@ -7821,7 +7821,7 @@
         <v>3</v>
       </c>
       <c r="Q73" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R73" s="19" t="s">
         <v>11</v>
@@ -7847,7 +7847,7 @@
         <v>201</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>38</v>
@@ -7883,7 +7883,7 @@
         <v>4</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R74" s="19" t="s">
         <v>11</v>
@@ -7897,19 +7897,19 @@
         <v>202</v>
       </c>
       <c r="C75" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="D75" s="19" t="s">
         <v>663</v>
       </c>
-      <c r="D75" s="19" t="s">
-        <v>664</v>
-      </c>
       <c r="E75" s="20" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>203</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>38</v>
@@ -7965,13 +7965,13 @@
         <v>441</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>205</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>17</v>
@@ -8007,7 +8007,7 @@
         <v>4</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R76" s="19" t="s">
         <v>11</v>
@@ -8033,7 +8033,7 @@
         <v>207</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>54</v>
@@ -8069,7 +8069,7 @@
         <v>3</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R77" s="19" t="s">
         <v>11</v>
@@ -8095,7 +8095,7 @@
         <v>209</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>12</v>
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R78" s="19" t="s">
         <v>11</v>
@@ -8157,7 +8157,7 @@
         <v>211</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>77</v>
@@ -8193,7 +8193,7 @@
         <v>4</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R79" s="19" t="s">
         <v>11</v>
@@ -8213,13 +8213,13 @@
         <v>442</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>214</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>23</v>
@@ -8255,7 +8255,7 @@
         <v>3</v>
       </c>
       <c r="Q80" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R80" s="19" t="s">
         <v>11</v>
@@ -8281,7 +8281,7 @@
         <v>216</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>23</v>
@@ -8317,7 +8317,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R81" s="19" t="s">
         <v>11</v>
@@ -8343,7 +8343,7 @@
         <v>218</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>12</v>
@@ -8379,7 +8379,7 @@
         <v>2</v>
       </c>
       <c r="Q82" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R82" s="19" t="s">
         <v>11</v>
@@ -8405,7 +8405,7 @@
         <v>220</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>12</v>
@@ -8441,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="Q83" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R83" s="19" t="s">
         <v>11</v>
@@ -8467,7 +8467,7 @@
         <v>222</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>12</v>
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="Q84" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R84" s="19" t="s">
         <v>11</v>
@@ -8529,7 +8529,7 @@
         <v>225</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>17</v>
@@ -8565,7 +8565,7 @@
         <v>2</v>
       </c>
       <c r="Q85" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R85" s="19" t="s">
         <v>11</v>
@@ -8591,10 +8591,10 @@
         <v>228</v>
       </c>
       <c r="G86" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H86" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I86" s="7">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
@@ -8627,7 +8627,7 @@
         <v>2</v>
       </c>
       <c r="Q86" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R86" s="19" t="s">
         <v>11</v>
@@ -8644,16 +8644,16 @@
         <v>297</v>
       </c>
       <c r="D87" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="E87" s="20" t="s">
         <v>559</v>
-      </c>
-      <c r="E87" s="20" t="s">
-        <v>560</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>230</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>23</v>
@@ -8689,7 +8689,7 @@
         <v>4</v>
       </c>
       <c r="Q87" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R87" s="19" t="s">
         <v>11</v>
@@ -8706,16 +8706,16 @@
         <v>11</v>
       </c>
       <c r="D88" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="E88" s="20" t="s">
         <v>543</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>544</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>17</v>
@@ -8751,7 +8751,7 @@
         <v>7</v>
       </c>
       <c r="Q88" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R88" s="19" t="s">
         <v>11</v>
@@ -8768,16 +8768,16 @@
         <v>298</v>
       </c>
       <c r="D89" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="E89" s="20" t="s">
         <v>567</v>
-      </c>
-      <c r="E89" s="20" t="s">
-        <v>568</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>234</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>17</v>
@@ -8813,7 +8813,7 @@
         <v>8</v>
       </c>
       <c r="Q89" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R89" s="19" t="s">
         <v>11</v>
@@ -8827,10 +8827,10 @@
         <v>235</v>
       </c>
       <c r="C90" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D90" s="20" t="s">
         <v>577</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>578</v>
       </c>
       <c r="E90" s="20" t="s">
         <v>461</v>
@@ -8839,7 +8839,7 @@
         <v>236</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>23</v>
@@ -8875,7 +8875,7 @@
         <v>8</v>
       </c>
       <c r="Q90" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R90" s="19" t="s">
         <v>11</v>
@@ -8889,22 +8889,22 @@
         <v>237</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D91" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>238</v>
       </c>
       <c r="G91" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I91" s="7">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
@@ -8954,16 +8954,16 @@
         <v>314</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>241</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>59</v>
@@ -9025,7 +9025,7 @@
         <v>243</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>54</v>
@@ -9061,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="Q93" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R93" s="19" t="s">
         <v>11</v>
@@ -9087,7 +9087,7 @@
         <v>245</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>38</v>
@@ -9123,7 +9123,7 @@
         <v>4</v>
       </c>
       <c r="Q94" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R94" s="19" t="s">
         <v>11</v>
@@ -9137,7 +9137,7 @@
         <v>43</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D95" s="19" t="s">
         <v>466</v>
@@ -9149,7 +9149,7 @@
         <v>247</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>38</v>
@@ -9211,7 +9211,7 @@
         <v>249</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>23</v>
@@ -9247,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R96" s="19" t="s">
         <v>11</v>
@@ -9273,7 +9273,7 @@
         <v>252</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>17</v>
@@ -9309,7 +9309,7 @@
         <v>2</v>
       </c>
       <c r="Q97" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R97" s="19" t="s">
         <v>11</v>
@@ -9335,7 +9335,7 @@
         <v>254</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>17</v>
@@ -9371,7 +9371,7 @@
         <v>3</v>
       </c>
       <c r="Q98" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R98" s="19" t="s">
         <v>11</v>
@@ -9388,7 +9388,7 @@
         <v>315</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E99" s="20" t="s">
         <v>452</v>
@@ -9397,7 +9397,7 @@
         <v>256</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>17</v>
@@ -9447,19 +9447,19 @@
         <v>257</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>258</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>17</v>
@@ -9512,19 +9512,19 @@
         <v>260</v>
       </c>
       <c r="D101" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="E101" s="20" t="s">
         <v>545</v>
-      </c>
-      <c r="E101" s="20" t="s">
-        <v>546</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>261</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I101" s="7">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
@@ -9557,7 +9557,7 @@
         <v>7</v>
       </c>
       <c r="Q101" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R101" s="19" t="s">
         <v>11</v>
@@ -9583,7 +9583,7 @@
         <v>264</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>59</v>
@@ -9619,7 +9619,7 @@
         <v>2</v>
       </c>
       <c r="Q102" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R102" s="19" t="s">
         <v>11</v>
@@ -9645,7 +9645,7 @@
         <v>267</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>59</v>
@@ -9681,7 +9681,7 @@
         <v>3</v>
       </c>
       <c r="Q103" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R103" s="19" t="s">
         <v>11</v>
@@ -9707,7 +9707,7 @@
         <v>269</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>59</v>
@@ -9743,7 +9743,7 @@
         <v>2</v>
       </c>
       <c r="Q104" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R104" s="19" t="s">
         <v>11</v>
@@ -9754,22 +9754,22 @@
         <v>129</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>302</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>59</v>
@@ -9822,19 +9822,19 @@
         <v>11</v>
       </c>
       <c r="D106" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="E106" s="20" t="s">
         <v>547</v>
-      </c>
-      <c r="E106" s="20" t="s">
-        <v>548</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>271</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I106" s="7">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
@@ -9867,7 +9867,7 @@
         <v>5</v>
       </c>
       <c r="Q106" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R106" s="19" t="s">
         <v>11</v>
@@ -9884,16 +9884,16 @@
         <v>304</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G107" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H107" t="s">
         <v>38</v>
@@ -9952,13 +9952,13 @@
         <v>183</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G108" t="s">
+        <v>532</v>
+      </c>
+      <c r="H108" t="s">
         <v>533</v>
-      </c>
-      <c r="H108" t="s">
-        <v>534</v>
       </c>
       <c r="I108" s="7">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
@@ -9991,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R108" s="19" t="s">
         <v>11</v>
@@ -10002,7 +10002,7 @@
         <v>136</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>11</v>
@@ -10014,10 +10014,10 @@
         <v>240</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G109" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H109" t="s">
         <v>59</v>
@@ -10053,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="Q109" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R109" s="19" t="s">
         <v>11</v>
@@ -10076,13 +10076,13 @@
         <v>308</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G110" t="s">
+        <v>532</v>
+      </c>
+      <c r="H110" t="s">
         <v>533</v>
-      </c>
-      <c r="H110" t="s">
-        <v>534</v>
       </c>
       <c r="I110" s="7">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
@@ -10115,7 +10115,7 @@
         <v>6</v>
       </c>
       <c r="Q110" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R110" s="19" t="s">
         <v>11</v>
@@ -10138,10 +10138,10 @@
         <v>236</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G111" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -10177,7 +10177,7 @@
         <v>1</v>
       </c>
       <c r="Q111" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R111" s="19" t="s">
         <v>11</v>
@@ -10188,7 +10188,7 @@
         <v>139</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>11</v>
@@ -10200,10 +10200,10 @@
         <v>11</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>23</v>
@@ -10239,7 +10239,7 @@
         <v>1</v>
       </c>
       <c r="Q112" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R112" s="19" t="s">
         <v>11</v>
@@ -10250,22 +10250,22 @@
         <v>140</v>
       </c>
       <c r="B113" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="C113" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>652</v>
-      </c>
-      <c r="E113" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>621</v>
-      </c>
       <c r="G113" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>17</v>
@@ -10289,7 +10289,7 @@
         <v>0</v>
       </c>
       <c r="N113" s="7">
-        <f t="shared" ref="N113:N114" si="11">IF(D113="-",0,LEN(D113)-LEN(SUBSTITUTE(D113,";",""))+1)</f>
+        <f t="shared" ref="N113" si="11">IF(D113="-",0,LEN(D113)-LEN(SUBSTITUTE(D113,";",""))+1)</f>
         <v>17</v>
       </c>
       <c r="O113" s="7">
@@ -10301,7 +10301,7 @@
         <v>18</v>
       </c>
       <c r="Q113" s="19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R113" s="19">
         <v>2</v>
@@ -10312,22 +10312,22 @@
         <v>141</v>
       </c>
       <c r="B114" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="F114" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="E114" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>626</v>
-      </c>
       <c r="G114" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>59</v>
@@ -10351,7 +10351,7 @@
         <v>0</v>
       </c>
       <c r="N114" s="7">
-        <f t="shared" ref="N114:N115" si="12">IF(D114="-",0,LEN(D114)-LEN(SUBSTITUTE(D114,";",""))+1)</f>
+        <f t="shared" ref="N114" si="12">IF(D114="-",0,LEN(D114)-LEN(SUBSTITUTE(D114,";",""))+1)</f>
         <v>2</v>
       </c>
       <c r="O114" s="7">
@@ -10363,7 +10363,7 @@
         <v>3</v>
       </c>
       <c r="Q114" s="19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R114" s="19">
         <v>129</v>
@@ -10374,22 +10374,22 @@
         <v>142</v>
       </c>
       <c r="B115" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="C115" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>603</v>
-      </c>
-      <c r="E115" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>629</v>
-      </c>
       <c r="G115" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>59</v>
@@ -10425,7 +10425,7 @@
         <v>2</v>
       </c>
       <c r="Q115" s="19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R115" s="19">
         <v>19</v>
@@ -10436,22 +10436,22 @@
         <v>143</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="19" t="s">
         <v>634</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" s="19" t="s">
+      <c r="E116" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="E116" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>636</v>
-      </c>
       <c r="G116" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>59</v>
@@ -10487,7 +10487,7 @@
         <v>5</v>
       </c>
       <c r="Q116" s="19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R116" s="19" t="s">
         <v>11</v>
@@ -10498,22 +10498,22 @@
         <v>144</v>
       </c>
       <c r="B117" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E117" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>17</v>
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="Q117" s="19" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="R117" s="19" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
@@ -10560,22 +10560,22 @@
         <v>145</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E118" s="20" t="s">
         <v>11</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H118" t="s">
         <v>12</v>
@@ -10592,29 +10592,29 @@
         <v>302</v>
       </c>
       <c r="L118" s="7">
-        <f t="shared" ref="L118:L119" si="16">IF(E118="-",0,1)+IF(D118="-",0,2)</f>
+        <f t="shared" ref="L118" si="16">IF(E118="-",0,1)+IF(D118="-",0,2)</f>
         <v>2</v>
       </c>
       <c r="M118" s="7">
         <v>4</v>
       </c>
       <c r="N118" s="7">
-        <f t="shared" ref="N118:N119" si="17">IF(D118="-",0,LEN(D118)-LEN(SUBSTITUTE(D118,";",""))+1)</f>
+        <f t="shared" ref="N118" si="17">IF(D118="-",0,LEN(D118)-LEN(SUBSTITUTE(D118,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="O118" s="7">
-        <f t="shared" ref="O118:O119" si="18">IF(E118="-",0,LEN(E118)-LEN(SUBSTITUTE(E118,";",""))+1)</f>
+        <f t="shared" ref="O118" si="18">IF(E118="-",0,LEN(E118)-LEN(SUBSTITUTE(E118,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="P118" s="7">
-        <f t="shared" ref="P118:P119" si="19">SUM(N118:O118)</f>
+        <f t="shared" ref="P118" si="19">SUM(N118:O118)</f>
         <v>1</v>
       </c>
       <c r="Q118" s="19" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="R118" s="19" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -10622,22 +10622,22 @@
         <v>146</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D119" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -10665,18 +10665,18 @@
         <v>5</v>
       </c>
       <c r="O119" s="7">
-        <f t="shared" ref="O119:O122" si="22">IF(E119="-",0,LEN(E119)-LEN(SUBSTITUTE(E119,";",""))+1)</f>
+        <f t="shared" ref="O119:O121" si="22">IF(E119="-",0,LEN(E119)-LEN(SUBSTITUTE(E119,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="P119" s="7">
-        <f t="shared" ref="P119:P122" si="23">SUM(N119:O119)</f>
+        <f t="shared" ref="P119:P121" si="23">SUM(N119:O119)</f>
         <v>6</v>
       </c>
       <c r="Q119" s="19" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="R119" s="19" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
@@ -10684,22 +10684,22 @@
         <v>147</v>
       </c>
       <c r="B120" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" s="17" t="s">
-        <v>649</v>
-      </c>
-      <c r="E120" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>648</v>
-      </c>
       <c r="G120" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>17</v>
@@ -10735,10 +10735,10 @@
         <v>1</v>
       </c>
       <c r="Q120" s="19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R120" s="19" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
@@ -10746,22 +10746,22 @@
         <v>148</v>
       </c>
       <c r="B121" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="D121" t="s">
+        <v>686</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="F121" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="D121" t="s">
-        <v>688</v>
-      </c>
-      <c r="E121" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>654</v>
-      </c>
       <c r="G121" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>12</v>
@@ -10778,14 +10778,14 @@
         <v>302</v>
       </c>
       <c r="L121" s="7">
-        <f t="shared" ref="L121:L122" si="26">IF(E121="-",0,1)+IF(D121="-",0,2)</f>
+        <f t="shared" ref="L121" si="26">IF(E121="-",0,1)+IF(D121="-",0,2)</f>
         <v>3</v>
       </c>
       <c r="M121" s="7">
         <v>7</v>
       </c>
       <c r="N121" s="7">
-        <f t="shared" ref="N121:N122" si="27">IF(D121="-",0,LEN(D121)-LEN(SUBSTITUTE(D121,";",""))+1)</f>
+        <f t="shared" ref="N121" si="27">IF(D121="-",0,LEN(D121)-LEN(SUBSTITUTE(D121,";",""))+1)</f>
         <v>10</v>
       </c>
       <c r="O121" s="7">
@@ -10800,7 +10800,7 @@
         <v>136</v>
       </c>
       <c r="R121" s="19" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
@@ -10808,22 +10808,22 @@
         <v>149</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>23</v>
@@ -10840,7 +10840,7 @@
         <v>304</v>
       </c>
       <c r="L122" s="7">
-        <f t="shared" ref="L122:L123" si="28">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
+        <f t="shared" ref="L122" si="28">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
         <v>3</v>
       </c>
       <c r="M122" s="7">
@@ -10851,7 +10851,7 @@
         <v>2</v>
       </c>
       <c r="O122" s="7">
-        <f t="shared" ref="O122:O123" si="30">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
+        <f t="shared" ref="O122" si="30">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="P122" s="7">
@@ -10862,7 +10862,7 @@
         <v>136</v>
       </c>
       <c r="R122" s="19" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
@@ -10870,25 +10870,25 @@
         <v>150</v>
       </c>
       <c r="B123" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="C123" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>680</v>
-      </c>
-      <c r="E123" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>681</v>
-      </c>
       <c r="G123" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H123" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I123" s="7">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -10902,7 +10902,7 @@
         <v>313</v>
       </c>
       <c r="L123" s="7">
-        <f t="shared" ref="L123:L124" si="32">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
+        <f t="shared" ref="L123" si="32">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
         <v>2</v>
       </c>
       <c r="M123" s="7">
@@ -10913,7 +10913,7 @@
         <v>2</v>
       </c>
       <c r="O123" s="7">
-        <f t="shared" ref="O123:O124" si="34">IF(E123="-",0,LEN(E123)-LEN(SUBSTITUTE(E123,";",""))+1)</f>
+        <f t="shared" ref="O123" si="34">IF(E123="-",0,LEN(E123)-LEN(SUBSTITUTE(E123,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="P123" s="7">
@@ -10924,7 +10924,7 @@
         <v>136</v>
       </c>
       <c r="R123" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="124" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -10932,22 +10932,22 @@
         <v>151</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>17</v>
@@ -10964,22 +10964,22 @@
         <v>327</v>
       </c>
       <c r="L124" s="7">
-        <f t="shared" ref="L124:L125" si="36">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
+        <f t="shared" ref="L124" si="36">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M124" s="7">
         <v>10</v>
       </c>
       <c r="N124" s="7">
-        <f t="shared" ref="N124:N125" si="37">IF(D124="-",0,LEN(D124)-LEN(SUBSTITUTE(D124,";",""))+1)</f>
+        <f t="shared" ref="N124" si="37">IF(D124="-",0,LEN(D124)-LEN(SUBSTITUTE(D124,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="O124" s="7">
-        <f t="shared" ref="O124:O125" si="38">IF(E124="-",0,LEN(E124)-LEN(SUBSTITUTE(E124,";",""))+1)</f>
+        <f t="shared" ref="O124" si="38">IF(E124="-",0,LEN(E124)-LEN(SUBSTITUTE(E124,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="P124" s="7">
-        <f t="shared" ref="P124:P125" si="39">SUM(N124:O124)</f>
+        <f t="shared" ref="P124" si="39">SUM(N124:O124)</f>
         <v>1</v>
       </c>
       <c r="Q124" s="19" t="s">
@@ -10994,7 +10994,7 @@
         <v>152</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>11</v>
@@ -11003,16 +11003,16 @@
         <v>11</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G125" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H125" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I125" s="7">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -11056,25 +11056,25 @@
         <v>153</v>
       </c>
       <c r="B126" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="F126" t="s">
         <v>710</v>
       </c>
-      <c r="C126" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="20" t="s">
-        <v>703</v>
-      </c>
-      <c r="F126" t="s">
-        <v>712</v>
-      </c>
       <c r="G126" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H126" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I126" s="7">
         <f>VLOOKUP(H126,cardsort_group_IDs!A:B,2,0)</f>
@@ -11110,7 +11110,7 @@
         <v>136</v>
       </c>
       <c r="R126" s="19" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
@@ -11118,7 +11118,7 @@
         <v>154</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>11</v>
@@ -11127,16 +11127,16 @@
         <v>11</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G127" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H127" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="I127" s="7">
         <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
@@ -11172,7 +11172,7 @@
         <v>136</v>
       </c>
       <c r="R127" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
@@ -11268,54 +11268,54 @@
   <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B112:B116 B119:B1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="41"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
     <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F81">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J35">
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
     <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
     <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J106">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B112:B116 B119:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11448,10 +11448,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -11514,10 +11514,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C17" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -11657,7 +11657,7 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>368</v>
@@ -11800,7 +11800,7 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>393</v>
@@ -11811,7 +11811,7 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>394</v>
@@ -11844,10 +11844,10 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C47" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -11869,7 +11869,7 @@
         <v>399</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -12064,7 +12064,7 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>431</v>
@@ -12097,10 +12097,10 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C70" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -12207,7 +12207,7 @@
         <v>502</v>
       </c>
       <c r="B80" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>383</v>
@@ -12229,7 +12229,7 @@
         <v>504</v>
       </c>
       <c r="B82" t="s">
-        <v>505</v>
+        <v>717</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>383</v>
@@ -12237,10 +12237,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="B83" t="s">
         <v>506</v>
-      </c>
-      <c r="B83" t="s">
-        <v>507</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>383</v>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="B84" t="s">
         <v>508</v>
-      </c>
-      <c r="B84" t="s">
-        <v>509</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>383</v>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B85" t="s">
         <v>266</v>
@@ -12270,10 +12270,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="B86" t="s">
         <v>511</v>
-      </c>
-      <c r="B86" t="s">
-        <v>512</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>383</v>
@@ -12281,10 +12281,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="B87" t="s">
         <v>513</v>
-      </c>
-      <c r="B87" t="s">
-        <v>514</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>383</v>
@@ -12292,10 +12292,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="B88" t="s">
         <v>515</v>
-      </c>
-      <c r="B88" t="s">
-        <v>516</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>383</v>
@@ -12303,10 +12303,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="B89" t="s">
         <v>517</v>
-      </c>
-      <c r="B89" t="s">
-        <v>518</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>383</v>
@@ -12314,10 +12314,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="B90" t="s">
         <v>519</v>
-      </c>
-      <c r="B90" t="s">
-        <v>520</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>383</v>
@@ -12325,10 +12325,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B91" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>385</v>
@@ -12336,7 +12336,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B92" t="s">
         <v>381</v>
@@ -12347,7 +12347,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B93" t="s">
         <v>503</v>
@@ -12369,7 +12369,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s">
         <v>381</v>
@@ -12380,7 +12380,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B96" t="s">
         <v>266</v>
@@ -12391,7 +12391,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B97" t="s">
         <v>381</v>
@@ -12526,7 +12526,7 @@
         <v>445</v>
       </c>
       <c r="B109" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>425</v>
@@ -12537,7 +12537,7 @@
         <v>446</v>
       </c>
       <c r="B110" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>425</v>
@@ -12567,7 +12567,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B113" t="s">
         <v>381</v>
@@ -12578,7 +12578,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B114" t="s">
         <v>381</v>
@@ -12589,233 +12589,233 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="B115" t="s">
         <v>590</v>
       </c>
-      <c r="B115" t="s">
-        <v>591</v>
-      </c>
       <c r="C115" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B116" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C116" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B117" t="s">
         <v>381</v>
       </c>
       <c r="C117" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B118" t="s">
         <v>488</v>
       </c>
       <c r="C118" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B119" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C119" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B120" t="s">
         <v>224</v>
       </c>
       <c r="C120" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B121" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C121" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B122" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C122" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B123" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C123" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B124" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C124" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B125" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C125" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B126" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C126" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B127" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C127" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B128" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C128" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B129" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C129" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B130" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C130" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B131" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C131" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="B132" t="s">
         <v>649</v>
       </c>
-      <c r="B132" t="s">
-        <v>650</v>
-      </c>
       <c r="C132" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B133" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C133" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B134" t="s">
         <v>396</v>
       </c>
       <c r="C134" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
+        <v>701</v>
+      </c>
+      <c r="B135" t="s">
         <v>703</v>
       </c>
-      <c r="B135" t="s">
-        <v>705</v>
-      </c>
       <c r="C135" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -12854,7 +12854,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B3">
         <v>203</v>

--- a/metrics and parser/final_list_of_metrics.xlsx
+++ b/metrics and parser/final_list_of_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509E3C2A-ACD3-4F70-9817-43A77781F806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2BBA4F-4B4F-4DD1-8CE8-5CBF8DBF1DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="562" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="376" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -46,37 +46,23 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={2443806D-D89D-4F46-8BFE-38F000C63452}</author>
     <author>tc={5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}</author>
-    <author>tc={738F5169-58A9-48F4-8196-48D2F743B5DF}</author>
-    <author>tc={B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}</author>
     <author>tc={E017DF4E-5656-4CEF-B774-80BA936A6D56}</author>
     <author>tc={8A92D669-9E50-4C59-82E5-97B139270D19}</author>
     <author>tc={121DA4BD-014E-470E-AB44-B9514592A80F}</author>
     <author>tc={41A1A9E9-8671-443A-BC53-E9E6789FC6B2}</author>
-    <author>tc={EF886BF9-B28D-42E1-9B64-C8A7E72E082A}</author>
     <author>tc={7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}</author>
     <author>tc={917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}</author>
     <author>tc={FDDDF671-A2B6-4958-A032-5551C66219BE}</author>
     <author>tc={9ABBA003-3752-4178-8927-349ABCC5DB99}</author>
-    <author>tc={80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}</author>
     <author>tc={45640671-D7E4-4EA6-9099-D4E52C010FD7}</author>
-    <author>tc={EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}</author>
     <author>tc={C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}</author>
     <author>tc={FCC3DA67-C366-4123-AE95-236C8FC56568}</author>
     <author>tc={24A13EBD-8030-4299-B820-E3DBAA902DCC}</author>
     <author>tc={65177E12-2939-4BCC-8B47-DB95E81C94F5}</author>
   </authors>
   <commentList>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{2443806D-D89D-4F46-8BFE-38F000C63452}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von „Coding“ zu „Produced Code“ geändert</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="1" shapeId="0" xr:uid="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,23 +70,7 @@
     Nach Andres Input zusammengefasst zu einem Eintrag.</t>
       </text>
     </comment>
-    <comment ref="H28" authorId="2" shapeId="0" xr:uid="{738F5169-58A9-48F4-8196-48D2F743B5DF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von Business zu Process verschoben.</t>
-      </text>
-    </comment>
-    <comment ref="B29" authorId="3" shapeId="0" xr:uid="{B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Umbenannt von „Developer Build Time“ to  „Local Build Time“ nach Andres Input.</t>
-      </text>
-    </comment>
-    <comment ref="C29" authorId="4" shapeId="0" xr:uid="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
+    <comment ref="C29" authorId="1" shapeId="0" xr:uid="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -110,7 +80,7 @@
     „Application/Package Build Duration“ von Lattice nach Andres Input ergänzt.</t>
       </text>
     </comment>
-    <comment ref="D29" authorId="5" shapeId="0" xr:uid="{8A92D669-9E50-4C59-82E5-97B139270D19}">
+    <comment ref="D29" authorId="2" shapeId="0" xr:uid="{8A92D669-9E50-4C59-82E5-97B139270D19}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -118,7 +88,7 @@
     Lattice von NextJS Page Compilation Duration</t>
       </text>
     </comment>
-    <comment ref="H34" authorId="6" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
+    <comment ref="H34" authorId="3" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -126,7 +96,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="C52" authorId="7" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
+    <comment ref="C52" authorId="4" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -134,15 +104,7 @@
     „Time to Restore Services“ ergänzt nach Andres Input.</t>
       </text>
     </comment>
-    <comment ref="B54" authorId="8" shapeId="0" xr:uid="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Name gekürzt nach Andres Input.</t>
-      </text>
-    </comment>
-    <comment ref="H58" authorId="9" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
+    <comment ref="H58" authorId="5" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -150,7 +112,7 @@
     Nach Andres Input von DevEx zu Business/HR gewechselt.</t>
       </text>
     </comment>
-    <comment ref="H61" authorId="10" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
+    <comment ref="H61" authorId="6" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -158,7 +120,7 @@
     Nach Andres Input von Business zu Quality verschoben.</t>
       </text>
     </comment>
-    <comment ref="J69" authorId="11" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
+    <comment ref="J69" authorId="7" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -166,7 +128,7 @@
     Von Knowledge Expansion zu Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="C76" authorId="12" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
+    <comment ref="C76" authorId="8" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -174,15 +136,7 @@
     Nach Andres Kommentar zu einer Metrik zusammengefasst.</t>
       </text>
     </comment>
-    <comment ref="B77" authorId="13" shapeId="0" xr:uid="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Name angepasst nach Andres Input. Ursprünglich „Quality of Reviews of Work Contributed by Team Members“</t>
-      </text>
-    </comment>
-    <comment ref="C80" authorId="14" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
+    <comment ref="C80" authorId="9" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -190,15 +144,7 @@
     Nach Andres Input Availability hinzugefügt.</t>
       </text>
     </comment>
-    <comment ref="H85" authorId="15" shapeId="0" xr:uid="{EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von Business zu Process verschoben.</t>
-      </text>
-    </comment>
-    <comment ref="C90" authorId="16" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
+    <comment ref="C90" authorId="10" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -206,7 +152,7 @@
     Nach Andres Input. Production Incidents und System Uptime / Availability hinzugefügt.</t>
       </text>
     </comment>
-    <comment ref="F90" authorId="17" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
+    <comment ref="F90" authorId="11" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -214,7 +160,7 @@
     Nach Andres Input angepasst.</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="18" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
+    <comment ref="H91" authorId="12" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -222,7 +168,7 @@
     Nach Andres Anregung von Business zu DevEx/Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="19" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
+    <comment ref="C92" authorId="13" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -235,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="735">
   <si>
     <t>id</t>
   </si>
@@ -710,9 +656,6 @@
     <t>When bottlenecks and inefficiencies are discovered (as informed by industry benchmarks), effective teams set data-backed goals against them (in addition to automated workflows). Regularly attaining these goals indicates both developer effectiveness and a good developer experience.</t>
   </si>
   <si>
-    <t>Connection Graph</t>
-  </si>
-  <si>
     <t>Network metrics that show who is connected to whom and how.</t>
   </si>
   <si>
@@ -2430,6 +2373,21 @@
   </si>
   <si>
     <t>140</t>
+  </si>
+  <si>
+    <t>Outcome Goals</t>
+  </si>
+  <si>
+    <t>Developer Experience</t>
+  </si>
+  <si>
+    <t>Organizational Effectiveness</t>
+  </si>
+  <si>
+    <t>Product Excellence</t>
+  </si>
+  <si>
+    <t>Communication Network Density</t>
   </si>
 </sst>
 </file>
@@ -2518,7 +2476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2583,6 +2541,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2595,16 +2556,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2650,6 +2601,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2670,21 +2631,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2770,21 +2731,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3260,17 +3221,8 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B15" dT="2025-05-23T08:50:23.62" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{2443806D-D89D-4F46-8BFE-38F000C63452}">
-    <text>Nach Andres Input von „Coding“ zu „Produced Code“ geändert</text>
-  </threadedComment>
   <threadedComment ref="C15" dT="2025-05-23T08:51:40.12" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
     <text>Nach Andres Input zusammengefasst zu einem Eintrag.</text>
-  </threadedComment>
-  <threadedComment ref="H28" dT="2025-06-02T18:38:57.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{738F5169-58A9-48F4-8196-48D2F743B5DF}">
-    <text>Nach Andres Input von Business zu Process verschoben.</text>
-  </threadedComment>
-  <threadedComment ref="B29" dT="2025-05-23T09:36:06.75" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{B51E8FD0-2567-4557-B58E-1C6A56D9BFA3}">
-    <text>Umbenannt von „Developer Build Time“ to  „Local Build Time“ nach Andres Input.</text>
   </threadedComment>
   <threadedComment ref="C29" dT="2025-05-23T09:38:31.42" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
     <text xml:space="preserve">„NextJS Page Compilation Duration“ ergänzt nach Andres Input.
@@ -3288,9 +3240,6 @@
   <threadedComment ref="C52" dT="2025-05-23T09:31:57.03" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
     <text>„Time to Restore Services“ ergänzt nach Andres Input.</text>
   </threadedComment>
-  <threadedComment ref="B54" dT="2025-05-23T09:06:49.45" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{EF886BF9-B28D-42E1-9B64-C8A7E72E082A}">
-    <text>Name gekürzt nach Andres Input.</text>
-  </threadedComment>
   <threadedComment ref="H58" dT="2025-06-03T11:52:12.80" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
     <text>Nach Andres Input von DevEx zu Business/HR gewechselt.</text>
   </threadedComment>
@@ -3303,14 +3252,8 @@
   <threadedComment ref="C76" dT="2025-06-02T18:24:12.03" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
     <text>Nach Andres Kommentar zu einer Metrik zusammengefasst.</text>
   </threadedComment>
-  <threadedComment ref="B77" dT="2025-05-23T09:24:06.88" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{80D5B2BD-D0F6-4AB8-8017-59A06F6C1C9C}">
-    <text>Name angepasst nach Andres Input. Ursprünglich „Quality of Reviews of Work Contributed by Team Members“</text>
-  </threadedComment>
   <threadedComment ref="C80" dT="2025-06-03T12:09:36.50" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
     <text>Nach Andres Input Availability hinzugefügt.</text>
-  </threadedComment>
-  <threadedComment ref="H85" dT="2025-06-02T18:38:57.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{EB733AEE-2F18-46F9-8A7B-0CA9B6B32FFC}">
-    <text>Nach Andres Input von Business zu Process verschoben.</text>
   </threadedComment>
   <threadedComment ref="C90" dT="2025-06-03T12:08:14.41" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
     <text>Nach Andres Input. Production Incidents und System Uptime / Availability hinzugefügt.</text>
@@ -3329,7 +3272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q141"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="7"/>
@@ -3344,11 +3287,12 @@
     <col min="13" max="13" width="28.42578125" style="9" customWidth="1"/>
     <col min="14" max="15" width="9.140625" style="7"/>
     <col min="16" max="16" width="18.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="7"/>
+    <col min="17" max="17" width="30.7109375" style="19" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3359,10 +3303,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>271</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>272</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3386,22 +3330,25 @@
         <v>9</v>
       </c>
       <c r="M1" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P1" s="22" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3412,16 +3359,16 @@
         <v>14</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>16</v>
@@ -3454,13 +3401,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="19" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>4</v>
       </c>
@@ -3480,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>22</v>
@@ -3513,13 +3463,16 @@
         <v>1</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q3" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>7</v>
       </c>
@@ -3527,22 +3480,22 @@
         <v>24</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3572,13 +3525,16 @@
         <v>8</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q4" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>9</v>
       </c>
@@ -3589,16 +3545,16 @@
         <v>10</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>16</v>
@@ -3631,13 +3587,16 @@
         <v>3</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>10</v>
       </c>
@@ -3645,22 +3604,22 @@
         <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3690,13 +3649,16 @@
         <v>4</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R6" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>11</v>
       </c>
@@ -3716,7 +3678,7 @@
         <v>34</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>11</v>
@@ -3749,13 +3711,16 @@
         <v>1</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>12</v>
       </c>
@@ -3766,16 +3731,16 @@
         <v>10</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>37</v>
@@ -3810,11 +3775,14 @@
       <c r="P8" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q8" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+      <c r="Q8" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R8" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>13</v>
       </c>
@@ -3834,7 +3802,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>37</v>
@@ -3867,13 +3835,16 @@
         <v>1</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>14</v>
       </c>
@@ -3884,7 +3855,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E10" s="20">
         <v>501</v>
@@ -3893,7 +3864,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>37</v>
@@ -3926,13 +3897,16 @@
         <v>2</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="150" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>15</v>
       </c>
@@ -3943,7 +3917,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E11" s="20">
         <v>501</v>
@@ -3952,7 +3926,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>16</v>
@@ -3985,13 +3959,16 @@
         <v>3</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>16</v>
       </c>
@@ -4002,16 +3979,16 @@
         <v>10</v>
       </c>
       <c r="D12" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>452</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>453</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>48</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>37</v>
@@ -4044,13 +4021,16 @@
         <v>6</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>17</v>
       </c>
@@ -4061,16 +4041,16 @@
         <v>51</v>
       </c>
       <c r="D13" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>545</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>546</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>53</v>
@@ -4103,13 +4083,16 @@
         <v>8</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R13" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>18</v>
       </c>
@@ -4117,10 +4100,10 @@
         <v>54</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>679</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>680</v>
       </c>
       <c r="E14" s="20">
         <v>131</v>
@@ -4129,7 +4112,7 @@
         <v>55</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>37</v>
@@ -4164,11 +4147,14 @@
       <c r="P14" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q14" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q14" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R14" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>19</v>
       </c>
@@ -4176,19 +4162,19 @@
         <v>56</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>57</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>58</v>
@@ -4221,13 +4207,16 @@
         <v>26</v>
       </c>
       <c r="P15" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q15" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q15" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R15" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>20</v>
       </c>
@@ -4235,22 +4224,22 @@
         <v>60</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="G16" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
@@ -4282,11 +4271,14 @@
       <c r="P16" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q16" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q16" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R16" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>22</v>
       </c>
@@ -4297,16 +4289,16 @@
         <v>10</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>16</v>
@@ -4339,13 +4331,16 @@
         <v>3</v>
       </c>
       <c r="P17" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q17" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R17" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>23</v>
       </c>
@@ -4353,19 +4348,19 @@
         <v>66</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>53</v>
@@ -4398,13 +4393,16 @@
         <v>2</v>
       </c>
       <c r="P18" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="150" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R18" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>24</v>
       </c>
@@ -4424,7 +4422,7 @@
         <v>72</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>11</v>
@@ -4457,13 +4455,16 @@
         <v>1</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q19" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q19" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R19" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>25</v>
       </c>
@@ -4477,13 +4478,13 @@
         <v>10</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>76</v>
@@ -4516,13 +4517,16 @@
         <v>3</v>
       </c>
       <c r="P20" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q20" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q20" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R20" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>26</v>
       </c>
@@ -4533,7 +4537,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E21" s="20">
         <v>131</v>
@@ -4542,7 +4546,7 @@
         <v>78</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>76</v>
@@ -4575,13 +4579,16 @@
         <v>3</v>
       </c>
       <c r="P21" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q21" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q21" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R21" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>27</v>
       </c>
@@ -4589,19 +4596,19 @@
         <v>29</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>657</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>658</v>
-      </c>
       <c r="E22" s="20" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>79</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>16</v>
@@ -4636,11 +4643,14 @@
       <c r="P22" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q22" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q22" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R22" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>28</v>
       </c>
@@ -4651,7 +4661,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E23" s="20">
         <v>501</v>
@@ -4660,10 +4670,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I23" s="7">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4693,13 +4703,16 @@
         <v>2</v>
       </c>
       <c r="P23" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q23" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q23" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R23" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>29</v>
       </c>
@@ -4707,7 +4720,7 @@
         <v>83</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>10</v>
@@ -4719,7 +4732,7 @@
         <v>84</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>37</v>
@@ -4752,13 +4765,16 @@
         <v>1</v>
       </c>
       <c r="P24" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q24" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q24" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R24" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>30</v>
       </c>
@@ -4769,16 +4785,16 @@
         <v>10</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>86</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>76</v>
@@ -4813,11 +4829,14 @@
       <c r="P25" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q25" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q25" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>31</v>
       </c>
@@ -4825,19 +4844,19 @@
         <v>87</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D26" s="19">
         <v>170</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>88</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>37</v>
@@ -4870,13 +4889,16 @@
         <v>4</v>
       </c>
       <c r="P26" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q26" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q26" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R26" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>32</v>
       </c>
@@ -4887,7 +4909,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E27" s="20">
         <v>501</v>
@@ -4896,7 +4918,7 @@
         <v>92</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>76</v>
@@ -4929,13 +4951,16 @@
         <v>2</v>
       </c>
       <c r="P27" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q27" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q27" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>33</v>
       </c>
@@ -4946,16 +4971,16 @@
         <v>10</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>16</v>
@@ -4988,13 +5013,16 @@
         <v>3</v>
       </c>
       <c r="P28" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q28" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q28" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R28" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>34</v>
       </c>
@@ -5002,19 +5030,19 @@
         <v>96</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D29" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>547</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>548</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>22</v>
@@ -5047,13 +5075,16 @@
         <v>8</v>
       </c>
       <c r="P29" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q29" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q29" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R29" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>35</v>
       </c>
@@ -5064,19 +5095,19 @@
         <v>10</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>99</v>
       </c>
       <c r="G30" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I30" s="7">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
@@ -5106,13 +5137,16 @@
         <v>3</v>
       </c>
       <c r="P30" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q30" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="180" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q30" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R30" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="180" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>36</v>
       </c>
@@ -5120,22 +5154,22 @@
         <v>101</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>102</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I31" s="7">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
@@ -5167,11 +5201,14 @@
       <c r="P31" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q31" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="255" x14ac:dyDescent="0.25">
+      <c r="Q31" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R31" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="255" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>37</v>
       </c>
@@ -5191,7 +5228,7 @@
         <v>105</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>11</v>
@@ -5224,13 +5261,16 @@
         <v>1</v>
       </c>
       <c r="P32" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q32" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="135" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q32" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R32" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>38</v>
       </c>
@@ -5238,19 +5278,19 @@
         <v>106</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>107</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>16</v>
@@ -5285,11 +5325,14 @@
       <c r="P33" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q33" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q33" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R33" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>39</v>
       </c>
@@ -5300,16 +5343,16 @@
         <v>10</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>109</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>16</v>
@@ -5342,13 +5385,16 @@
         <v>3</v>
       </c>
       <c r="P34" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q34" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R34" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>40</v>
       </c>
@@ -5359,19 +5405,19 @@
         <v>110</v>
       </c>
       <c r="D35" s="20" t="s">
+        <v>536</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>537</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>538</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I35" s="7">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5403,11 +5449,14 @@
       <c r="P35" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q35" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q35" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R35" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>41</v>
       </c>
@@ -5415,22 +5464,22 @@
         <v>112</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>113</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I36" s="7">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5460,13 +5509,16 @@
         <v>6</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q36" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q36" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R36" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>42</v>
       </c>
@@ -5474,19 +5526,19 @@
         <v>114</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>115</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>37</v>
@@ -5519,13 +5571,16 @@
         <v>2</v>
       </c>
       <c r="P37" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q37" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q37" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R37" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>43</v>
       </c>
@@ -5536,19 +5591,19 @@
         <v>10</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>117</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I38" s="7">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
@@ -5578,13 +5633,16 @@
         <v>3</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q38" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q38" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R38" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>44</v>
       </c>
@@ -5592,19 +5650,19 @@
         <v>119</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>22</v>
@@ -5639,11 +5697,14 @@
       <c r="P39" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q39" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q39" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R39" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>45</v>
       </c>
@@ -5657,13 +5718,13 @@
         <v>10</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>124</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>22</v>
@@ -5696,13 +5757,16 @@
         <v>2</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q40" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q40" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R40" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>46</v>
       </c>
@@ -5716,13 +5780,13 @@
         <v>10</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>127</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>53</v>
@@ -5757,11 +5821,14 @@
       <c r="P41" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q41" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q41" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R41" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>50</v>
       </c>
@@ -5775,16 +5842,16 @@
         <v>10</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>130</v>
       </c>
       <c r="G42" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I42" s="7">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5814,13 +5881,16 @@
         <v>2</v>
       </c>
       <c r="P42" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q42" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q42" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R42" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>51</v>
       </c>
@@ -5840,7 +5910,7 @@
         <v>132</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>16</v>
@@ -5873,13 +5943,16 @@
         <v>1</v>
       </c>
       <c r="P43" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q43" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q43" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R43" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>54</v>
       </c>
@@ -5899,7 +5972,7 @@
         <v>134</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>16</v>
@@ -5932,13 +6005,16 @@
         <v>1</v>
       </c>
       <c r="P44" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q44" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="135" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q44" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R44" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>56</v>
       </c>
@@ -5946,22 +6022,22 @@
         <v>135</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>136</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I45" s="7">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -5991,13 +6067,16 @@
         <v>4</v>
       </c>
       <c r="P45" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q45" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q45" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R45" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>57</v>
       </c>
@@ -6017,7 +6096,7 @@
         <v>139</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>11</v>
@@ -6050,13 +6129,16 @@
         <v>1</v>
       </c>
       <c r="P46" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q46" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="360" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q46" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R46" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="360" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>58</v>
       </c>
@@ -6064,22 +6146,22 @@
         <v>140</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>141</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I47" s="7">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
@@ -6111,11 +6193,14 @@
       <c r="P47" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q47" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q47" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R47" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>59</v>
       </c>
@@ -6123,22 +6208,22 @@
         <v>142</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>143</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I48" s="7">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -6170,11 +6255,14 @@
       <c r="P48" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q48" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q48" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R48" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>62</v>
       </c>
@@ -6185,16 +6273,16 @@
         <v>146</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>147</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>16</v>
@@ -6227,13 +6315,16 @@
         <v>11</v>
       </c>
       <c r="P49" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q49" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q49" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R49" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>63</v>
       </c>
@@ -6241,19 +6332,19 @@
         <v>148</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>150</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>37</v>
@@ -6288,11 +6379,14 @@
       <c r="P50" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q50" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q50" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R50" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>64</v>
       </c>
@@ -6312,7 +6406,7 @@
         <v>152</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>22</v>
@@ -6345,13 +6439,16 @@
         <v>1</v>
       </c>
       <c r="P51" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q51" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="150" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q51" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R51" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>65</v>
       </c>
@@ -6359,19 +6456,19 @@
         <v>153</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>154</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>22</v>
@@ -6404,13 +6501,16 @@
         <v>16</v>
       </c>
       <c r="P52" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q52" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q52" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R52" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>66</v>
       </c>
@@ -6418,7 +6518,7 @@
         <v>155</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>10</v>
@@ -6430,7 +6530,7 @@
         <v>156</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>53</v>
@@ -6463,33 +6563,36 @@
         <v>1</v>
       </c>
       <c r="P53" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q53" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q53" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R53" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>67</v>
       </c>
       <c r="B54" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="G54" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>53</v>
@@ -6522,33 +6625,36 @@
         <v>3</v>
       </c>
       <c r="P54" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q54" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q54" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R54" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>69</v>
       </c>
       <c r="B55" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>450</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>160</v>
-      </c>
       <c r="G55" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>76</v>
@@ -6581,33 +6687,36 @@
         <v>3</v>
       </c>
       <c r="P55" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q55" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q55" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R55" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>70</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>162</v>
-      </c>
       <c r="G56" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>37</v>
@@ -6640,33 +6749,36 @@
         <v>2</v>
       </c>
       <c r="P56" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q56" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q56" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R56" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>71</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="G57" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>16</v>
@@ -6699,33 +6811,36 @@
         <v>3</v>
       </c>
       <c r="P57" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q57" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q57" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R57" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>72</v>
       </c>
       <c r="B58" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>166</v>
-      </c>
       <c r="G58" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>11</v>
@@ -6735,7 +6850,7 @@
         <v>201</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K58" s="7">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6758,33 +6873,36 @@
         <v>3</v>
       </c>
       <c r="P58" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q58" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q58" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R58" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>73</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>169</v>
-      </c>
       <c r="G59" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>22</v>
@@ -6794,7 +6912,7 @@
         <v>202</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K59" s="7">
         <f>VLOOKUP(J59,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6817,18 +6935,21 @@
         <v>3</v>
       </c>
       <c r="P59" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q59" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q59" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R59" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>74</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>10</v>
@@ -6840,10 +6961,10 @@
         <v>183</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>11</v>
@@ -6876,33 +6997,36 @@
         <v>1</v>
       </c>
       <c r="P60" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q60" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q60" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R60" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>75</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E61" s="20">
         <v>183</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>37</v>
@@ -6935,33 +7059,36 @@
         <v>2</v>
       </c>
       <c r="P61" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q61" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q61" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R61" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>76</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>176</v>
-      </c>
       <c r="G62" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>11</v>
@@ -6994,36 +7121,39 @@
         <v>2</v>
       </c>
       <c r="P62" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q62" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q62" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R62" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>77</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="G63" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I63" s="7">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -7053,36 +7183,39 @@
         <v>3</v>
       </c>
       <c r="P63" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q63" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q63" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R63" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>78</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="19" t="s">
-        <v>673</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>181</v>
-      </c>
       <c r="G64" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I64" s="7">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
@@ -7114,31 +7247,34 @@
       <c r="P64" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q64" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q64" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R64" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>79</v>
       </c>
       <c r="B65" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>183</v>
-      </c>
       <c r="G65" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>76</v>
@@ -7173,16 +7309,19 @@
       <c r="P65" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q65" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+      <c r="Q65" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R65" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>80</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>10</v>
@@ -7194,10 +7333,10 @@
         <v>509</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>76</v>
@@ -7230,33 +7369,36 @@
         <v>1</v>
       </c>
       <c r="P66" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q66" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q66" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R66" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>81</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E67" s="20">
         <v>202</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>37</v>
@@ -7289,18 +7431,21 @@
         <v>2</v>
       </c>
       <c r="P67" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q67" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q67" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R67" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>82</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>10</v>
@@ -7312,10 +7457,10 @@
         <v>509</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>11</v>
@@ -7325,7 +7470,7 @@
         <v>201</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K68" s="7">
         <f>VLOOKUP(J68,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7348,36 +7493,39 @@
         <v>1</v>
       </c>
       <c r="P68" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q68" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q68" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R68" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>83</v>
       </c>
       <c r="B69" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>666</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>667</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>191</v>
-      </c>
       <c r="G69" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I69" s="7">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
@@ -7409,11 +7557,14 @@
       <c r="P69" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q69" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q69" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R69" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>84</v>
       </c>
@@ -7424,16 +7575,16 @@
         <v>10</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E70" s="20">
         <v>501</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>22</v>
@@ -7466,33 +7617,36 @@
         <v>2</v>
       </c>
       <c r="P70" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q70" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q70" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R70" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>85</v>
       </c>
       <c r="B71" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>194</v>
-      </c>
       <c r="G71" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>16</v>
@@ -7525,33 +7679,36 @@
         <v>1</v>
       </c>
       <c r="P71" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q71" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="135" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q71" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R71" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>87</v>
       </c>
       <c r="B72" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="G72" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>16</v>
@@ -7584,33 +7741,36 @@
         <v>3</v>
       </c>
       <c r="P72" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q72" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q72" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R72" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>88</v>
       </c>
       <c r="B73" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D73" s="17" t="s">
-        <v>535</v>
-      </c>
-      <c r="E73" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>198</v>
-      </c>
       <c r="G73" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>37</v>
@@ -7643,33 +7803,36 @@
         <v>3</v>
       </c>
       <c r="P73" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q73" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q73" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R73" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>89</v>
       </c>
       <c r="B74" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>200</v>
-      </c>
       <c r="G74" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>37</v>
@@ -7702,33 +7865,36 @@
         <v>4</v>
       </c>
       <c r="P74" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q74" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q74" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R74" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>90</v>
       </c>
       <c r="B75" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>659</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="F75" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>660</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>692</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="G75" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>37</v>
@@ -7763,31 +7929,34 @@
       <c r="P75" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q75" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q75" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R75" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>91</v>
       </c>
       <c r="B76" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="E76" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="G76" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>16</v>
@@ -7820,33 +7989,36 @@
         <v>4</v>
       </c>
       <c r="P76" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q76" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q76" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R76" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>92</v>
       </c>
       <c r="B77" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F77" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E77" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>206</v>
-      </c>
       <c r="G77" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>53</v>
@@ -7879,18 +8051,21 @@
         <v>3</v>
       </c>
       <c r="P77" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q77" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q77" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R77" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>93</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>10</v>
@@ -7902,10 +8077,10 @@
         <v>509</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>11</v>
@@ -7938,33 +8113,36 @@
         <v>1</v>
       </c>
       <c r="P78" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q78" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q78" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R78" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>94</v>
       </c>
       <c r="B79" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="E79" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>210</v>
-      </c>
       <c r="G79" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>76</v>
@@ -7997,33 +8175,36 @@
         <v>4</v>
       </c>
       <c r="P79" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q79" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q79" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R79" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>95</v>
       </c>
       <c r="B80" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="D80" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D80" s="20" t="s">
-        <v>441</v>
-      </c>
-      <c r="E80" s="20" t="s">
-        <v>584</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>213</v>
-      </c>
       <c r="G80" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>22</v>
@@ -8033,7 +8214,7 @@
         <v>202</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K80" s="7">
         <f>VLOOKUP(J80,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8056,18 +8237,21 @@
         <v>3</v>
       </c>
       <c r="P80" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q80" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q80" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R80" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>97</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>10</v>
@@ -8079,10 +8263,10 @@
         <v>508</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>22</v>
@@ -8115,21 +8299,24 @@
         <v>1</v>
       </c>
       <c r="P81" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q81" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q81" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R81" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>98</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D82" s="17">
         <v>209</v>
@@ -8138,10 +8325,10 @@
         <v>506</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>11</v>
@@ -8151,7 +8338,7 @@
         <v>201</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K82" s="7">
         <f>VLOOKUP(J82,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8174,18 +8361,21 @@
         <v>2</v>
       </c>
       <c r="P82" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q82" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q82" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R82" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>99</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>10</v>
@@ -8197,10 +8387,10 @@
         <v>508</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>11</v>
@@ -8233,18 +8423,21 @@
         <v>1</v>
       </c>
       <c r="P83" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q83" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q83" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R83" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>100</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>10</v>
@@ -8256,10 +8449,10 @@
         <v>509</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>11</v>
@@ -8292,33 +8485,36 @@
         <v>1</v>
       </c>
       <c r="P84" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q84" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q84" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R84" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>102</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E85" s="20">
         <v>501</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>16</v>
@@ -8351,36 +8547,39 @@
         <v>2</v>
       </c>
       <c r="P85" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q85" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q85" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R85" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>104</v>
       </c>
       <c r="B86" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="D86" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D86" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="E86" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>227</v>
-      </c>
       <c r="G86" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H86" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I86" s="7">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
@@ -8410,33 +8609,36 @@
         <v>2</v>
       </c>
       <c r="P86" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q86" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q86" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R86" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>105</v>
       </c>
       <c r="B87" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>554</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="F87" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D87" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="E87" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>229</v>
-      </c>
       <c r="G87" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>22</v>
@@ -8469,33 +8671,36 @@
         <v>4</v>
       </c>
       <c r="P87" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q87" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="180" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q87" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R87" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="180" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>107</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="F88" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>231</v>
-      </c>
       <c r="G88" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>16</v>
@@ -8528,33 +8733,36 @@
         <v>7</v>
       </c>
       <c r="P88" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q88" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q88" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R88" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>108</v>
       </c>
       <c r="B89" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="F89" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>563</v>
-      </c>
-      <c r="E89" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>233</v>
-      </c>
       <c r="G89" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>16</v>
@@ -8587,33 +8795,36 @@
         <v>8</v>
       </c>
       <c r="P89" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q89" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q89" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R89" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>109</v>
       </c>
       <c r="B90" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="F90" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>573</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="E90" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>235</v>
-      </c>
       <c r="G90" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>22</v>
@@ -8623,7 +8834,7 @@
         <v>202</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K90" s="7">
         <f>VLOOKUP(J90,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8646,36 +8857,39 @@
         <v>8</v>
       </c>
       <c r="P90" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q90" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q90" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R90" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>112</v>
       </c>
       <c r="B91" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="D91" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="F91" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="D91" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="20" t="s">
-        <v>708</v>
-      </c>
-      <c r="F91" s="10" t="s">
-        <v>237</v>
-      </c>
       <c r="G91" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I91" s="7">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
@@ -8707,31 +8921,34 @@
       <c r="P91" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q91" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="135" x14ac:dyDescent="0.25">
+      <c r="Q91" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R91" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>114</v>
       </c>
       <c r="B92" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>562</v>
-      </c>
-      <c r="E92" s="20" t="s">
-        <v>702</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>240</v>
-      </c>
       <c r="G92" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>58</v>
@@ -8766,16 +8983,19 @@
       <c r="P92" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q92" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q92" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R92" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>115</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>10</v>
@@ -8787,10 +9007,10 @@
         <v>183</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>53</v>
@@ -8823,33 +9043,36 @@
         <v>1</v>
       </c>
       <c r="P93" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q93" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q93" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R93" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>116</v>
       </c>
       <c r="B94" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="F94" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="E94" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="G94" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>37</v>
@@ -8859,7 +9082,7 @@
         <v>205</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K94" s="7">
         <f>VLOOKUP(J94,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8882,13 +9105,16 @@
         <v>4</v>
       </c>
       <c r="P94" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q94" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q94" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R94" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>117</v>
       </c>
@@ -8896,19 +9122,19 @@
         <v>42</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>37</v>
@@ -8943,16 +9169,19 @@
       <c r="P95" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q95" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q95" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R95" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>118</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>10</v>
@@ -8964,10 +9193,10 @@
         <v>10</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>22</v>
@@ -8977,7 +9206,7 @@
         <v>202</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K96" s="7">
         <f>VLOOKUP(J96,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9000,33 +9229,36 @@
         <v>1</v>
       </c>
       <c r="P96" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q96" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q96" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R96" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>119</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E97" s="20">
         <v>501</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>16</v>
@@ -9059,33 +9291,36 @@
         <v>2</v>
       </c>
       <c r="P97" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q97" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q97" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R97" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>120</v>
       </c>
       <c r="B98" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E98" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="G98" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>16</v>
@@ -9118,33 +9353,36 @@
         <v>3</v>
       </c>
       <c r="P98" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q98" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q98" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R98" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>121</v>
       </c>
       <c r="B99" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>670</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="D99" s="19" t="s">
-        <v>671</v>
-      </c>
-      <c r="E99" s="20" t="s">
-        <v>451</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>255</v>
-      </c>
       <c r="G99" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>16</v>
@@ -9179,31 +9417,34 @@
       <c r="P99" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q99" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q99" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R99" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>122</v>
       </c>
       <c r="B100" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="F100" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="D100" s="17" t="s">
-        <v>670</v>
-      </c>
-      <c r="E100" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>257</v>
-      </c>
       <c r="G100" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>16</v>
@@ -9238,34 +9479,37 @@
       <c r="P100" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q100" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q100" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R100" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>124</v>
       </c>
       <c r="B101" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="D101" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D101" s="19" t="s">
-        <v>541</v>
-      </c>
-      <c r="E101" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="G101" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I101" s="7">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
@@ -9295,33 +9539,36 @@
         <v>7</v>
       </c>
       <c r="P101" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q101" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q101" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R101" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>126</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E102" s="20">
         <v>501</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>58</v>
@@ -9354,33 +9601,36 @@
         <v>2</v>
       </c>
       <c r="P102" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q102" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q102" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R102" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>127</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C103" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E103" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D103" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="E103" s="20" t="s">
-        <v>300</v>
-      </c>
       <c r="F103" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>58</v>
@@ -9413,33 +9663,36 @@
         <v>3</v>
       </c>
       <c r="P103" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q103" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q103" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R103" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>128</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E104" s="20">
         <v>501</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>58</v>
@@ -9472,33 +9725,36 @@
         <v>2</v>
       </c>
       <c r="P104" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q104" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q104" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R104" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>129</v>
       </c>
       <c r="B105" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="F105" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="C105" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D105" s="19" t="s">
-        <v>654</v>
-      </c>
-      <c r="E105" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>653</v>
-      </c>
       <c r="G105" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>58</v>
@@ -9533,34 +9789,37 @@
       <c r="P105" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q105" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" ht="135" x14ac:dyDescent="0.25">
+      <c r="Q105" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R105" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>130</v>
       </c>
       <c r="B106" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C106" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="E106" s="20" t="s">
-        <v>544</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>270</v>
-      </c>
       <c r="G106" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I106" s="7">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
@@ -9590,33 +9849,36 @@
         <v>5</v>
       </c>
       <c r="P106" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q106" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q106" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R106" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>134</v>
       </c>
       <c r="B107" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>303</v>
-      </c>
       <c r="D107" s="17" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G107" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H107" t="s">
         <v>37</v>
@@ -9651,16 +9913,19 @@
       <c r="P107" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q107" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q107" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R107" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>135</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>10</v>
@@ -9672,13 +9937,13 @@
         <v>183</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G108" t="s">
+        <v>528</v>
+      </c>
+      <c r="H108" t="s">
         <v>529</v>
-      </c>
-      <c r="H108" t="s">
-        <v>530</v>
       </c>
       <c r="I108" s="7">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
@@ -9708,18 +9973,21 @@
         <v>1</v>
       </c>
       <c r="P108" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q108" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q108" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R108" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>136</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>10</v>
@@ -9731,10 +9999,10 @@
         <v>240</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G109" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H109" t="s">
         <v>58</v>
@@ -9767,36 +10035,39 @@
         <v>1</v>
       </c>
       <c r="P109" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q109" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q109" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R109" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>137</v>
       </c>
       <c r="B110" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="D110" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="D110" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="21" t="s">
-        <v>307</v>
-      </c>
       <c r="F110" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G110" t="s">
+        <v>528</v>
+      </c>
+      <c r="H110" t="s">
         <v>529</v>
-      </c>
-      <c r="H110" t="s">
-        <v>530</v>
       </c>
       <c r="I110" s="7">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
@@ -9826,21 +10097,24 @@
         <v>6</v>
       </c>
       <c r="P110" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q110" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q110" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R110" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>138</v>
       </c>
       <c r="B111" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>308</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>309</v>
       </c>
       <c r="D111" s="19" t="s">
         <v>10</v>
@@ -9849,10 +10123,10 @@
         <v>236</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G111" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H111" t="s">
         <v>11</v>
@@ -9885,18 +10159,21 @@
         <v>1</v>
       </c>
       <c r="P111" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q111" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q111" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R111" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>139</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>10</v>
@@ -9908,10 +10185,10 @@
         <v>10</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>22</v>
@@ -9921,7 +10198,7 @@
         <v>202</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K112" s="7">
         <f>VLOOKUP(J112,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9944,33 +10221,36 @@
         <v>1</v>
       </c>
       <c r="P112" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q112" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+      <c r="Q112" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R112" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>140</v>
       </c>
       <c r="B113" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="C113" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>648</v>
-      </c>
-      <c r="E113" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>617</v>
-      </c>
       <c r="G113" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>16</v>
@@ -10003,33 +10283,36 @@
         <v>18</v>
       </c>
       <c r="P113" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q113" s="19">
+        <v>618</v>
+      </c>
+      <c r="Q113" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R113" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>141</v>
       </c>
       <c r="B114" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="F114" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D114" s="19" t="s">
-        <v>623</v>
-      </c>
-      <c r="E114" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>622</v>
-      </c>
       <c r="G114" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>58</v>
@@ -10062,33 +10345,36 @@
         <v>3</v>
       </c>
       <c r="P114" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q114" s="19">
+        <v>618</v>
+      </c>
+      <c r="Q114" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R114" s="19">
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>142</v>
       </c>
       <c r="B115" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>598</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="C115" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="E115" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>625</v>
-      </c>
       <c r="G115" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>58</v>
@@ -10121,33 +10407,36 @@
         <v>2</v>
       </c>
       <c r="P115" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q115" s="19">
+        <v>618</v>
+      </c>
+      <c r="Q115" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R115" s="19">
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>143</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" s="19" t="s">
         <v>630</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D116" s="19" t="s">
+      <c r="E116" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="E116" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>632</v>
-      </c>
       <c r="G116" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>58</v>
@@ -10180,33 +10469,36 @@
         <v>5</v>
       </c>
       <c r="P116" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q116" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="Q116" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R116" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>144</v>
       </c>
       <c r="B117" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E117" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>16</v>
@@ -10239,33 +10531,36 @@
         <v>1</v>
       </c>
       <c r="P117" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q117" s="19" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="Q117" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R117" s="19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>145</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E118" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H118" t="s">
         <v>11</v>
@@ -10298,33 +10593,36 @@
         <v>1</v>
       </c>
       <c r="P118" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q118" s="19" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="Q118" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R118" s="19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>146</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D119" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H119" t="s">
         <v>11</v>
@@ -10357,33 +10655,36 @@
         <v>6</v>
       </c>
       <c r="P119" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q119" s="19" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="Q119" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R119" s="19" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>147</v>
       </c>
       <c r="B120" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D120" s="17" t="s">
-        <v>645</v>
-      </c>
-      <c r="E120" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>644</v>
-      </c>
       <c r="G120" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>16</v>
@@ -10416,33 +10717,36 @@
         <v>1</v>
       </c>
       <c r="P120" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q120" s="19" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+      <c r="Q120" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R120" s="19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>148</v>
       </c>
       <c r="B121" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="D121" t="s">
+        <v>682</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="F121" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="D121" t="s">
-        <v>683</v>
-      </c>
-      <c r="E121" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>650</v>
-      </c>
       <c r="G121" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>11</v>
@@ -10477,31 +10781,34 @@
       <c r="P121" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q121" s="19" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q121" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R121" s="19" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>149</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>22</v>
@@ -10511,7 +10818,7 @@
         <v>202</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K122" s="7">
         <f>VLOOKUP(J122,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10536,34 +10843,37 @@
       <c r="P122" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q122" s="19" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q122" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R122" s="19" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>150</v>
       </c>
       <c r="B123" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="C123" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D123" s="19" t="s">
+      <c r="E123" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="E123" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>676</v>
-      </c>
       <c r="G123" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H123" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I123" s="7">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -10595,31 +10905,34 @@
       <c r="P123" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q123" s="19" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q123" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R123" s="19" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>151</v>
       </c>
       <c r="B124" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="F124" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="C124" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="D124" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E124" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>688</v>
-      </c>
       <c r="G124" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>16</v>
@@ -10654,34 +10967,37 @@
       <c r="P124" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q124" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q124" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="R124" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>152</v>
       </c>
       <c r="B125" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="F125" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="C125" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D125" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E125" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>704</v>
-      </c>
       <c r="G125" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H125" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I125" s="7">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -10713,16 +11029,19 @@
       <c r="P125" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q125" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q125" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R125" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>153</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>10</v>
@@ -10731,16 +11050,16 @@
         <v>10</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F126" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G126" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H126" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I126" s="7">
         <f>VLOOKUP(H126,cardsort_group_IDs!A:B,2,0)</f>
@@ -10772,34 +11091,37 @@
       <c r="P126" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q126" s="19" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q126" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="R126" s="19" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>154</v>
       </c>
       <c r="B127" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="F127" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="C127" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E127" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>712</v>
-      </c>
       <c r="G127" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H127" s="7" t="s">
         <v>529</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>530</v>
       </c>
       <c r="I127" s="7">
         <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
@@ -10831,11 +11153,14 @@
       <c r="P127" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="Q127" s="19" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q127" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="R127" s="19" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="M128" s="7"/>
     </row>
     <row r="129" spans="13:13" x14ac:dyDescent="0.25">
@@ -10938,8 +11263,8 @@
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
     <cfRule type="duplicateValues" dxfId="17" priority="7"/>
@@ -10962,20 +11287,20 @@
     <cfRule type="duplicateValues" dxfId="10" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64">
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
     <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69">
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J106">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10996,16 +11321,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B1" t="s">
         <v>421</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>422</v>
-      </c>
-      <c r="C1" t="s">
-        <v>715</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11013,13 +11338,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D2" t="s">
         <v>315</v>
-      </c>
-      <c r="C2" t="s">
-        <v>725</v>
-      </c>
-      <c r="D2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11027,13 +11352,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" t="s">
+        <v>724</v>
+      </c>
+      <c r="D3" t="s">
         <v>317</v>
-      </c>
-      <c r="C3" t="s">
-        <v>725</v>
-      </c>
-      <c r="D3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11041,13 +11366,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" t="s">
+        <v>724</v>
+      </c>
+      <c r="D4" t="s">
         <v>319</v>
-      </c>
-      <c r="C4" t="s">
-        <v>725</v>
-      </c>
-      <c r="D4" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11055,13 +11380,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" t="s">
+        <v>724</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>321</v>
-      </c>
-      <c r="C5" t="s">
-        <v>725</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11069,13 +11394,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" t="s">
+        <v>724</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>323</v>
-      </c>
-      <c r="C6" t="s">
-        <v>725</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11083,13 +11408,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>325</v>
-      </c>
-      <c r="C7" t="s">
-        <v>725</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11097,13 +11422,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" t="s">
+        <v>724</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>327</v>
-      </c>
-      <c r="C8" t="s">
-        <v>725</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11111,13 +11436,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" t="s">
+        <v>724</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>329</v>
-      </c>
-      <c r="C9" t="s">
-        <v>725</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11125,13 +11450,13 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C10" t="s">
+        <v>724</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>331</v>
-      </c>
-      <c r="C10" t="s">
-        <v>725</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11139,13 +11464,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D11" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11153,13 +11478,13 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" t="s">
+        <v>724</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>333</v>
-      </c>
-      <c r="C12" t="s">
-        <v>725</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11167,13 +11492,13 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
+        <v>334</v>
+      </c>
+      <c r="C13" t="s">
+        <v>724</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>335</v>
-      </c>
-      <c r="C13" t="s">
-        <v>725</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11181,13 +11506,13 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" t="s">
+        <v>724</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>337</v>
-      </c>
-      <c r="C14" t="s">
-        <v>725</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11195,13 +11520,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C15" t="s">
+        <v>724</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="C15" t="s">
-        <v>725</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11209,13 +11534,13 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" t="s">
+        <v>724</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>341</v>
-      </c>
-      <c r="C16" t="s">
-        <v>725</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11223,13 +11548,13 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C17" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D17" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11237,13 +11562,13 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
+        <v>342</v>
+      </c>
+      <c r="C18" t="s">
+        <v>724</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>343</v>
-      </c>
-      <c r="C18" t="s">
-        <v>725</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11251,13 +11576,13 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
+        <v>344</v>
+      </c>
+      <c r="C19" t="s">
+        <v>724</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="C19" t="s">
-        <v>725</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11265,13 +11590,13 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
+        <v>346</v>
+      </c>
+      <c r="C20" t="s">
+        <v>724</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>347</v>
-      </c>
-      <c r="C20" t="s">
-        <v>725</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11279,13 +11604,13 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" t="s">
+        <v>724</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>349</v>
-      </c>
-      <c r="C21" t="s">
-        <v>725</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11293,13 +11618,13 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22" t="s">
+        <v>724</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>351</v>
-      </c>
-      <c r="C22" t="s">
-        <v>725</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11307,13 +11632,13 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
+        <v>352</v>
+      </c>
+      <c r="C23" t="s">
+        <v>724</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="C23" t="s">
-        <v>725</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11321,13 +11646,13 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
+        <v>354</v>
+      </c>
+      <c r="C24" t="s">
+        <v>724</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="C24" t="s">
-        <v>725</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11335,13 +11660,13 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C25" t="s">
+        <v>724</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>357</v>
-      </c>
-      <c r="C25" t="s">
-        <v>725</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11349,13 +11674,13 @@
         <v>57</v>
       </c>
       <c r="B26" t="s">
+        <v>358</v>
+      </c>
+      <c r="C26" t="s">
+        <v>724</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>359</v>
-      </c>
-      <c r="C26" t="s">
-        <v>725</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11363,13 +11688,13 @@
         <v>62</v>
       </c>
       <c r="B27" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" t="s">
+        <v>724</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="C27" t="s">
-        <v>725</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11377,13 +11702,13 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
+        <v>362</v>
+      </c>
+      <c r="C28" t="s">
+        <v>724</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="C28" t="s">
-        <v>725</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11391,13 +11716,13 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
+        <v>364</v>
+      </c>
+      <c r="C29" t="s">
+        <v>724</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>365</v>
-      </c>
-      <c r="C29" t="s">
-        <v>725</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11405,13 +11730,13 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11419,13 +11744,13 @@
         <v>96</v>
       </c>
       <c r="B31" t="s">
+        <v>367</v>
+      </c>
+      <c r="C31" t="s">
+        <v>724</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="C31" t="s">
-        <v>725</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -11433,13 +11758,13 @@
         <v>101</v>
       </c>
       <c r="B32" t="s">
+        <v>369</v>
+      </c>
+      <c r="C32" t="s">
+        <v>724</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C32" t="s">
-        <v>725</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11447,13 +11772,13 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
+        <v>371</v>
+      </c>
+      <c r="C33" t="s">
+        <v>724</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C33" t="s">
-        <v>725</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -11461,13 +11786,13 @@
         <v>108</v>
       </c>
       <c r="B34" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" t="s">
+        <v>724</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="C34" t="s">
-        <v>725</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11475,13 +11800,13 @@
         <v>111</v>
       </c>
       <c r="B35" t="s">
+        <v>375</v>
+      </c>
+      <c r="C35" t="s">
+        <v>724</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>376</v>
-      </c>
-      <c r="C35" t="s">
-        <v>725</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11489,13 +11814,13 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
+        <v>377</v>
+      </c>
+      <c r="C36" t="s">
+        <v>724</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>378</v>
-      </c>
-      <c r="C36" t="s">
-        <v>725</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11503,13 +11828,13 @@
         <v>131</v>
       </c>
       <c r="B37" t="s">
+        <v>380</v>
+      </c>
+      <c r="C37" t="s">
+        <v>724</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>381</v>
-      </c>
-      <c r="C37" t="s">
-        <v>725</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -11517,13 +11842,13 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
+        <v>382</v>
+      </c>
+      <c r="C38" t="s">
+        <v>724</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>383</v>
-      </c>
-      <c r="C38" t="s">
-        <v>725</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -11531,13 +11856,13 @@
         <v>160</v>
       </c>
       <c r="B39" t="s">
+        <v>384</v>
+      </c>
+      <c r="C39" t="s">
+        <v>724</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>385</v>
-      </c>
-      <c r="C39" t="s">
-        <v>725</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11548,10 +11873,10 @@
         <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11559,13 +11884,13 @@
         <v>182</v>
       </c>
       <c r="B41" t="s">
+        <v>387</v>
+      </c>
+      <c r="C41" t="s">
+        <v>724</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>388</v>
-      </c>
-      <c r="C41" t="s">
-        <v>725</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -11573,13 +11898,13 @@
         <v>183</v>
       </c>
       <c r="B42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C42" t="s">
+        <v>724</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>390</v>
-      </c>
-      <c r="C42" t="s">
-        <v>725</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11587,13 +11912,13 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C43" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11601,13 +11926,13 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C44" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11618,10 +11943,10 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -11632,10 +11957,10 @@
         <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -11643,13 +11968,13 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C47" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D47" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11657,13 +11982,13 @@
         <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11671,13 +11996,13 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C49" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -11685,10 +12010,10 @@
         <v>232</v>
       </c>
       <c r="B50" t="s">
+        <v>398</v>
+      </c>
+      <c r="D50" s="15" t="s">
         <v>399</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -11696,13 +12021,13 @@
         <v>233</v>
       </c>
       <c r="B51" t="s">
+        <v>400</v>
+      </c>
+      <c r="C51" t="s">
+        <v>724</v>
+      </c>
+      <c r="D51" s="15" t="s">
         <v>401</v>
-      </c>
-      <c r="C51" t="s">
-        <v>725</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -11710,13 +12035,13 @@
         <v>234</v>
       </c>
       <c r="B52" t="s">
+        <v>402</v>
+      </c>
+      <c r="C52" t="s">
+        <v>724</v>
+      </c>
+      <c r="D52" s="15" t="s">
         <v>403</v>
-      </c>
-      <c r="C52" t="s">
-        <v>725</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -11724,13 +12049,13 @@
         <v>235</v>
       </c>
       <c r="B53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C53" t="s">
+        <v>724</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="C53" t="s">
-        <v>725</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -11738,13 +12063,13 @@
         <v>236</v>
       </c>
       <c r="B54" t="s">
+        <v>406</v>
+      </c>
+      <c r="C54" t="s">
+        <v>724</v>
+      </c>
+      <c r="D54" s="15" t="s">
         <v>407</v>
-      </c>
-      <c r="C54" t="s">
-        <v>725</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -11752,13 +12077,13 @@
         <v>237</v>
       </c>
       <c r="B55" t="s">
+        <v>408</v>
+      </c>
+      <c r="C55" t="s">
+        <v>724</v>
+      </c>
+      <c r="D55" s="15" t="s">
         <v>409</v>
-      </c>
-      <c r="C55" t="s">
-        <v>725</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -11766,13 +12091,13 @@
         <v>238</v>
       </c>
       <c r="B56" t="s">
+        <v>410</v>
+      </c>
+      <c r="C56" t="s">
+        <v>724</v>
+      </c>
+      <c r="D56" s="15" t="s">
         <v>411</v>
-      </c>
-      <c r="C56" t="s">
-        <v>725</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -11780,13 +12105,13 @@
         <v>240</v>
       </c>
       <c r="B57" t="s">
+        <v>412</v>
+      </c>
+      <c r="C57" t="s">
+        <v>724</v>
+      </c>
+      <c r="D57" s="15" t="s">
         <v>413</v>
-      </c>
-      <c r="C57" t="s">
-        <v>725</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -11794,13 +12119,13 @@
         <v>241</v>
       </c>
       <c r="B58" t="s">
+        <v>414</v>
+      </c>
+      <c r="C58" t="s">
+        <v>724</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>415</v>
-      </c>
-      <c r="C58" t="s">
-        <v>725</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -11808,13 +12133,13 @@
         <v>243</v>
       </c>
       <c r="B59" t="s">
+        <v>416</v>
+      </c>
+      <c r="C59" t="s">
+        <v>724</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>417</v>
-      </c>
-      <c r="C59" t="s">
-        <v>725</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -11822,13 +12147,13 @@
         <v>244</v>
       </c>
       <c r="B60" t="s">
+        <v>418</v>
+      </c>
+      <c r="C60" t="s">
+        <v>724</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>419</v>
-      </c>
-      <c r="C60" t="s">
-        <v>725</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -11836,13 +12161,13 @@
         <v>501</v>
       </c>
       <c r="B61" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C61" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -11850,13 +12175,13 @@
         <v>502</v>
       </c>
       <c r="B62" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C62" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -11864,13 +12189,13 @@
         <v>503</v>
       </c>
       <c r="B63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C63" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -11878,13 +12203,13 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
+        <v>471</v>
+      </c>
+      <c r="C64" t="s">
+        <v>724</v>
+      </c>
+      <c r="D64" s="15" t="s">
         <v>472</v>
-      </c>
-      <c r="C64" t="s">
-        <v>725</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -11892,13 +12217,13 @@
         <v>505</v>
       </c>
       <c r="B65" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C65" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11909,10 +12234,10 @@
         <v>67</v>
       </c>
       <c r="C66" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -11920,13 +12245,13 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C67" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -11937,10 +12262,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -11951,10 +12276,10 @@
         <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -11962,923 +12287,923 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C70" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D70" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B71" t="s">
         <v>485</v>
       </c>
-      <c r="B71" t="s">
-        <v>486</v>
-      </c>
       <c r="C71" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="B72" t="s">
         <v>487</v>
       </c>
-      <c r="B72" t="s">
-        <v>488</v>
-      </c>
       <c r="C72" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C73" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B74" t="s">
         <v>490</v>
       </c>
-      <c r="B74" t="s">
-        <v>491</v>
-      </c>
       <c r="C74" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C75" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="B76" t="s">
         <v>493</v>
       </c>
-      <c r="B76" t="s">
-        <v>494</v>
-      </c>
       <c r="C76" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="B77" t="s">
         <v>495</v>
       </c>
-      <c r="B77" t="s">
-        <v>496</v>
-      </c>
       <c r="C77" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B78" t="s">
         <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B79" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C79" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B80" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C80" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C81" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B82" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C82" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="B83" t="s">
         <v>502</v>
       </c>
-      <c r="B83" t="s">
-        <v>503</v>
-      </c>
       <c r="C83" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="B84" t="s">
         <v>504</v>
       </c>
-      <c r="B84" t="s">
-        <v>505</v>
-      </c>
       <c r="C84" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B85" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C85" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="B86" t="s">
         <v>507</v>
       </c>
-      <c r="B86" t="s">
-        <v>508</v>
-      </c>
       <c r="C86" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="B87" t="s">
         <v>509</v>
       </c>
-      <c r="B87" t="s">
-        <v>510</v>
-      </c>
       <c r="C87" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="B88" t="s">
         <v>511</v>
       </c>
-      <c r="B88" t="s">
-        <v>512</v>
-      </c>
       <c r="C88" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="B89" t="s">
         <v>513</v>
       </c>
-      <c r="B89" t="s">
-        <v>514</v>
-      </c>
       <c r="C89" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="B90" t="s">
         <v>515</v>
       </c>
-      <c r="B90" t="s">
-        <v>516</v>
-      </c>
       <c r="C90" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B91" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C91" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C92" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B93" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C93" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B94" t="s">
         <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B95" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C95" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C96" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B97" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C97" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="B98" t="s">
         <v>476</v>
       </c>
-      <c r="B98" t="s">
-        <v>477</v>
-      </c>
       <c r="C98" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B99" t="s">
         <v>81</v>
       </c>
       <c r="C99" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B100" t="s">
         <v>91</v>
       </c>
       <c r="C100" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="B101" t="s">
         <v>478</v>
       </c>
-      <c r="B101" t="s">
-        <v>479</v>
-      </c>
       <c r="C101" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="B102" t="s">
         <v>480</v>
       </c>
-      <c r="B102" t="s">
-        <v>481</v>
-      </c>
       <c r="C102" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="B103" t="s">
         <v>482</v>
       </c>
-      <c r="B103" t="s">
-        <v>483</v>
-      </c>
       <c r="C103" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B104" t="s">
         <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B105" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C105" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B106" t="s">
         <v>120</v>
       </c>
       <c r="C106" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B107" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C107" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B108" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B109" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C109" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B110" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C110" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B111" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B112" t="s">
         <v>40</v>
       </c>
       <c r="C112" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B113" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C113" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B114" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C114" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B115" t="s">
         <v>586</v>
       </c>
-      <c r="B115" t="s">
-        <v>587</v>
-      </c>
       <c r="C115" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D115" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B116" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C116" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D116" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B117" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C117" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D117" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B118" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C118" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D118" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B119" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C119" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D119" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B120" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C120" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D120" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B121" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C121" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D121" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B122" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C122" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D122" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B123" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C123" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D123" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B124" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C124" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D124" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B125" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C125" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D125" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B126" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C126" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D126" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B127" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C127" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D127" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B128" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C128" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D128" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B129" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C129" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D129" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B130" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C130" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D130" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B131" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C131" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D131" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="B132" t="s">
         <v>645</v>
       </c>
-      <c r="B132" t="s">
-        <v>646</v>
-      </c>
       <c r="C132" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D132" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B133" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C133" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D133" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B134" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C134" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D134" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="B135" t="s">
+        <v>699</v>
+      </c>
+      <c r="C135" t="s">
+        <v>724</v>
+      </c>
+      <c r="D135" t="s">
         <v>698</v>
-      </c>
-      <c r="B135" t="s">
-        <v>700</v>
-      </c>
-      <c r="C135" t="s">
-        <v>725</v>
-      </c>
-      <c r="D135" t="s">
-        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -12929,7 +13254,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13014,7 +13339,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -13206,7 +13531,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -13214,7 +13539,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -13222,7 +13547,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -13230,7 +13555,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -13256,50 +13581,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>716</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
+        <v>719</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>720</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>723</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>725</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>726</v>
       </c>
     </row>
   </sheetData>
